--- a/data/Evidence_Table.xlsx
+++ b/data/Evidence_Table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramanaye/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramanaye/Documents/GitHub/cancer_nutrition_evidence_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F14132E-BE0C-D94F-9059-BC4A3F134180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B8C70F-0CA1-6B48-B3C3-43510BB83579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16140" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
   </bookViews>
   <sheets>
     <sheet name="Evidence Table" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="305">
   <si>
     <t>Year</t>
   </si>
@@ -47,16 +47,10 @@
     <t>Key Findings</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
     <t>Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Author </t>
   </si>
   <si>
     <t>Title</t>
@@ -458,9 +452,6 @@
     <t>REHAB group- received standard post-surgical rehabilitation</t>
   </si>
   <si>
-    <t>high compliance with supervised sessions (98%) did not lead to a greater increase in functional capacity than previously seen in studies using only unsupervised home-based programs, suggesting that factors like exercise intensity or higher frequency of supervised sessions might be necessary to further improve outcomes</t>
-  </si>
-  <si>
     <t>&gt;90% in PREHAB+ group in preoperative phase
 &gt;70% for both groups in postoperative phase</t>
   </si>
@@ -514,9 +505,6 @@
 3. Psychology- A 60-min psychological session for anxiety reduction, lifestyle advise including smoking cessation and alcohol abstinence</t>
   </si>
   <si>
-    <t xml:space="preserve"> A major conclusion was that such a complex, trimodal program is feasible and effective in a Central European healthcare environment with limited expenditure</t>
-  </si>
-  <si>
     <t>Prehabilitation - 92 (15)
 Control - 92 (20)</t>
   </si>
@@ -528,6 +516,651 @@
   </si>
   <si>
     <t>Low Risk</t>
+  </si>
+  <si>
+    <t>Prehab -24 (6)
+Control -10 (2)</t>
+  </si>
+  <si>
+    <t>Control group- received standard hospital care</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nutritional component -93.2%
+Exercises- 88.2% (home-based) and 84.1% (supervised)
+</t>
+  </si>
+  <si>
+    <t>The study's open-label design and retrospective registration increased risks of performance, detection, and outcome reporting bias. Furthermore, the COVID-19 pandemic caused significant missing data and a 38.2% dropout rate for preoperative assessments, necessitating the use of statistical imputations</t>
+  </si>
+  <si>
+    <t>Multimodal Prehabilitation During Neoadjuvant Therapy Prior to Esophagogastric Cancer Resection: Effect on Cardiopulmonary Exercise Test Performance, Muscle Mass and Quality of Life—A Pilot Randomized Clinical Trial</t>
+  </si>
+  <si>
+    <t>Esophagogastric</t>
+  </si>
+  <si>
+    <t>Prognostic impact of a 3-week multimodal prehabilitation program on frail elderly patients undergoing elective gastric cancer surgery: a randomized trial</t>
+  </si>
+  <si>
+    <t>Chen et al.</t>
+  </si>
+  <si>
+    <t>Lung</t>
+  </si>
+  <si>
+    <t>Abdominal</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 123 (26)
+Control– 128 (20)</t>
+  </si>
+  <si>
+    <t>Control group- received standard care and followed ERAS pathway</t>
+  </si>
+  <si>
+    <t>77% for exercise
+Not reported for other components</t>
+  </si>
+  <si>
+    <t>Early termination and open-label design</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 64 (5)
+Control– 64 (5)</t>
+  </si>
+  <si>
+    <t>Control group- received standard preoperative care</t>
+  </si>
+  <si>
+    <t>Low (43%) participation rate, a lack of participant blinding, and the absence of objective tools to monitor intervention adherence</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 43 (6) 
+Control – 42 (6)</t>
+  </si>
+  <si>
+    <t>2 weeks</t>
+  </si>
+  <si>
+    <t>The study featured a relatively small sample size from a single center, potentially limiting generalizability. Additionally, the follow-up period was limited to 30 days, leaving long-term recovery effects unknown</t>
+  </si>
+  <si>
+    <t>Control group-  received usual clinical care</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 18 (6) 
+Control – 22 (2)</t>
+  </si>
+  <si>
+    <t>control group -received standard care which consisted of nutritional counseling, physical activity recommendations, and advice on smoking cessation</t>
+  </si>
+  <si>
+    <t>The study was underpowered due to a small sample size and a potential bias from the control group receiving "partial prehabilitation" through standard preoperative advice</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 35 (16) 
+Control – 35 (14)</t>
+  </si>
+  <si>
+    <t>Control group-received standard perioperative care, which included risk assessment, medication management, treatment of anemia, and smoking cessation counseling</t>
+  </si>
+  <si>
+    <t>27 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6 days </t>
+  </si>
+  <si>
+    <t>The study had a significant loss to follow-up at post-surgical assessment points, primarily due to logistic challenges like the long distance between patients' homes and the hospital,. These factors hinder the generalizability of the results</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 30 (7) 
+Control – 30 (9)</t>
+  </si>
+  <si>
+    <t>Standard care group- received no specific education or recommendations regarding physical activity, nutrition, or relaxation beyond the standard ERAS protocols</t>
+  </si>
+  <si>
+    <t>The study is primarily limited by its small sample size as a pilot study and a high loss to follow-up rate (over 25%) largely driven by the COVID-19 pandemic</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 19 (3) 
+Control– 21 (1)</t>
+  </si>
+  <si>
+    <t>Control group-  received standard care, including intravenous iron for anaemic patients, preoperative lung physiotherapy, patient education, limited fasting, carbohydrate loading, and the full enhanced recovery after surgery (ERAS) pathway</t>
+  </si>
+  <si>
+    <t>4 weeks</t>
+  </si>
+  <si>
+    <t>Exercise - 100%
+Nutrition - 98%</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 35 (3) 
+Control – 37 (6)</t>
+  </si>
+  <si>
+    <t>Control group- received usual care</t>
+  </si>
+  <si>
+    <t>6 months</t>
+  </si>
+  <si>
+    <t>Exercise - 41% were adherent to aerobic exercise and 26% were adherent to resistance training</t>
+  </si>
+  <si>
+    <t>Prehabilitation - 75 (9) 
+Control– 75 (10)</t>
+  </si>
+  <si>
+    <t>Control group -received standard perioperative care, which included routine preoperative education but no structured exercise, nutritional, or psychological interventions</t>
+  </si>
+  <si>
+    <t>1 week</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Single-center design and short follow-up period that lacks long-term survival data</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 45 (2) 
+Control – 45 (3)</t>
+  </si>
+  <si>
+    <t>Control group -received standard care, following hospital's  ERAS  protocol</t>
+  </si>
+  <si>
+    <t>14.2 ± 3.6 weeks</t>
+  </si>
+  <si>
+    <t>The study relied on self-reported logs rather than wearable device data and had a small sample size. It also lacked detailed daily nutritional intake data and was conducted at a single center, which may limit the generalizability of the findings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control group received one initial session of exercise instruction from a physical therapist, but no specific exercise routine was set, did not receive additional instructions, feedback, or oral nutritional supplements </t>
+  </si>
+  <si>
+    <t>m-Prehab – 25 (0) 
+Control – 25 (1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92% for protein intake 
+</t>
+  </si>
+  <si>
+    <t>Prehabilitation (Group C) – 33 (2)
+Exercise Only (Group B) – 31 (5)
+Control (Group A) – 35 (4)</t>
+  </si>
+  <si>
+    <t>Group A (standard care).- included physical activity recommendations, nutritional counseling (if malnourished), smoking cessation, alcohol intake reduction, and wearing pedometers to track daily steps</t>
+  </si>
+  <si>
+    <t>8.7 weeks</t>
+  </si>
+  <si>
+    <t>76% for the exercise program, 62% for walking steps, 160% for handgrip training, and 45% for nutritional supplementation.</t>
+  </si>
+  <si>
+    <t>Small-scale, single-center, open-label trial, which may limit generalizability and introduce participant bias. Exercise therapy and non-supplement dietary intake were largely unsupervised and left to the patients' own motivation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Single-center design, small sample size, and low compliance with nutritional supplements. Also, it lacked long-term evaluation of oncological outcomes and physical performance</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 54 (5)
+ Control – 56 (4)</t>
+  </si>
+  <si>
+    <t>Control group received standard care based on ERAS principles</t>
+  </si>
+  <si>
+    <t>76% for walking, 77% for resistance training, and 73% for HMB supplementation</t>
+  </si>
+  <si>
+    <t>The study was a single-center trial with a small sample size not powered to detect differences in postoperative clinical outcomes. Its open-label design and reliance on patient-reported diaries for adherence may have also introduced bias</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 52 (10) 
+Control – 52 (6)</t>
+  </si>
+  <si>
+    <t>Control group received standard preoperative care, which included dietary guidance, advice on maintaining warmth, and precautions to prevent respiratory infections</t>
+  </si>
+  <si>
+    <t>study was limited by its single-center design and lack of blinding, It excluded structured resistance training and relied on the 6-minute walk test rather than more sensitive cardiorespiratory fitness measures</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 100 (0)
+ Control – 100 (0)</t>
+  </si>
+  <si>
+    <t>control group received standard perioperative care, general instructions on exercises like deep breathing and effective coughing. They did not receive additional nutritional supplements.</t>
+  </si>
+  <si>
+    <t>7 days</t>
+  </si>
+  <si>
+    <t>100% for inspiratory muscle training, 98.5% for aerobic exercise, 96% for prescribed nutritional supplements, and 94% for psychological-related activities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Study's short intervention duration (7 days) and single-center design may limit the generalizability and full physiological impact of the findings. </t>
+  </si>
+  <si>
+    <t>36  days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 weeks </t>
+  </si>
+  <si>
+    <t>3-6 weeks</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 92 (±33) days</t>
+  </si>
+  <si>
+    <t>17 days</t>
+  </si>
+  <si>
+    <t>preoperative period and continued for 6–8 weeks after surgery.</t>
+  </si>
+  <si>
+    <t>Aerobic exercise</t>
+  </si>
+  <si>
+    <t>Resistance training</t>
+  </si>
+  <si>
+    <t>Protein supplementation</t>
+  </si>
+  <si>
+    <t>Overall Risk of bias</t>
+  </si>
+  <si>
+    <t>Concerning domain(s)</t>
+  </si>
+  <si>
+    <t>Psychological</t>
+  </si>
+  <si>
+    <t>Lifestyle (smoking/alcohol)</t>
+  </si>
+  <si>
+    <t>Post-operative complications</t>
+  </si>
+  <si>
+    <t>Length of hospital stay</t>
+  </si>
+  <si>
+    <t>Quality of Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colorectal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lung </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gastric </t>
+  </si>
+  <si>
+    <t>Pancreatic</t>
+  </si>
+  <si>
+    <t>Bladder</t>
+  </si>
+  <si>
+    <t>Colorectal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breast </t>
+  </si>
+  <si>
+    <t>Gastric</t>
+  </si>
+  <si>
+    <t>Esophageal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esophageal </t>
+  </si>
+  <si>
+    <t>Periampullary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esophagogastric </t>
+  </si>
+  <si>
+    <t>Intervention Overview</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 57 (5) 
+Control – 58 (6)</t>
+  </si>
+  <si>
+    <t>Multimodal program:
+1. Exercise: A 3-week individualized, supervised program consisting of 30 minutes of moderate aerobic exercise (3+ times/week) and 25 minutes of resistance training focusing on major muscle groups (2-3 times/week), overseen by a physiotherapist.
+2. Nutritional support: Individualized optimization by a dietitian aiming for 1.5 g/kg/d protein intake, including whey protein supplementation if necessary, and calorie tracking via an app/website.
+3. Respiratory training: Daily use of a TRI-BALL® respiratory trainer for 10 minutes, 3 times daily, using the Sustained Maximal Inspiration (SMI) technique.
+4. Psychosocial: Anxiety-coping interventions including relaxation techniques and deep breathing exercises provided by a trained nurse, with psychologist referral if needed</t>
+  </si>
+  <si>
+    <t>Significantly lower incidence of severe complications (CCI &gt; 20) in the intervention group (10.5% vs. 25.9%, p = 0.033) and fewer medical complications (12.3% vs. 29.3%, p = 0.025). Improved functional walking capacity with more patients in the intervention group achieving a preoperative increase of ≥ 20 m in 6MWD (47.4% vs. 27.6%, p = 0.028) and returning to baseline 6MWD levels at 4 weeks postoperatively (63.2% vs. 43.1%, p = 0.031). Multimodal prehabilitation was an independent protective factor for 30-day overall complications (OR 1.971, p = 0.039). No significant differences were observed in the primary outcome of 30-day CCI, nor in length of hospital stay, 30-day readmission rates, quality of life, or psychological status</t>
+  </si>
+  <si>
+    <t>High, with 85% of participants completing 3 weekly aerobic sessions, 83% performing at least 2 resistance sessions, 92% adherence to respiratory training, and 100% adherence to protein supplementation</t>
+  </si>
+  <si>
+    <t>The single-center design and small sample size may limit generalizability and increase the risk of false-positive or false-negative results. Findings may be limited to centers with well-established ERAS protocols and a high prevalence of minimally invasive surgery</t>
+  </si>
+  <si>
+    <t>Allen et al.</t>
+  </si>
+  <si>
+    <t>Pilot Randomized Controlled Trial</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 26
+Control – 28</t>
+  </si>
+  <si>
+    <t>Multimodal program (15 weeks during neoadjuvant therapy):
+1. Exercise: Twice-weekly 1-hour supervised sessions including 25 minutes of cycling at 40%–60% heart rate reserve, resistance training for six major muscle groups (2 sets of 12 repetitions), and flexibility exercises. This was supplemented by thrice-weekly 1-hour home exercises focusing on resistance and core stability.
+2. Nutritional support: Tailored, needs-based input from specialist dieticians focused on optimizing calorie and protein intake.
+3. Psychosocial (Medical Coaching): Six sessions (face-to-face or teleconference) with accredited medical coaches focusing on resilience, emotional management, and goal setting</t>
+  </si>
+  <si>
+    <t>No significant difference was observed in the primary outcome of anaerobic threshold (AT) between groups. However, the prehabilitation group showed a significantly attenuated decline in peak VO2 compared to controls (-0.4 vs. -2.5 mL/kg/min; p = 0.022). Prehabilitation also resulted in significantly less skeletal muscle loss (-11.6 vs. -15.6 cm2/m2; p = 0.049) and improved retention of hand-grip strength postoperatively (p = 0.009 at 6 weeks). Quality of life (global health status) and psychological markers (anxiety and depression) were significantly better in the intervention group at multiple preoperative and postoperative time points. Notably, more prehabilitation patients completed their full dose of neoadjuvant therapy (75% vs. 46%; p = 0.036). There were no significant differences in postoperative complications, length of stay, or 3-year mortality</t>
+  </si>
+  <si>
+    <t>supervised exercise - 76 ± 14%, 
+home exercise - 65 ± 27%
+medical coaching adherence - 82 ± 20%</t>
+  </si>
+  <si>
+    <t>Small sample size and single-center design limit generalizability. The study was powered for physiological (AT) rather than clinical outcomes. There was variability in the neoadjuvant chemotherapy regimens prescribed to participant</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 52 (14) 
+Rehabilitation – 43 (15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multimodal program:
+1. Exercise: Home-based, unsupervised. Moderate-vigorous aerobic training for 30 minutes, 3 days/week. Resistance training with 10 exercises targeting major muscle groups, 2 sets of 8–12 repetitions, 3 days/week using elastic bands.
+2. Nutritional support: Individualized care from a registered dietitian. Target protein intake of 1.5 g/kg ideal body weight, supplemented with whey protein within 1 hour of exercise as needed.
+Psychosocial: Anxiety-reducing strategies including relaxation exercises (imagery, visualization, and deep breathing) provided via meetings and a home-use CD
+</t>
+  </si>
+  <si>
+    <t>No significant difference was observed in the primary outcome of functional capacity (6MWT) between groups at any time point. Both groups returned to baseline functional capacity by 8 weeks postoperatively. The PREHAB group showed significantly better health-related quality of life (SF-36) at 4 weeks postoperatively in Physical Summary (p = 0.006), General Health (p = 0.007), and Mental Health (p = 0.044) scores. Significantly more PREHAB patients were discharged by postoperative day 2 (42% vs. 16%; p = 0.007). There were no significant differences in 30-day emergency visits, readmissions, or postoperative complications</t>
+  </si>
+  <si>
+    <t>Pre-op PREHAB: Exercise - 84.9 ± 25.3%, Nutrition - 89.5 ± 23.5%</t>
+  </si>
+  <si>
+    <t>Significant loss to follow-up and missing data, which reached 48% at eight weeks post-operation, limit the generalizability and power of the results. The study was not powered for clinical postoperative outcomes and faced potential performance bias, as control participants may have increased activity levels before surgery</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 11 (0) 
+Control – 11 (0)</t>
+  </si>
+  <si>
+    <t>control group - received usual care. As a placebo, they were provided with a Fitbit Flex 2 smartwatch that had no display screen and provided no physical activity feedback to the wearer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exercise Programme: 84%
+Nutritional Food Log:  82.9% 
+Mindfulness App: 15% </t>
+  </si>
+  <si>
+    <t>30.5 days</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 68 (6) 
+Control– 68 (10)</t>
+  </si>
+  <si>
+    <t>control group - intervention included routine preoperative preparation, such as smoking and alcohol cessation advice and pulmonary function exercises, but they received no additional structured exercise or nutritional interventions</t>
+  </si>
+  <si>
+    <t>7-9 weeks</t>
+  </si>
+  <si>
+    <t>83.8% for physical training
+ 92.6% for nutritional support
+92% for psychological counseling</t>
+  </si>
+  <si>
+    <t>The study faced selection bias from excluding unwilling participants and variability in chemotherapy regimens which may affect generalizability. Additionally, the short follow-up period meant long-term outcomes like progression-free and overall survival were not assessed</t>
+  </si>
+  <si>
+    <t>3 weeks</t>
+  </si>
+  <si>
+    <t>Control group received usual clinical care, which consisted of standard perioperative management guided by the Enhanced Recovery After Surgery (ERAS) protocols</t>
+  </si>
+  <si>
+    <t>Control group- followed the standard esophagogastric care pathway without the structured prehabilitation program</t>
+  </si>
+  <si>
+    <t>15 weeks</t>
+  </si>
+  <si>
+    <t>Rehabilitation (REHAB) Group (Control): This group, which served as the comparison to limit bias, received the same multimodal program initiated immediately after the operation for a duration of 8 weeks</t>
+  </si>
+  <si>
+    <t>Respiratory/Inspiratory Muscle Training</t>
+  </si>
+  <si>
+    <t>Primary Outcome</t>
+  </si>
+  <si>
+    <t>Randomized Clinical Trial (quasi-randomisation)</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Improved</t>
+  </si>
+  <si>
+    <t>No effect</t>
+  </si>
+  <si>
+    <t>Neoadjuvant chemotherapy adherence</t>
+  </si>
+  <si>
+    <t>4-week multimodal prehabilitation program did not reduce 30-day postoperative complications (measured by the Comprehensive Complication Index) compared to postoperative rehabilitation. There were also no significant differences in length of stay, readmissions, or emergency department visits between the two groups. While the main analysis showed no benefit for functional capacity, a per-protocol analysis revealed that patients who adhered to ≥75% of the prehabilitation sessions walked an average of 29 meters farther than those in the rehabilitation group before surgery. However, this improved physical fitness did not translate into better clinical outcomes</t>
+  </si>
+  <si>
+    <t>Functional Capacity</t>
+  </si>
+  <si>
+    <t>Complete  ONS</t>
+  </si>
+  <si>
+    <t>Micronutrients</t>
+  </si>
+  <si>
+    <t>Dietary councelling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reduction in overall postoperative complications (17.4% vs. 33.3%), and a shorter hospital stay (5.74 vs. 6.67 days),  although the difference was  not statistically significant. Patients achieved a significant improvement in the 6-MWT (+78.9 m pre-surgery and +68.9 m at 6 weeks post-surgery compared to diagnosis) and improved cardiorespiratory function </t>
+  </si>
+  <si>
+    <t>The intervention was associated with a 21.9 point higher Quality of Recovery-15 score during the first 3 postoperative days compared to the control group, exceeding the minimal clinically relevant difference (includes 15 questions related to common postoperative conditions, including pain, nausea/vomiting, exhaustion, anxiety, and overall well-being). No statistically significant differences in postoperative complication rates, length of stay, or reoperation were found between the groups. Study participants demonstrated a median adherence and compliance of 100% with the training intervention</t>
+  </si>
+  <si>
+    <t>Quality of Recovery-15 (QoR-15)</t>
+  </si>
+  <si>
+    <t>Performance bias
+Detection bias</t>
+  </si>
+  <si>
+    <t>Feasibility</t>
+  </si>
+  <si>
+    <t>Postoperative complications</t>
+  </si>
+  <si>
+    <t>Performance bias</t>
+  </si>
+  <si>
+    <t>Functional capacity</t>
+  </si>
+  <si>
+    <t>Change in aerobic thershold</t>
+  </si>
+  <si>
+    <t>Change in skeletal muscle mass</t>
+  </si>
+  <si>
+    <t>Change in lean body mass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No </t>
+  </si>
+  <si>
+    <t>Nutritional Status</t>
+  </si>
+  <si>
+    <t>Functional capacity
+Nutritional status</t>
+  </si>
+  <si>
+    <t>Selection bias
+Performance bias</t>
+  </si>
+  <si>
+    <t>Performance bias
+Attrition bias</t>
+  </si>
+  <si>
+    <t>30-day postoperative Comprehensive Complication Index (CCI)</t>
+  </si>
+  <si>
+    <t>Functional capacity
+Psychological health</t>
+  </si>
+  <si>
+    <t>Randomized Controlled Feasibility Trial</t>
+  </si>
+  <si>
+    <t>Performance bias
+Detection bias
+Reporting bias
+Attrition bias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Some concerns </t>
+  </si>
+  <si>
+    <t>Some concerns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High </t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>The study had a small sample size with a risk of Type 2 error and lacked complete participant blinding.
+The nutritional intervention window was short (2–3 weeks), and there was poor compliance with the psychological component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Low</t>
+  </si>
+  <si>
+    <t>Notes on optimal delivery</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">multimodal prehabilitation should </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>prioritize high-risk, sedentary patients</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, who are significantly more likely to see meaningful improvements in functional capacity (most significant benefits were seen in previously inactive and sedentary patients, particularly women, who were 7.07 times more likely to improve functional capacity through prehabilitation). Effective programs must integrate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>aerobic and resistance exercise with nutritional support</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, specifically timing protein intake within the "anabolic window" for maximum benefit. To outperform standard home-based programs, practitioners should consider </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>increased exercise intensity or a higher frequency of supervised sessions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Finally, involving </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>qualified professionals for supervision</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is essential to promote patient confidence and ensure adherence to recommended clinical goals</t>
+    </r>
+  </si>
+  <si>
+    <t>Author</t>
+  </si>
+  <si>
+    <t>For frail patients, a 4-to-5-week prehabilitation window may be insufficient to build the necessary physiological reserve; significant improvements in lean body mass, functional capacity, and muscle strength in elderly populations have typically been observed only after 12 weeks of more intense exercise and protein supplementation. Optimal nutrition is a cornerstone of this process, requiring high-target protein intake (1.5 g/kg) specifically timed within one hour of exercise to maximize muscle protein synthesis and counteract surgical stress. In environments already optimized by Enhanced Recovery Pathways (ERPs), prehabilitation may need to be more intensive or targeted toward patients undergoing major open surgeries where the potential for clinical improvement is greater</t>
   </si>
   <si>
     <r>
@@ -550,585 +1183,57 @@
         <rFont val="Aptos Narrow"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> to detect significant differences in secondary clinical endpoints like morbidity or mortality</t>
+      <t xml:space="preserve"> to detect significant differences in secondary clinical endpoints like morbidity or mortality. ~19% dropout/exclusion rate and missed follow-up visits introduce attrition bias</t>
     </r>
   </si>
   <si>
-    <t>Prehab -24 (6)
-Control -10 (2)</t>
-  </si>
-  <si>
-    <t>Control group- received standard hospital care</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nutritional component -93.2%
-Exercises- 88.2% (home-based) and 84.1% (supervised)
-</t>
-  </si>
-  <si>
-    <t>The study's open-label design and retrospective registration increased risks of performance, detection, and outcome reporting bias. Furthermore, the COVID-19 pandemic caused significant missing data and a 38.2% dropout rate for preoperative assessments, necessitating the use of statistical imputations</t>
-  </si>
-  <si>
-    <t>The primary objective of this trial was to assess the feasibility of the intervention rather than to provide definitive evidence of clinical efficacy. The researchers emphasize that this "pilot trial provides feasibility data supporting the design of larger efficacy and implementation trials</t>
-  </si>
-  <si>
-    <t>Multimodal Prehabilitation During Neoadjuvant Therapy Prior to Esophagogastric Cancer Resection: Effect on Cardiopulmonary Exercise Test Performance, Muscle Mass and Quality of Life—A Pilot Randomized Clinical Trial</t>
-  </si>
-  <si>
-    <t>Esophagogastric</t>
-  </si>
-  <si>
-    <t>Prognostic impact of a 3-week multimodal prehabilitation program on frail elderly patients undergoing elective gastric cancer surgery: a randomized trial</t>
-  </si>
-  <si>
-    <t>Chen et al.</t>
-  </si>
-  <si>
-    <t>Lung</t>
-  </si>
-  <si>
-    <t>Abdominal</t>
-  </si>
-  <si>
-    <t>Prehabilitation – 123 (26)
-Control– 128 (20)</t>
-  </si>
-  <si>
-    <t>Control group- received standard care and followed ERAS pathway</t>
-  </si>
-  <si>
-    <t>77% for exercise
-Not reported for other components</t>
-  </si>
-  <si>
-    <t>Early termination and open-label design</t>
-  </si>
-  <si>
-    <t>Prehabilitation – 64 (5)
-Control– 64 (5)</t>
-  </si>
-  <si>
-    <t>Control group- received standard preoperative care</t>
-  </si>
-  <si>
-    <t>Low (43%) participation rate, a lack of participant blinding, and the absence of objective tools to monitor intervention adherence</t>
-  </si>
-  <si>
-    <t>Prehabilitation – 43 (6) 
-Control – 42 (6)</t>
-  </si>
-  <si>
-    <t>2 weeks</t>
-  </si>
-  <si>
-    <t>70% (mean)</t>
-  </si>
-  <si>
-    <t>The study featured a relatively small sample size from a single center, potentially limiting generalizability. Additionally, the follow-up period was limited to 30 days, leaving long-term recovery effects unknown</t>
-  </si>
-  <si>
-    <t>Control group-  received usual clinical care</t>
-  </si>
-  <si>
-    <t>Prehabilitation – 18 (6) 
-Control – 22 (2)</t>
-  </si>
-  <si>
-    <t>control group -received standard care which consisted of nutritional counseling, physical activity recommendations, and advice on smoking cessation</t>
-  </si>
-  <si>
-    <t>The study was underpowered due to a small sample size and a potential bias from the control group receiving "partial prehabilitation" through standard preoperative advice</t>
-  </si>
-  <si>
-    <t>Prehabilitation – 35 (16) 
-Control – 35 (14)</t>
-  </si>
-  <si>
-    <t>Control group-received standard perioperative care, which included risk assessment, medication management, treatment of anemia, and smoking cessation counseling</t>
-  </si>
-  <si>
-    <t>27 days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6 days </t>
-  </si>
-  <si>
-    <t>The study had a significant loss to follow-up at post-surgical assessment points, primarily due to logistic challenges like the long distance between patients' homes and the hospital,. These factors hinder the generalizability of the results</t>
-  </si>
-  <si>
-    <t>Prehabilitation – 30 (7) 
-Control – 30 (9)</t>
-  </si>
-  <si>
-    <t>Standard care group- received no specific education or recommendations regarding physical activity, nutrition, or relaxation beyond the standard ERAS protocols</t>
-  </si>
-  <si>
-    <t>The study is primarily limited by its small sample size as a pilot study and a high loss to follow-up rate (over 25%) largely driven by the COVID-19 pandemic</t>
-  </si>
-  <si>
-    <t>Prehabilitation – 19 (3) 
-Control– 21 (1)</t>
-  </si>
-  <si>
-    <t>Control group-  received standard care, including intravenous iron for anaemic patients, preoperative lung physiotherapy, patient education, limited fasting, carbohydrate loading, and the full enhanced recovery after surgery (ERAS) pathway</t>
-  </si>
-  <si>
-    <t>4 weeks</t>
-  </si>
-  <si>
-    <t>Exercise - 100%
-Nutrition - 98%</t>
-  </si>
-  <si>
-    <t>Small sample size</t>
-  </si>
-  <si>
-    <t>Prehabilitation – 35 (3) 
-Control – 37 (6)</t>
-  </si>
-  <si>
-    <t>Control group- received usual care</t>
-  </si>
-  <si>
-    <t>6 months</t>
-  </si>
-  <si>
-    <t>Exercise - 41% were adherent to aerobic exercise and 26% were adherent to resistance training</t>
-  </si>
-  <si>
-    <t>Because the qualitative component was introduced after the study began, most interviewed participants had experienced their prehabilitation during the peak of the COVID-19 pandemic, which may have influenced their feedback</t>
-  </si>
-  <si>
-    <t>Prehabilitation - 75 (9) 
-Control– 75 (10)</t>
-  </si>
-  <si>
-    <t>Control group -received standard perioperative care, which included routine preoperative education but no structured exercise, nutritional, or psychological interventions</t>
-  </si>
-  <si>
-    <t>1 week</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Single-center design and short follow-up period that lacks long-term survival data</t>
-  </si>
-  <si>
-    <t>Prehabilitation – 45 (2) 
-Control – 45 (3)</t>
-  </si>
-  <si>
-    <t>Control group -received standard care, following hospital's  ERAS  protocol</t>
-  </si>
-  <si>
-    <t>14.2 ± 3.6 weeks</t>
-  </si>
-  <si>
-    <t>The study relied on self-reported logs rather than wearable device data and had a small sample size. It also lacked detailed daily nutritional intake data and was conducted at a single center, which may limit the generalizability of the findings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control group received one initial session of exercise instruction from a physical therapist, but no specific exercise routine was set, did not receive additional instructions, feedback, or oral nutritional supplements </t>
-  </si>
-  <si>
-    <t>m-Prehab – 25 (0) 
-Control – 25 (1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92% for protein intake 
-</t>
-  </si>
-  <si>
-    <t>Prehabilitation (Group C) – 33 (2)
-Exercise Only (Group B) – 31 (5)
-Control (Group A) – 35 (4)</t>
-  </si>
-  <si>
-    <t>Group A (standard care).- included physical activity recommendations, nutritional counseling (if malnourished), smoking cessation, alcohol intake reduction, and wearing pedometers to track daily steps</t>
-  </si>
-  <si>
-    <t>8.7 weeks</t>
-  </si>
-  <si>
-    <t>76% for the exercise program, 62% for walking steps, 160% for handgrip training, and 45% for nutritional supplementation.</t>
-  </si>
-  <si>
-    <t>Small-scale, single-center, open-label trial, which may limit generalizability and introduce participant bias. Exercise therapy and non-supplement dietary intake were largely unsupervised and left to the patients' own motivation</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Single-center design, small sample size, and low compliance with nutritional supplements. Also, it lacked long-term evaluation of oncological outcomes and physical performance</t>
-  </si>
-  <si>
-    <t>Prehabilitation – 54 (5)
- Control – 56 (4)</t>
-  </si>
-  <si>
-    <t>Control group received standard care based on ERAS principles</t>
-  </si>
-  <si>
-    <t>76% for walking, 77% for resistance training, and 73% for HMB supplementation</t>
-  </si>
-  <si>
-    <t>The study was a single-center trial with a small sample size not powered to detect differences in postoperative clinical outcomes. Its open-label design and reliance on patient-reported diaries for adherence may have also introduced bias</t>
-  </si>
-  <si>
-    <t>Prehabilitation – 52 (10) 
-Control – 52 (6)</t>
-  </si>
-  <si>
-    <t>Control group received standard preoperative care, which included dietary guidance, advice on maintaining warmth, and precautions to prevent respiratory infections</t>
-  </si>
-  <si>
-    <t>study was limited by its single-center design and lack of blinding, It excluded structured resistance training and relied on the 6-minute walk test rather than more sensitive cardiorespiratory fitness measures</t>
-  </si>
-  <si>
-    <t>Prehabilitation – 100 (0)
- Control – 100 (0)</t>
-  </si>
-  <si>
-    <t>control group received standard perioperative care, general instructions on exercises like deep breathing and effective coughing. They did not receive additional nutritional supplements.</t>
-  </si>
-  <si>
-    <t>7 days</t>
-  </si>
-  <si>
-    <t>100% for inspiratory muscle training, 98.5% for aerobic exercise, 96% for prescribed nutritional supplements, and 94% for psychological-related activities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Study's short intervention duration (7 days) and single-center design may limit the generalizability and full physiological impact of the findings. </t>
-  </si>
-  <si>
-    <t>36  days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 weeks </t>
-  </si>
-  <si>
-    <t>3-6 weeks</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 92 (±33) days</t>
-  </si>
-  <si>
-    <t>17 days</t>
-  </si>
-  <si>
-    <t>preoperative period and continued for 6–8 weeks after surgery.</t>
-  </si>
-  <si>
-    <t>Aerobic exercise</t>
-  </si>
-  <si>
-    <t>Resistance training</t>
-  </si>
-  <si>
-    <t>Protein supplementation</t>
-  </si>
-  <si>
-    <t>Overall Risk of bias</t>
-  </si>
-  <si>
-    <t>Concerning domain(s)</t>
-  </si>
-  <si>
-    <t>Psychological</t>
-  </si>
-  <si>
-    <t>Lifestyle (smoking/alcohol)</t>
-  </si>
-  <si>
-    <t>Post-operative complications</t>
-  </si>
-  <si>
-    <t>Length of hospital stay</t>
-  </si>
-  <si>
-    <t>Quality of Life</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colorectal </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lung </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gastric </t>
-  </si>
-  <si>
-    <t>Pancreatic</t>
-  </si>
-  <si>
-    <t>Bladder</t>
-  </si>
-  <si>
-    <t>Colorectal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Breast </t>
-  </si>
-  <si>
-    <t>Gastric</t>
-  </si>
-  <si>
-    <t>Esophageal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esophageal </t>
-  </si>
-  <si>
-    <t>Periampullary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esophagogastric </t>
-  </si>
-  <si>
-    <t>Intervention Overview</t>
-  </si>
-  <si>
-    <t>Prehabilitation – 57 (5) 
-Control – 58 (6)</t>
-  </si>
-  <si>
-    <t>Multimodal program:
-1. Exercise: A 3-week individualized, supervised program consisting of 30 minutes of moderate aerobic exercise (3+ times/week) and 25 minutes of resistance training focusing on major muscle groups (2-3 times/week), overseen by a physiotherapist.
-2. Nutritional support: Individualized optimization by a dietitian aiming for 1.5 g/kg/d protein intake, including whey protein supplementation if necessary, and calorie tracking via an app/website.
-3. Respiratory training: Daily use of a TRI-BALL® respiratory trainer for 10 minutes, 3 times daily, using the Sustained Maximal Inspiration (SMI) technique.
-4. Psychosocial: Anxiety-coping interventions including relaxation techniques and deep breathing exercises provided by a trained nurse, with psychologist referral if needed</t>
-  </si>
-  <si>
-    <t>Significantly lower incidence of severe complications (CCI &gt; 20) in the intervention group (10.5% vs. 25.9%, p = 0.033) and fewer medical complications (12.3% vs. 29.3%, p = 0.025). Improved functional walking capacity with more patients in the intervention group achieving a preoperative increase of ≥ 20 m in 6MWD (47.4% vs. 27.6%, p = 0.028) and returning to baseline 6MWD levels at 4 weeks postoperatively (63.2% vs. 43.1%, p = 0.031). Multimodal prehabilitation was an independent protective factor for 30-day overall complications (OR 1.971, p = 0.039). No significant differences were observed in the primary outcome of 30-day CCI, nor in length of hospital stay, 30-day readmission rates, quality of life, or psychological status</t>
-  </si>
-  <si>
-    <t>High, with 85% of participants completing 3 weekly aerobic sessions, 83% performing at least 2 resistance sessions, 92% adherence to respiratory training, and 100% adherence to protein supplementation</t>
-  </si>
-  <si>
-    <t>The single-center design and small sample size may limit generalizability and increase the risk of false-positive or false-negative results. Findings may be limited to centers with well-established ERAS protocols and a high prevalence of minimally invasive surgery</t>
-  </si>
-  <si>
-    <t>Allen et al.</t>
-  </si>
-  <si>
-    <t>Pilot Randomized Controlled Trial</t>
-  </si>
-  <si>
-    <t>Prehabilitation – 26
-Control – 28</t>
-  </si>
-  <si>
-    <t>Multimodal program (15 weeks during neoadjuvant therapy):
-1. Exercise: Twice-weekly 1-hour supervised sessions including 25 minutes of cycling at 40%–60% heart rate reserve, resistance training for six major muscle groups (2 sets of 12 repetitions), and flexibility exercises. This was supplemented by thrice-weekly 1-hour home exercises focusing on resistance and core stability.
-2. Nutritional support: Tailored, needs-based input from specialist dieticians focused on optimizing calorie and protein intake.
-3. Psychosocial (Medical Coaching): Six sessions (face-to-face or teleconference) with accredited medical coaches focusing on resilience, emotional management, and goal setting</t>
-  </si>
-  <si>
-    <t>No significant difference was observed in the primary outcome of anaerobic threshold (AT) between groups. However, the prehabilitation group showed a significantly attenuated decline in peak VO2 compared to controls (-0.4 vs. -2.5 mL/kg/min; p = 0.022). Prehabilitation also resulted in significantly less skeletal muscle loss (-11.6 vs. -15.6 cm2/m2; p = 0.049) and improved retention of hand-grip strength postoperatively (p = 0.009 at 6 weeks). Quality of life (global health status) and psychological markers (anxiety and depression) were significantly better in the intervention group at multiple preoperative and postoperative time points. Notably, more prehabilitation patients completed their full dose of neoadjuvant therapy (75% vs. 46%; p = 0.036). There were no significant differences in postoperative complications, length of stay, or 3-year mortality</t>
-  </si>
-  <si>
-    <t>supervised exercise - 76 ± 14%, 
-home exercise - 65 ± 27%
-medical coaching adherence - 82 ± 20%</t>
-  </si>
-  <si>
-    <t>Small sample size and single-center design limit generalizability. The study was powered for physiological (AT) rather than clinical outcomes. There was variability in the neoadjuvant chemotherapy regimens prescribed to participant</t>
-  </si>
-  <si>
-    <t>Prehabilitation – 52 (14) 
-Rehabilitation – 43 (15)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multimodal program:
-1. Exercise: Home-based, unsupervised. Moderate-vigorous aerobic training for 30 minutes, 3 days/week. Resistance training with 10 exercises targeting major muscle groups, 2 sets of 8–12 repetitions, 3 days/week using elastic bands.
-2. Nutritional support: Individualized care from a registered dietitian. Target protein intake of 1.5 g/kg ideal body weight, supplemented with whey protein within 1 hour of exercise as needed.
-Psychosocial: Anxiety-reducing strategies including relaxation exercises (imagery, visualization, and deep breathing) provided via meetings and a home-use CD
-</t>
-  </si>
-  <si>
-    <t>No significant difference was observed in the primary outcome of functional capacity (6MWT) between groups at any time point. Both groups returned to baseline functional capacity by 8 weeks postoperatively. The PREHAB group showed significantly better health-related quality of life (SF-36) at 4 weeks postoperatively in Physical Summary (p = 0.006), General Health (p = 0.007), and Mental Health (p = 0.044) scores. Significantly more PREHAB patients were discharged by postoperative day 2 (42% vs. 16%; p = 0.007). There were no significant differences in 30-day emergency visits, readmissions, or postoperative complications</t>
-  </si>
-  <si>
-    <t>Pre-op PREHAB: Exercise - 84.9 ± 25.3%, Nutrition - 89.5 ± 23.5%</t>
-  </si>
-  <si>
-    <t>Significant loss to follow-up and missing data, which reached 48% at eight weeks post-operation, limit the generalizability and power of the results. The study was not powered for clinical postoperative outcomes and faced potential performance bias, as control participants may have increased activity levels before surgery</t>
-  </si>
-  <si>
-    <t>Prehabilitation – 11 (0) 
-Control – 11 (0)</t>
-  </si>
-  <si>
-    <t>control group - received usual care. As a placebo, they were provided with a Fitbit Flex 2 smartwatch that had no display screen and provided no physical activity feedback to the wearer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exercise Programme: 84%
-Nutritional Food Log:  82.9% 
-Mindfulness App: 15% </t>
-  </si>
-  <si>
-    <t>30.5 days</t>
-  </si>
-  <si>
-    <t>Prehabilitation – 68 (6) 
-Control– 68 (10)</t>
-  </si>
-  <si>
-    <t>control group - intervention included routine preoperative preparation, such as smoking and alcohol cessation advice and pulmonary function exercises, but they received no additional structured exercise or nutritional interventions</t>
-  </si>
-  <si>
-    <t>7-9 weeks</t>
-  </si>
-  <si>
-    <t>83.8% for physical training
- 92.6% for nutritional support
-92% for psychological counseling</t>
-  </si>
-  <si>
-    <t>The study faced selection bias from excluding unwilling participants and variability in chemotherapy regimens which may affect generalizability. Additionally, the short follow-up period meant long-term outcomes like progression-free and overall survival were not assessed</t>
-  </si>
-  <si>
-    <t>3 weeks</t>
-  </si>
-  <si>
-    <t>Control group received usual clinical care, which consisted of standard perioperative management guided by the Enhanced Recovery After Surgery (ERAS) protocols</t>
-  </si>
-  <si>
-    <t>Control group- followed the standard esophagogastric care pathway without the structured prehabilitation program</t>
-  </si>
-  <si>
-    <t>15 weeks</t>
-  </si>
-  <si>
-    <t>Rehabilitation (REHAB) Group (Control): This group, which served as the comparison to limit bias, received the same multimodal program initiated immediately after the operation for a duration of 8 weeks</t>
-  </si>
-  <si>
-    <t>Respiratory/Inspiratory Muscle Training</t>
-  </si>
-  <si>
-    <t>Primary Outcome</t>
-  </si>
-  <si>
-    <t>Randomized Clinical Trial (quasi-randomisation)</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Improved</t>
-  </si>
-  <si>
-    <t>No effect</t>
-  </si>
-  <si>
-    <t>Neoadjuvant chemotherapy adherence</t>
-  </si>
-  <si>
-    <t>4-week multimodal prehabilitation program did not reduce 30-day postoperative complications (measured by the Comprehensive Complication Index) compared to postoperative rehabilitation. There were also no significant differences in length of stay, readmissions, or emergency department visits between the two groups. While the main analysis showed no benefit for functional capacity, a per-protocol analysis revealed that patients who adhered to ≥75% of the prehabilitation sessions walked an average of 29 meters farther than those in the rehabilitation group before surgery. However, this improved physical fitness did not translate into better clinical outcomes</t>
-  </si>
-  <si>
-    <t>Functional Capacity</t>
-  </si>
-  <si>
-    <t>Complete  ONS</t>
-  </si>
-  <si>
-    <t>Micronutrients</t>
-  </si>
-  <si>
-    <t>Dietary councelling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reduction in overall postoperative complications (17.4% vs. 33.3%), and a shorter hospital stay (5.74 vs. 6.67 days),  although the difference was  not statistically significant. Patients achieved a significant improvement in the 6-MWT (+78.9 m pre-surgery and +68.9 m at 6 weeks post-surgery compared to diagnosis) and improved cardiorespiratory function </t>
-  </si>
-  <si>
-    <t>Postoperative Recovery</t>
-  </si>
-  <si>
-    <t>The intervention was associated with a 21.9 point higher Quality of Recovery-15 score during the first 3 postoperative days compared to the control group, exceeding the minimal clinically relevant difference (includes 15 questions related to common postoperative conditions, including pain, nausea/vomiting, exhaustion, anxiety, and overall well-being). No statistically significant differences in postoperative complication rates, length of stay, or reoperation were found between the groups. Study participants demonstrated a median adherence and compliance of 100% with the training intervention</t>
-  </si>
-  <si>
-    <t>Quality of Recovery-15 (QoR-15)</t>
-  </si>
-  <si>
-    <t>Performance bias
-Detection bias</t>
-  </si>
-  <si>
-    <t>Feasibility</t>
-  </si>
-  <si>
-    <t>Postoperative complications</t>
-  </si>
-  <si>
-    <t>Performance bias</t>
-  </si>
-  <si>
-    <t>Functional capacity</t>
-  </si>
-  <si>
-    <t>Change in aerobic thershold</t>
-  </si>
-  <si>
-    <t>Change in skeletal muscle mass</t>
-  </si>
-  <si>
-    <t>Change in lean body mass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No </t>
-  </si>
-  <si>
-    <t>Nutritional Status</t>
+    <t>The primary objective of this trial was to assess the feasibility of the intervention rather than to provide definitive evidence of clinical efficacy. The researchers emphasize that this "pilot trial provides feasibility data supporting the design of larger efficacy and implementation trials. Optimal prehabilitation should be multimodal and personalized, combining supervised exercise with targeted nutritional and psychological support to maximize functional reserves before surgery. The nutrition component is critical; it should go beyond basic advice to include anabolic-promoting supplements like whey protein (reaching ≥1.5 g/kg/d), leucine, and omega-3 fatty acids, which work synergistically with exercise to enhance muscle protein synthesis. Maintaining high adherence (ideally &gt;80%) through regular monitoring and palatable, nutrient-dense supplements is essential for the intervention's success. This integrated approach ensures patients are physiologically and mentally prepared to withstand the stress of surgery and recover more efficiently.</t>
   </si>
   <si>
     <t>Functional capacity
-Nutritional status</t>
-  </si>
-  <si>
-    <t>Selection bias
-Performance bias</t>
-  </si>
-  <si>
-    <t>Performance bias
-Attrition bias</t>
-  </si>
-  <si>
-    <t>30-day postoperative Comprehensive Complication Index (CCI)</t>
-  </si>
-  <si>
-    <t>Comprehensive Complications Index (CCI)</t>
-  </si>
-  <si>
-    <t>Functional capacity
-Psychological health</t>
-  </si>
-  <si>
-    <t>Randomized Controlled Feasibility Trial</t>
-  </si>
-  <si>
-    <t>Performance bias
-Detection bias
-Reporting bias
-Attrition bias</t>
-  </si>
-  <si>
-    <t>Functional capacity
-Comprehensive Complication Index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Some concerns </t>
-  </si>
-  <si>
-    <t>Some concerns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High </t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>The study had a small sample size with a risk of Type 2 error and lacked complete participant blinding.
-The nutritional intervention window was short (2–3 weeks), and there was poor compliance with the psychological component</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Low</t>
+Postoperative complications</t>
+  </si>
+  <si>
+    <t>Optimal delivery of multimodal prehabilitation requires a supervised, personalized program (ideally 4 weeks) that integrates high-intensity exercise, psychological resilience training, and robust nutritional support. The nutritional component is critical and should be dietitian-led, focusing on achieving a high protein goal of 1.5g/kg/day through targeted dietary counseling and whey protein supplementation. Furthermore, the inclusion of micronutrients (Vitamin D and multivitamins) is essential to correct underlying deficiencies and optimize the metabolic environment for recovery. This synergistic approach effectively increases a patient’s physiological reserve, enabling them to better withstand surgical stress and avoid severe medical complications</t>
+  </si>
+  <si>
+    <t>Consider introducing supervised training sessions, a consistent duration of the intervention, and better integration into medical treatment. The nutritional component should be individualized by a dietitian to adjust for the metabolic stress of surgery, providing support even to patients who do not show signs of baseline malnutrition. It is essential to ensure a high daily protein intake of 1.2 to 1.5 g/kg through whey protein supplementation, which is most effective when consumed immediately following exercise sessions. Finally, success is bolstered by active weekly telephone monitoring from both nutritionists and kinesiologists to address adherence barriers and provide corrective feedback throughout the care continuum</t>
+  </si>
+  <si>
+    <t>Good (specific % not reported)</t>
+  </si>
+  <si>
+    <t>multimodal prehabilitation requires a multidisciplinary team to integrate exercise, nutrition, and psychological support into a cohesive, patient-centered plan. The nutrition component should focus on high-quality protein supplementation (such as 1.5 g/kg/d of whey protein) administered within one hour of exercise to specifically facilitate muscle synthesis. This synergistic approach, combined with individualized dietary counseling to correct unhealthy eating habits and ensure caloric needs are met, provides the physiological reserve necessary to withstand surgical stress and improve functional recovery</t>
+  </si>
+  <si>
+    <t>Optimal delivery should utilize a personalized, trimodal approach combining endurance/resistance exercise, nutritional optimization, and psychological support, ideally integrated throughout the neoadjuvant treatment phase to maximize physiological reserve. The nutritional component focuses on achieving high protein targets (1.5 g/kg) and using Oral Nutritional Supplements (ONS) to prevent sarcopenia and malnutrition often exacerbated by chemotherapy. Home-based, semi-supervised models are recommended as they are cost-effective, require minimal hospital visits, and improve patient participation compared to fully supervised hospital-based programs. Finally, using objective monitoring tools (such as wearables) is essential for accurately tracking adherence and ensuring the intervention's intensity is sufficient to drive clinical improvements</t>
+  </si>
+  <si>
+    <t>multimodal prehabilitation should be delivered over a 2-4 week preoperative window, integrating high-intensity aerobic/resistance training with targeted nutritional and psychological support. The nutrition component must begin with a formal assessment (such as the PG-SGA) to guide the delivery of protein-rich oral nutritional supplements (ONS) and micronutrients (specifically Vitamins A, D, and E) to combat cancer-related malnutrition and sarcopenia. In pancreatic cases, mandatory Pancreatic Enzyme Replacement Therapy (PERT) is critical to ensure the absorption of these nutrients, thereby maximizing the patient's physiological reserve before the surgical insult.</t>
+  </si>
+  <si>
+    <t>A synergistic, multidisciplinary approach combining exercise, nutrition, and psychological support is needed to mitigate the multifactorial stress of surgery. The nutritional component should be individualized by a dietitian to achieve a daily protein target of 1.5 g/kg of ideal body weight, ideally utilizing whey protein supplementation immediately post-exercise to maximize muscle protein synthesis. To overcome barriers like distance and "assessment fatigue," programs should integrate telemedicine for remote monitoring and align follow-up assessments with standard clinical surgical visits. This comprehensive strategy ensures that patients are not just physically active, but metabolically and mentally prepared for the catabolic demands of major surgery</t>
+  </si>
+  <si>
+    <t>Quality of Recovery score</t>
+  </si>
+  <si>
+    <t>Optimal delivery involves an individualized approach that tailors exercise intensity to a patient's baseline fitness to ensure both safety and adherence. The nutrition component is critical, specifically requiring hyperproteic supplementation (1.2–1.5 g/kg/day), often combined with Vitamin D and CaHMB, to provide the necessary substrate for muscle synthesis and counteract surgical catabolism. Integrating these with psychological relaxation and aerobic/resistance training creates a synergistic effect that significantly attenuates the loss of functional capacity. For maximum efficacy, this multimodal program should be maintained throughout the entire perioperative window, from diagnosis until several weeks after surgery.</t>
+  </si>
+  <si>
+    <t>Multimodal prehabilitation should involve supervised, individualized exercise programs combined with comprehensive medical optimization and nutritional support. The nutritional component requires early dietician consultation and high-dose protein supplementation (e.g., 60g daily) alongside micronutrients like Vitamin D to counteract anabolic resistance in older or vulnerable patients. Ensuring high adherence and compliance through supervised sessions and regular follow-ups is critical for achieving significant improvements in early postoperative recovery. When delivered as an adjunct to a rigorous ERAS pathway, these interventions can effectively bridge the gap between low baseline functional capacity and the physiological demands of surgery.</t>
+  </si>
+  <si>
+    <t>Prehabilitation requires a minimum window of 4 weeks to successfully translate physiological training into measurable functional gains. The nutrition component should be individualized based on screening tools like MUST, utilizing dietary fortification and ONS to counteract the metabolic stress of the tumor and surgery. To maximize efficacy, this must be paired with psychological support to reduce pre-operative anxiety, which otherwise serves as a major barrier to patient adherence. In resource-limited settings, "walk/breathing" protocols are a feasible and cost-effective alternative to expensive supervised gym programs</t>
+  </si>
+  <si>
+    <t>multimodal prehabilitation requires a personalized, home-based approach supported by biweekly professional check-ins to foster accountability and address barriers like treatment-related fatigue. A critical nutrition component should focus on early individualized assessment and counseling to optimize nutrient intake and manage chemotherapy-induced side effects such as nausea and food aversions. Integrating these services immediately at diagnosis helps patients regain a sense of control and provides essential health education that often persists into the long-term survivorship period. Furthermore, delivery must be sensitive to the patient's emotional state, as the diagnosis period is frequently described as extremely overwhelming, which can hinder initial enrollment</t>
+  </si>
+  <si>
+    <t>Small sample size. Since the primary outcome (QoR-15) is a self-reported questionnaire, the knowledge of group assignment could have introduced  bias, potentially inflating the scores in the intervention group.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Because the qualitative component was introduced after the study began, most interviewed participants had experienced their prehabilitation during the peak of the COVID-19 pandemic, which may have influenced their feedback. Outcome assessors in this study were not blinded to group allotment causing detection bias. </t>
   </si>
 </sst>
 </file>
@@ -1316,10 +1421,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1666,108 +1767,108 @@
     <col min="29" max="29" width="29.5" customWidth="1"/>
     <col min="30" max="31" width="28.83203125" customWidth="1"/>
     <col min="32" max="32" width="35.5" customWidth="1"/>
-    <col min="33" max="33" width="63.83203125" customWidth="1"/>
+    <col min="33" max="33" width="82.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="34">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>6</v>
+        <v>286</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="K1" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="N1" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="L1" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>264</v>
-      </c>
       <c r="O1" s="7" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>3</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="153">
@@ -1775,97 +1876,100 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>2018</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="G2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="AC2" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="G2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H2" s="6" t="s">
+      <c r="AD2" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="AE2" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="AF2" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="AC2" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="AD2" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="AE2" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="AF2" s="4" t="s">
-        <v>93</v>
+      <c r="AG2" s="4" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:33" ht="255">
@@ -1873,100 +1977,100 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>2018</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F3" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB3" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC3" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="G3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="R3" s="6" t="s">
+      <c r="AD3" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="AE3" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="AF3" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="S3" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="AA3" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB3" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="AC3" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AD3" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="AE3" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="AF3" s="4" t="s">
-        <v>109</v>
-      </c>
       <c r="AG3" s="4" t="s">
-        <v>107</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:33" ht="221">
@@ -1974,97 +2078,100 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4">
         <v>2020</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G4" t="s">
+        <v>202</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="U4" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="W4" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="X4" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y4" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA4" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB4" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC4" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G4" t="s">
-        <v>211</v>
-      </c>
-      <c r="H4" s="6" t="s">
+      <c r="AD4" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="AE4" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="AF4" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="S4" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="U4" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="V4" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="W4" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="X4" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="Y4" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z4" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="AA4" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="AB4" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="AC4" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="AD4" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="AE4" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="AF4" s="6" t="s">
-        <v>114</v>
+      <c r="AG4" s="6" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:33" s="5" customFormat="1" ht="153">
@@ -2072,100 +2179,100 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4">
         <v>2021</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>258</v>
+        <v>4</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AA5" s="4" t="s">
-        <v>260</v>
+        <v>115</v>
       </c>
       <c r="AB5" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AD5" s="4" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="AE5" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AF5" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="AG5" s="5" t="s">
-        <v>116</v>
+        <v>288</v>
+      </c>
+      <c r="AG5" s="4" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="6" spans="1:33" s="3" customFormat="1" ht="204">
@@ -2173,100 +2280,100 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3">
         <v>2021</v>
       </c>
       <c r="D6" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="I6" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="R6" s="17" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="W6" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="X6" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y6" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="Z6" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA6" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB6" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC6" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="X6" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y6" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="Z6" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="AA6" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB6" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="AC6" s="4" t="s">
-        <v>124</v>
-      </c>
       <c r="AD6" s="4" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="AE6" s="4" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="AF6" s="4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="AG6" s="4" t="s">
-        <v>126</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:33" ht="170">
@@ -2274,97 +2381,100 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3">
         <v>2023</v>
       </c>
       <c r="D7" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="T7" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q7" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="R7" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="S7" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="T7" s="8" t="s">
-        <v>26</v>
-      </c>
       <c r="U7" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="V7" s="8" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="W7" s="8" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="X7" s="8" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Y7" s="8" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Z7" s="8" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AA7" s="8" t="s">
-        <v>259</v>
+        <v>115</v>
       </c>
       <c r="AB7" s="8" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AC7" s="4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="AD7" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="AE7" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="AF7" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG7" s="4" t="s">
         <v>291</v>
-      </c>
-      <c r="AE7" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="AF7" s="4" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:33" s="3" customFormat="1" ht="187">
@@ -2372,97 +2482,100 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3">
         <v>2023</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="S8" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="T8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="R8" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="S8" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="T8" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="U8" s="4" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AA8" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AB8" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AC8" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AD8" s="4" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="AE8" s="4" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="AF8" s="4" t="s">
-        <v>139</v>
+        <v>133</v>
+      </c>
+      <c r="AG8" s="4" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="204">
@@ -2470,97 +2583,100 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C9" s="3">
         <v>2020</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R9" s="17" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="Z9" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AA9" s="4" t="s">
-        <v>119</v>
+        <v>251</v>
       </c>
       <c r="AB9" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AC9" s="4" t="s">
-        <v>142</v>
+        <v>293</v>
       </c>
       <c r="AD9" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="AE9" s="4" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="AF9" s="4" t="s">
-        <v>143</v>
+        <v>136</v>
+      </c>
+      <c r="AG9" s="4" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:33" s="3" customFormat="1" ht="204">
@@ -2568,97 +2684,100 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C10" s="3">
         <v>2019</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="S10" s="5" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Y10" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="Z10" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AA10" s="4" t="s">
-        <v>259</v>
+        <v>115</v>
       </c>
       <c r="AB10" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AC10" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AD10" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="AE10" s="4" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="AF10" s="4" t="s">
-        <v>147</v>
+        <v>140</v>
+      </c>
+      <c r="AG10" s="4" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:33" ht="238">
@@ -2666,97 +2785,100 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C11">
         <v>2019</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="S11" s="6" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="W11" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Y11" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="Z11" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AA11" s="4" t="s">
-        <v>259</v>
+        <v>115</v>
       </c>
       <c r="AB11" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AC11" s="20">
         <v>0.83299999999999996</v>
       </c>
       <c r="AD11" s="4" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="AE11" s="4" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="AF11" s="4" t="s">
-        <v>152</v>
+        <v>145</v>
+      </c>
+      <c r="AG11" s="4" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:33" ht="187">
@@ -2764,97 +2886,100 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C12">
         <v>2023</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="G12" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Y12" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="Z12" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AA12" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AB12" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AC12" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AD12" s="4" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="AE12" s="4" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="AF12" s="4" t="s">
-        <v>155</v>
+        <v>148</v>
+      </c>
+      <c r="AG12" s="4" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:33" ht="221">
@@ -2862,97 +2987,100 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C13">
         <v>2023</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G13" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="S13" s="6" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="V13" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="X13" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Y13" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="Z13" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AA13" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AB13" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AC13" s="4" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AD13" s="4" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="AE13" s="4" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="AF13" s="4" t="s">
-        <v>160</v>
+        <v>303</v>
+      </c>
+      <c r="AG13" s="5" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="14" spans="1:33" ht="170">
@@ -2960,97 +3088,100 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C14">
         <v>2024</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="G14" t="s">
+        <v>208</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="S14" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="T14" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="G14" t="s">
-        <v>217</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="S14" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="T14" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="U14" s="4" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="Y14" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Z14" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AA14" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AB14" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AC14" s="4" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="AD14" s="4" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="AE14" s="4" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="AF14" s="4" t="s">
-        <v>165</v>
+        <v>304</v>
+      </c>
+      <c r="AG14" s="4" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:33" ht="204">
@@ -3058,97 +3189,97 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C15">
         <v>2026</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="G15" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="Z15" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AA15" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AB15" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AC15" s="21">
         <v>0.873</v>
       </c>
       <c r="AD15" s="4" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="AE15" s="4" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="AF15" s="4" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:33" ht="204">
@@ -3156,97 +3287,97 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C16">
         <v>2026</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="G16" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="S16" s="6" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="V16" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="W16" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AA16" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AB16" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AC16" s="20">
         <v>0.84399999999999997</v>
       </c>
       <c r="AD16" s="4" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="AE16" s="4" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="AF16" s="4" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:32" ht="170">
@@ -3254,97 +3385,97 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C17">
         <v>2025</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="G17" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="R17" s="9" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="S17" s="9" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="V17" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="W17" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="Z17" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AA17" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AB17" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AC17" s="4" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="AD17" s="4" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="AE17" s="4" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="AF17" s="4" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:32" ht="170">
@@ -3352,97 +3483,97 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C18">
         <v>2025</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="G18" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="U18" s="4" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="V18" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="W18" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="X18" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Y18" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="Z18" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AA18" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AB18" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AC18" s="4" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="AD18" s="4" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="AE18" s="4" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="AF18" s="4" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:32" ht="153">
@@ -3450,97 +3581,97 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C19">
         <v>2026</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="G19" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="U19" s="4" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="V19" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="W19" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="X19" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Y19" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="Z19" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AA19" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AB19" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AC19" s="4" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="AD19" s="4" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="AE19" s="4" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="AF19" s="4" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:32" ht="204">
@@ -3548,97 +3679,97 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C20">
         <v>2025</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="G20" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="S20" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="V20" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="W20" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="Y20" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="Z20" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AA20" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AB20" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AC20" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AD20" s="4" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="AE20" s="4" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="AF20" s="4" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:32" ht="170">
@@ -3646,97 +3777,97 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C21">
         <v>2026</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="G21" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="S21" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="T21" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U21" s="4" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="V21" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="W21" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="X21" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="Y21" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="Z21" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AA21" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AB21" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AC21" s="4" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="AD21" s="4" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="AE21" s="4" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="AF21" s="4" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:32" s="3" customFormat="1" ht="204">
@@ -3744,97 +3875,97 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C22" s="3">
         <v>2022</v>
       </c>
       <c r="D22" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="O22" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="P22" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="S22" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="T22" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="M22" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N22" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="O22" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="P22" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q22" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="R22" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="S22" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="T22" s="4" t="s">
-        <v>85</v>
-      </c>
       <c r="U22" s="4" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="V22" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="W22" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="Y22" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Z22" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AA22" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AB22" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AC22" s="4" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AD22" s="4" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="AE22" s="4" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="AF22" s="5" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:32" ht="221">
@@ -3842,97 +3973,97 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C23" s="3">
         <v>2024</v>
       </c>
       <c r="D23" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="P23" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="S23" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="T23" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="O23" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="P23" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q23" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="R23" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="S23" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="T23" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="U23" s="4" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="V23" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="W23" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="X23" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="Y23" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="Z23" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AA23" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AB23" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AC23" s="4" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="AD23" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE23" s="4" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="AF23" s="4" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:32" ht="221">
@@ -3940,97 +4071,97 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C24" s="3">
         <v>2021</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K24" s="22" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M24" s="22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N24" s="22" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="O24" s="22" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="P24" s="22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q24" s="22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="S24" s="11" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="W24" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="X24" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Y24" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="Z24" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AA24" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AB24" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AC24" s="4" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="AD24" s="6" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="AE24" s="4" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="AF24" s="4" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" spans="1:32" s="3" customFormat="1" ht="221">
@@ -4038,97 +4169,97 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C25" s="3">
         <v>2022</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="V25" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="W25" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="X25" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Y25" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="Z25" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AA25" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AB25" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AC25" s="5" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="AD25" s="5" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="AE25" s="4" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="AF25" s="4" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:32" s="3" customFormat="1" ht="272">
@@ -4136,97 +4267,97 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C26" s="3">
         <v>2024</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N26" s="5" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="O26" s="5" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="P26" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q26" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="S26" s="5" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="T26" s="4" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="V26" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="W26" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="X26" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Y26" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="Z26" s="4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AA26" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AB26" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AC26" s="5" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="AD26" s="4" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="AE26" s="5" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="AF26" s="4" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:32">

--- a/data/Evidence_Table.xlsx
+++ b/data/Evidence_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramanaye/Documents/GitHub/cancer_nutrition_evidence_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B8C70F-0CA1-6B48-B3C3-43510BB83579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD90B36-B2A7-2E42-A88B-BB7F2B4B4531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16140" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
   </bookViews>
   <sheets>
     <sheet name="Evidence Table" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="317">
   <si>
     <t>Year</t>
   </si>
@@ -684,10 +684,6 @@
 Control – 25 (1)</t>
   </si>
   <si>
-    <t xml:space="preserve">92% for protein intake 
-</t>
-  </si>
-  <si>
     <t>Prehabilitation (Group C) – 33 (2)
 Exercise Only (Group B) – 31 (5)
 Control (Group A) – 35 (4)</t>
@@ -778,12 +774,6 @@
   </si>
   <si>
     <t>Concerning domain(s)</t>
-  </si>
-  <si>
-    <t>Psychological</t>
-  </si>
-  <si>
-    <t>Lifestyle (smoking/alcohol)</t>
   </si>
   <si>
     <t>Post-operative complications</t>
@@ -860,10 +850,6 @@
     <t>Pilot Randomized Controlled Trial</t>
   </si>
   <si>
-    <t>Prehabilitation – 26
-Control – 28</t>
-  </si>
-  <si>
     <t>Multimodal program (15 weeks during neoadjuvant therapy):
 1. Exercise: Twice-weekly 1-hour supervised sessions including 25 minutes of cycling at 40%–60% heart rate reserve, resistance training for six major muscle groups (2 sets of 12 repetitions), and flexibility exercises. This was supplemented by thrice-weekly 1-hour home exercises focusing on resistance and core stability.
 2. Nutritional support: Tailored, needs-based input from specialist dieticians focused on optimizing calorie and protein intake.
@@ -949,9 +935,6 @@
     <t>Rehabilitation (REHAB) Group (Control): This group, which served as the comparison to limit bias, received the same multimodal program initiated immediately after the operation for a duration of 8 weeks</t>
   </si>
   <si>
-    <t>Respiratory/Inspiratory Muscle Training</t>
-  </si>
-  <si>
     <t>Primary Outcome</t>
   </si>
   <si>
@@ -974,12 +957,6 @@
   </si>
   <si>
     <t>Functional Capacity</t>
-  </si>
-  <si>
-    <t>Complete  ONS</t>
-  </si>
-  <si>
-    <t>Micronutrients</t>
   </si>
   <si>
     <t>Dietary councelling</t>
@@ -1008,9 +985,6 @@
   </si>
   <si>
     <t>Functional capacity</t>
-  </si>
-  <si>
-    <t>Change in aerobic thershold</t>
   </si>
   <si>
     <t>Change in skeletal muscle mass</t>
@@ -1067,10 +1041,6 @@
   <si>
     <t>The study had a small sample size with a risk of Type 2 error and lacked complete participant blinding.
 The nutritional intervention window was short (2–3 weeks), and there was poor compliance with the psychological component</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Low</t>
   </si>
   <si>
     <t>Notes on optimal delivery</t>
@@ -1215,9 +1185,6 @@
     <t>A synergistic, multidisciplinary approach combining exercise, nutrition, and psychological support is needed to mitigate the multifactorial stress of surgery. The nutritional component should be individualized by a dietitian to achieve a daily protein target of 1.5 g/kg of ideal body weight, ideally utilizing whey protein supplementation immediately post-exercise to maximize muscle protein synthesis. To overcome barriers like distance and "assessment fatigue," programs should integrate telemedicine for remote monitoring and align follow-up assessments with standard clinical surgical visits. This comprehensive strategy ensures that patients are not just physically active, but metabolically and mentally prepared for the catabolic demands of major surgery</t>
   </si>
   <si>
-    <t>Quality of Recovery score</t>
-  </si>
-  <si>
     <t>Optimal delivery involves an individualized approach that tailors exercise intensity to a patient's baseline fitness to ensure both safety and adherence. The nutrition component is critical, specifically requiring hyperproteic supplementation (1.2–1.5 g/kg/day), often combined with Vitamin D and CaHMB, to provide the necessary substrate for muscle synthesis and counteract surgical catabolism. Integrating these with psychological relaxation and aerobic/resistance training creates a synergistic effect that significantly attenuates the loss of functional capacity. For maximum efficacy, this multimodal program should be maintained throughout the entire perioperative window, from diagnosis until several weeks after surgery.</t>
   </si>
   <si>
@@ -1234,6 +1201,74 @@
   </si>
   <si>
     <t xml:space="preserve">Because the qualitative component was introduced after the study began, most interviewed participants had experienced their prehabilitation during the peak of the COVID-19 pandemic, which may have influenced their feedback. Outcome assessors in this study were not blinded to group allotment causing detection bias. </t>
+  </si>
+  <si>
+    <t>Respiratory  Muscle Training</t>
+  </si>
+  <si>
+    <t>Complete  Oral Nutritional Supplement</t>
+  </si>
+  <si>
+    <t>Micronutrients supplementation</t>
+  </si>
+  <si>
+    <t>Psychological interventions</t>
+  </si>
+  <si>
+    <t>Quality of Recovery Score</t>
+  </si>
+  <si>
+    <t>An optimal delivery model is a short-course (1-week) multimodal program, which balances clinical efficacy with the need for timely surgery to prevent tumor progression. A critical nutrition component involves achieving high protein (1.2–1.5 g/kg/day) and calorie (25–30 kcal/kg/day) targets using tumor-targeted immunonutrition to specifically address cancer-driven metabolic and immune derangements. To maximize results, this nutritional support must be synergistically paired with supervised physical training and psychological counseling to remove emotional barriers and physically prepare the patient for surgical stress</t>
+  </si>
+  <si>
+    <t>Optimal delivery requires a  supervised multimodal approach initiated at the start of neoadjuvant therapy to counteract the hypercatabolic state and physical decline induced by chemotherapy. The nutrition component utilizing regular dietitian assessments and  immune-enhancing ONS to prevent skeletal muscle loss and enhance surgical resilience. Success depends on the synergy between exercise and nutrition, where structured physical activity stimulates anabolic pathways to optimize the utilization of provided nutrients. This comprehensive, "whole-course" strategy is essential for reducing postoperative complications and ensuring high chemotherapy completion rates</t>
+  </si>
+  <si>
+    <t>Change in anerobic thershold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92% for protein intake </t>
+  </si>
+  <si>
+    <t>Optimal delivery requires a supervised, synergistic approach combining exercise and nutrition for a duration typically exceeding 4 weeks, as shorter programs (like the 2-week version in this study) may fail to improve cardiopulmonary reserves. The nutrition component must provide high-dose protein, ideally ≥1.5 g/kg/day—alongside branched-chain amino acids and micronutrients like zinc to effectively counteract sarcopenia and stimulate muscle synthesis. Success depends on high-intensity physical activity (monitored via step counts or wearable devices) to ensure the body utilizes these nutrients to build functional reserve rather than just increasing intake. Ultimately, a multidisciplinary team approach is essential to provide the feedback and motivation necessary to achieve meaningful improvements in surgical resilience</t>
+  </si>
+  <si>
+    <t>For older patients, optimal delivery requires a synergistic approach, as the sources demonstrate that exercise alone is insufficient to increase skeletal muscle mass during chemotherapy. The nutrition component must specifically include leucine-rich amino acids to overcome the anabolic resistance common in the elderly, effectively stimulating muscle protein synthesis. To address the low compliance seen in this trial, delivery should involve a multidisciplinary team providing continuous monitoring and patient interviews. Furthermore, exercise should be individually tailored in intensity to accommodate the variable physical capacities of older adults, which can enhance overall adherence and clinical outcomes.</t>
+  </si>
+  <si>
+    <t>Performance bias
+Unclear Detection bias</t>
+  </si>
+  <si>
+    <t>a synergistic multidisciplinary approach is required where resistance training provides the mechanical stimulus and targeted nutrition - specifically leucine-rich amino acids or HMB which overcomes anabolic resistance in older adults. The  nutrition component must be carefully monitored to ensure high adherence, as the preservation of lean body mass is significantly greater in patients who strictly follow both the exercise and supplement protocols. To be most effective, programs should be risk-adapted, focusing on vulnerable populations (such as women or those with low baseline muscle mass) who demonstrate the highest potential for measurable improvement. Furthermore, a duration longer than the average 17 days may be necessary to build a durable physiological reserve that can withstand the intense catabolic stress of major surgery</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> multidisciplinary approach typically lasting at least 2 weeks is needed, though 4–8 weeks is ideal if surgery can be safely delayed. The nutrition component should involve personalized counseling to hit targets of 25–30 kcal/kg of energy and 1.2–2.0 g/kg of protein, using whey protein or ONS when natural intake is insufficient. For high-risk patients (NRS-2002 ≥ 5), early oral or enteral support is preferred to boost physiological reserves before the stress of surgery. Integration of structured resistance training alongside aerobic and respiratory exercises is also recommended to counteract cancer-related cachexia and further optimize metabolic resilience</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Provision of high-quality protein (like the 1,000 ml/d ONS used in this study) during the post-exercise "window of synergy"maximizes protein synthesis and attenuate surgical catabolism. For short-course programs, high intervention intensity and frequency (e.g., supervised daily sessions) are necessary to compensate for the limited duration and ensure clinical effectiveness. Finally, psychological modulation acts as a catalyst by reducing anxiety-induced stress and securing the high behavioral adherence needed for the other components to succeed.</t>
+  </si>
+  <si>
+    <t>Optimal multimodal prehabilitation should begin with a baseline nutritional screening using validated tools like the NRS-2002 to identify patients at risk of malnutrition who require Oral Nutritional Supplementation (ONS) alongside dietary counseling to effectively preserve muscle mass. Integrating exercise, nutrition, and psychological support into a single, user-friendly digital platform can enhance adherence, particularly for components that typically see lower engagement. Furthermore, the intervention should ideally span at least three to four weeks to ensure sufficient time for physiological improvements to translate into better post-operative outcomes. Focus should remain on individualized targets, such as specific protein goals and tailored exercise intensities, to maximize functional gains prior to surgery</t>
+  </si>
+  <si>
+    <t>multimodal prehabilitation involves a structured, home-based program lasting at least 7–9 weeks, ideally synchronized with neoadjuvant chemotherapy to maximize physiological gains without delaying surgery. A robust nutritional component is critical, prioritizing high-quality protein supplementation (1.2–1.5 g/kg) and targeted oral nutritional supplementation (400–900 kcal/d) supervised by professional dietitians to counteract the catabolic effects of chemotherapy. This multidisciplinary approach effectively preserves and enhances functional and nutritional reserves, leading to fewer pulmonary complications and faster postoperative recovery</t>
+  </si>
+  <si>
+    <t>multimodal prehabilitation should be highly personalized, ideally integrating supervised exercise sessions to improve patient engagement and ensure physiological gains. The nutrition component is critical; it must provide adequate protein (e.g., 1.5 g/kg ideal body weight) and energy to serve as a substrate for the anabolic effects of exercise and to counteract surgical catabolism. For maximum benefit, whey protein should be ingested within one hour of exercise sessions. Finally, incorporating psychological support not only reduces perioperative anxiety but also serves as a motivational tool to enhance adherence to the exercise and diet protocols.</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 26 (2)
+Control – 28 (4)</t>
+  </si>
+  <si>
+    <t>Change in anaerobic thershold</t>
+  </si>
+  <si>
+    <t>Optimal delivery should span the entire 15-week neoadjuvant period to counteract the toxic effects of chemotherapy and preserve physiological reserve. Nutritional intervention must involve frequent, tailored input from specialist dieticians rather than generic advice, focusing on optimizing calorie and protein intake to support muscle synthesis during exercise. Combining supervised aerobic/resistance sessions with flexible home-based exercises and psychological coaching ensures high adherence and builds the resilience necessary for patients to complete their full dose of neoadjuvant therapy</t>
+  </si>
+  <si>
+    <t>Optimal delivery requires an individualized, supervised approach integrating aerobic and resistance exercise, nutritional optimization, and psychological support for at least 3 weeks to enhance functional reserve. The nutrition component is vital, specifically targeting a protein intake of 1.5 g/kg/day, which often necessitates high-quality whey protein supplementation consumed within one hour post-exercise to maximize muscle protein synthesis. Incorporating digital tracking tools (like calorie-counting apps) and structured home-based regimens with completion diaries can significantly boost patient adherence and self-management. Finally, while short durations of 2–3 weeks maximize compliance and prevent surgical delays, they may be insufficient to impact long-term quality of life or deep-seated psychological distress</t>
   </si>
 </sst>
 </file>
@@ -1740,7 +1775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E6C0315-B915-B14D-AC51-9D3C9D78CEB9}">
-  <dimension ref="A1:AG45"/>
+  <dimension ref="A1:AF45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.5" style="3" customWidth="1"/>
@@ -1752,30 +1787,30 @@
     <col min="9" max="9" width="25" style="6" customWidth="1"/>
     <col min="10" max="11" width="25.6640625" style="6" customWidth="1"/>
     <col min="12" max="12" width="28.1640625" style="6" customWidth="1"/>
-    <col min="13" max="17" width="22.5" style="6" customWidth="1"/>
-    <col min="18" max="18" width="34" style="6" customWidth="1"/>
-    <col min="19" max="19" width="34.5" style="6" customWidth="1"/>
-    <col min="20" max="20" width="67.33203125" customWidth="1"/>
-    <col min="21" max="21" width="39.83203125" customWidth="1"/>
-    <col min="22" max="22" width="29" customWidth="1"/>
-    <col min="23" max="23" width="25.5" customWidth="1"/>
-    <col min="24" max="24" width="20.1640625" customWidth="1"/>
-    <col min="25" max="25" width="18.5" customWidth="1"/>
-    <col min="26" max="26" width="12.5" customWidth="1"/>
-    <col min="27" max="27" width="16.83203125" customWidth="1"/>
-    <col min="28" max="28" width="25.83203125" customWidth="1"/>
-    <col min="29" max="29" width="29.5" customWidth="1"/>
-    <col min="30" max="31" width="28.83203125" customWidth="1"/>
-    <col min="32" max="32" width="35.5" customWidth="1"/>
-    <col min="33" max="33" width="82.83203125" customWidth="1"/>
+    <col min="13" max="16" width="22.5" style="6" customWidth="1"/>
+    <col min="17" max="17" width="34" style="6" customWidth="1"/>
+    <col min="18" max="18" width="34.5" style="6" customWidth="1"/>
+    <col min="19" max="19" width="67.33203125" customWidth="1"/>
+    <col min="20" max="20" width="39.83203125" customWidth="1"/>
+    <col min="21" max="21" width="29" customWidth="1"/>
+    <col min="22" max="22" width="25.5" customWidth="1"/>
+    <col min="23" max="23" width="20.1640625" customWidth="1"/>
+    <col min="24" max="24" width="18.5" customWidth="1"/>
+    <col min="25" max="25" width="12.5" customWidth="1"/>
+    <col min="26" max="26" width="16.83203125" customWidth="1"/>
+    <col min="27" max="27" width="25.83203125" customWidth="1"/>
+    <col min="28" max="28" width="29.5" customWidth="1"/>
+    <col min="29" max="30" width="28.83203125" customWidth="1"/>
+    <col min="31" max="31" width="35.5" customWidth="1"/>
+    <col min="32" max="32" width="82.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="34">
+    <row r="1" spans="1:32" ht="34">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1793,85 +1828,82 @@
         <v>1</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I1" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="L1" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="K1" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="S1" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>195</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>196</v>
+        <v>95</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="153">
+    <row r="2" spans="1:32" ht="153">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1903,7 +1935,7 @@
         <v>4</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>4</v>
@@ -1912,67 +1944,64 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="O2" s="6" t="s">
         <v>115</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>249</v>
+        <v>98</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>90</v>
+        <v>258</v>
       </c>
       <c r="U2" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC2" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="AD2" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="V2" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="AC2" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD2" s="4" t="s">
-        <v>278</v>
-      </c>
       <c r="AE2" s="4" t="s">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="AF2" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AG2" s="4" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="255">
+    <row r="3" spans="1:32" ht="255">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1992,7 +2021,7 @@
         <v>103</v>
       </c>
       <c r="G3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>101</v>
@@ -2004,7 +2033,7 @@
         <v>4</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>4</v>
@@ -2013,67 +2042,64 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="P3" s="6" t="s">
         <v>4</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>249</v>
+        <v>104</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="S3" s="6" t="s">
         <v>151</v>
       </c>
+      <c r="S3" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="T3" s="4" t="s">
-        <v>102</v>
+        <v>258</v>
       </c>
       <c r="U3" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB3" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="AC3" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="AD3" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="V3" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA3" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB3" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC3" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="AD3" s="4" t="s">
-        <v>279</v>
-      </c>
       <c r="AE3" s="4" t="s">
-        <v>273</v>
+        <v>106</v>
       </c>
       <c r="AF3" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="AG3" s="4" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="221">
+    <row r="4" spans="1:32" ht="221">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2093,7 +2119,7 @@
         <v>107</v>
       </c>
       <c r="G4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>108</v>
@@ -2105,7 +2131,7 @@
         <v>4</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>4</v>
@@ -2114,67 +2140,64 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="P4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Q4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="R4" s="4" t="s">
+      <c r="Q4" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="S4" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>253</v>
+      <c r="R4" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="U4" s="6" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="V4" s="6" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="W4" s="6" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="X4" s="6" t="s">
-        <v>251</v>
+        <v>115</v>
       </c>
       <c r="Y4" s="6" t="s">
-        <v>115</v>
+        <v>246</v>
       </c>
       <c r="Z4" s="6" t="s">
-        <v>251</v>
+        <v>115</v>
       </c>
       <c r="AA4" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="AB4" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC4" s="4" t="s">
+      <c r="AB4" s="4" t="s">
         <v>110</v>
       </c>
+      <c r="AC4" s="6" t="s">
+        <v>271</v>
+      </c>
       <c r="AD4" s="6" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="AE4" s="6" t="s">
-        <v>273</v>
+        <v>111</v>
       </c>
       <c r="AF4" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="AG4" s="6" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
     </row>
-    <row r="5" spans="1:33" s="5" customFormat="1" ht="153">
+    <row r="5" spans="1:32" s="5" customFormat="1" ht="153">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -2194,7 +2217,7 @@
         <v>113</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>112</v>
@@ -2203,7 +2226,7 @@
         <v>4</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>4</v>
@@ -2218,64 +2241,61 @@
         <v>4</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="P5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>114</v>
+        <v>187</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>188</v>
+        <v>16</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>16</v>
+        <v>267</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>251</v>
+        <v>115</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>115</v>
+        <v>245</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="AA5" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="AB5" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC5" s="2" t="s">
-        <v>115</v>
+      <c r="AB5" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>271</v>
       </c>
       <c r="AD5" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="AE5" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="AE5" s="4" t="s">
-        <v>273</v>
-      </c>
       <c r="AF5" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="AG5" s="4" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
     </row>
-    <row r="6" spans="1:33" s="3" customFormat="1" ht="204">
+    <row r="6" spans="1:32" s="3" customFormat="1" ht="204">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2289,13 +2309,13 @@
         <v>18</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>117</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>20</v>
@@ -2307,7 +2327,7 @@
         <v>4</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>4</v>
@@ -2324,59 +2344,56 @@
       <c r="P6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="Q6" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="R6" s="17" t="s">
+      <c r="Q6" s="17" t="s">
         <v>118</v>
       </c>
+      <c r="R6" s="4" t="s">
+        <v>151</v>
+      </c>
       <c r="S6" s="4" t="s">
-        <v>151</v>
+        <v>19</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>19</v>
+        <v>255</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>251</v>
+        <v>115</v>
       </c>
       <c r="W6" s="4" t="s">
         <v>115</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>115</v>
+        <v>246</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="Z6" s="4" t="s">
-        <v>251</v>
+        <v>115</v>
       </c>
       <c r="AA6" s="4" t="s">
         <v>115</v>
       </c>
       <c r="AB6" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AC6" s="4" t="s">
-        <v>119</v>
+        <v>272</v>
       </c>
       <c r="AD6" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="AE6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF6" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="AE6" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="AF6" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="AG6" s="4" t="s">
-        <v>289</v>
-      </c>
     </row>
-    <row r="7" spans="1:33" ht="170">
+    <row r="7" spans="1:32" ht="170">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2396,7 +2413,7 @@
         <v>127</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>23</v>
@@ -2408,7 +2425,7 @@
         <v>4</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>4</v>
@@ -2426,58 +2443,55 @@
         <v>4</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="R7" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="S7" s="9" t="s">
         <v>151</v>
       </c>
+      <c r="S7" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="T7" s="8" t="s">
-        <v>24</v>
+        <v>281</v>
       </c>
       <c r="U7" s="8" t="s">
-        <v>290</v>
+        <v>245</v>
       </c>
       <c r="V7" s="8" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="W7" s="8" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="X7" s="8" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="Y7" s="8" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="Z7" s="8" t="s">
-        <v>251</v>
+        <v>115</v>
       </c>
       <c r="AA7" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="AB7" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC7" s="4" t="s">
+      <c r="AB7" s="4" t="s">
         <v>129</v>
       </c>
+      <c r="AC7" s="8" t="s">
+        <v>271</v>
+      </c>
       <c r="AD7" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="AE7" s="8" t="s">
-        <v>273</v>
+        <v>265</v>
+      </c>
+      <c r="AE7" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="AF7" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="AG7" s="4" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
     </row>
-    <row r="8" spans="1:33" s="3" customFormat="1" ht="187">
+    <row r="8" spans="1:32" s="3" customFormat="1" ht="187">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2497,7 +2511,7 @@
         <v>131</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>28</v>
@@ -2521,64 +2535,61 @@
         <v>4</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>4</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>249</v>
+        <v>132</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="S8" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>29</v>
+        <v>256</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>251</v>
+        <v>115</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>115</v>
+        <v>245</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="AA8" s="4" t="s">
-        <v>115</v>
+        <v>245</v>
       </c>
       <c r="AB8" s="4" t="s">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="AC8" s="4" t="s">
-        <v>115</v>
+        <v>271</v>
       </c>
       <c r="AD8" s="4" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="AE8" s="4" t="s">
-        <v>264</v>
+        <v>133</v>
       </c>
       <c r="AF8" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="AG8" s="4" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="204">
+    <row r="9" spans="1:32" ht="204">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2622,64 +2633,61 @@
         <v>4</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="P9" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Q9" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="R9" s="17" t="s">
+      <c r="Q9" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="S9" s="6" t="s">
+      <c r="R9" s="6" t="s">
         <v>135</v>
       </c>
+      <c r="S9" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="T9" s="4" t="s">
-        <v>44</v>
+        <v>258</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>251</v>
+        <v>115</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>115</v>
+        <v>246</v>
       </c>
       <c r="Z9" s="4" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="AA9" s="4" t="s">
-        <v>251</v>
+        <v>115</v>
       </c>
       <c r="AB9" s="4" t="s">
-        <v>115</v>
+        <v>284</v>
       </c>
       <c r="AC9" s="4" t="s">
-        <v>293</v>
+        <v>116</v>
       </c>
       <c r="AD9" s="4" t="s">
-        <v>116</v>
+        <v>257</v>
       </c>
       <c r="AE9" s="4" t="s">
-        <v>264</v>
+        <v>136</v>
       </c>
       <c r="AF9" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="AG9" s="4" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
     </row>
-    <row r="10" spans="1:33" s="3" customFormat="1" ht="204">
+    <row r="10" spans="1:32" s="3" customFormat="1" ht="204">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -2699,7 +2707,7 @@
         <v>138</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>47</v>
@@ -2726,31 +2734,31 @@
         <v>4</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>4</v>
+        <v>139</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="S10" s="5" t="s">
         <v>144</v>
       </c>
+      <c r="S10" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="T10" s="4" t="s">
-        <v>48</v>
+        <v>256</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>251</v>
+        <v>115</v>
       </c>
       <c r="Y10" s="4" t="s">
         <v>115</v>
@@ -2765,22 +2773,19 @@
         <v>115</v>
       </c>
       <c r="AC10" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AD10" s="4" t="s">
-        <v>116</v>
+        <v>257</v>
       </c>
       <c r="AE10" s="4" t="s">
-        <v>264</v>
+        <v>140</v>
       </c>
       <c r="AF10" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="AG10" s="4" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="238">
+    <row r="11" spans="1:32" ht="238">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2800,7 +2805,7 @@
         <v>141</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>49</v>
@@ -2812,7 +2817,7 @@
         <v>4</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>4</v>
@@ -2821,67 +2826,64 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>4</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="S11" s="6" t="s">
         <v>143</v>
       </c>
+      <c r="S11" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="T11" s="4" t="s">
-        <v>50</v>
+        <v>258</v>
       </c>
       <c r="U11" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="V11" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="W11" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="X11" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y11" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="Z11" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA11" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB11" s="20">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="AC11" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="AD11" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="V11" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="W11" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="X11" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y11" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z11" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="AA11" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB11" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC11" s="20">
-        <v>0.83299999999999996</v>
-      </c>
-      <c r="AD11" s="4" t="s">
-        <v>279</v>
-      </c>
       <c r="AE11" s="4" t="s">
-        <v>273</v>
+        <v>145</v>
       </c>
       <c r="AF11" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="AG11" s="4" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="187">
+    <row r="12" spans="1:32" ht="187">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2901,7 +2903,7 @@
         <v>146</v>
       </c>
       <c r="G12" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>52</v>
@@ -2931,58 +2933,55 @@
         <v>4</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="R12" s="6" t="s">
         <v>147</v>
       </c>
+      <c r="R12" s="4" t="s">
+        <v>190</v>
+      </c>
       <c r="S12" s="4" t="s">
-        <v>191</v>
+        <v>251</v>
       </c>
       <c r="T12" s="4" t="s">
         <v>258</v>
       </c>
       <c r="U12" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="V12" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="W12" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="X12" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y12" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z12" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA12" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB12" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC12" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="AD12" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="V12" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="W12" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="X12" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y12" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z12" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA12" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB12" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC12" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AD12" s="4" t="s">
-        <v>279</v>
-      </c>
       <c r="AE12" s="4" t="s">
-        <v>273</v>
+        <v>148</v>
       </c>
       <c r="AF12" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="AG12" s="4" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="221">
+    <row r="13" spans="1:32" ht="221">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3002,7 +3001,7 @@
         <v>149</v>
       </c>
       <c r="G13" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>54</v>
@@ -3014,7 +3013,7 @@
         <v>4</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>4</v>
@@ -3023,67 +3022,64 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>4</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="S13" s="6" t="s">
         <v>151</v>
       </c>
+      <c r="S13" s="4" t="s">
+        <v>252</v>
+      </c>
       <c r="T13" s="4" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="V13" s="4" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="X13" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="Y13" s="4" t="s">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="Z13" s="4" t="s">
-        <v>115</v>
+        <v>245</v>
       </c>
       <c r="AA13" s="4" t="s">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="AB13" s="4" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="AC13" s="4" t="s">
-        <v>152</v>
+        <v>271</v>
       </c>
       <c r="AD13" s="4" t="s">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="AE13" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="AF13" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="AG13" s="5" t="s">
-        <v>300</v>
+        <v>293</v>
+      </c>
+      <c r="AF13" s="5" t="s">
+        <v>290</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="170">
+    <row r="14" spans="1:32" ht="170">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3103,7 +3099,7 @@
         <v>153</v>
       </c>
       <c r="G14" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>57</v>
@@ -3115,7 +3111,7 @@
         <v>4</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>115</v>
@@ -3133,58 +3129,55 @@
         <v>4</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>4</v>
+        <v>154</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>155</v>
+        <v>58</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>58</v>
+        <v>255</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="W14" s="4" t="s">
         <v>115</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>115</v>
+        <v>246</v>
       </c>
       <c r="Y14" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="Z14" s="4" t="s">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="AA14" s="4" t="s">
         <v>115</v>
       </c>
       <c r="AB14" s="4" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="AC14" s="4" t="s">
-        <v>156</v>
+        <v>272</v>
       </c>
       <c r="AD14" s="4" t="s">
-        <v>280</v>
+        <v>254</v>
       </c>
       <c r="AE14" s="4" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="AF14" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="AG14" s="4" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="204">
+    <row r="15" spans="1:32" ht="204">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3204,7 +3197,7 @@
         <v>157</v>
       </c>
       <c r="G15" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>60</v>
@@ -3228,61 +3221,61 @@
         <v>4</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>4</v>
+        <v>115</v>
       </c>
       <c r="P15" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="Q15" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="R15" s="2" t="s">
+      <c r="Q15" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="S15" s="5" t="s">
+      <c r="R15" s="5" t="s">
         <v>159</v>
       </c>
+      <c r="S15" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="T15" s="4" t="s">
-        <v>61</v>
+        <v>256</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="Z15" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AA15" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="AB15" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC15" s="21">
+        <v>115</v>
+      </c>
+      <c r="AB15" s="21">
         <v>0.873</v>
       </c>
+      <c r="AC15" s="4" t="s">
+        <v>273</v>
+      </c>
       <c r="AD15" s="4" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
       <c r="AE15" s="4" t="s">
-        <v>264</v>
+        <v>160</v>
       </c>
       <c r="AF15" s="4" t="s">
-        <v>160</v>
+        <v>300</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="204">
+    <row r="16" spans="1:32" ht="204">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3302,7 +3295,7 @@
         <v>161</v>
       </c>
       <c r="G16" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>62</v>
@@ -3314,7 +3307,7 @@
         <v>4</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>115</v>
@@ -3332,52 +3325,52 @@
         <v>4</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>249</v>
+        <v>162</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="S16" s="6" t="s">
         <v>163</v>
       </c>
+      <c r="S16" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="T16" s="4" t="s">
-        <v>63</v>
+        <v>258</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="V16" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="W16" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="AA16" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="AB16" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="AC16" s="20">
+        <v>245</v>
+      </c>
+      <c r="AB16" s="20">
         <v>0.84399999999999997</v>
       </c>
+      <c r="AC16" s="4" t="s">
+        <v>273</v>
+      </c>
       <c r="AD16" s="4" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
       <c r="AE16" s="4" t="s">
-        <v>264</v>
+        <v>164</v>
       </c>
       <c r="AF16" s="4" t="s">
-        <v>164</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17" spans="1:32" ht="170">
@@ -3400,7 +3393,7 @@
         <v>166</v>
       </c>
       <c r="G17" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>65</v>
@@ -3412,7 +3405,7 @@
         <v>4</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L17" s="9" t="s">
         <v>4</v>
@@ -3427,55 +3420,55 @@
         <v>4</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>249</v>
+        <v>165</v>
       </c>
       <c r="R17" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="S17" s="9" t="s">
         <v>135</v>
       </c>
+      <c r="S17" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="T17" s="4" t="s">
-        <v>66</v>
+        <v>302</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="V17" s="4" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="W17" s="4" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="Z17" s="4" t="s">
         <v>115</v>
       </c>
       <c r="AA17" s="4" t="s">
-        <v>251</v>
+        <v>115</v>
       </c>
       <c r="AB17" s="4" t="s">
-        <v>115</v>
+        <v>303</v>
       </c>
       <c r="AC17" s="4" t="s">
-        <v>167</v>
+        <v>271</v>
       </c>
       <c r="AD17" s="4" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="AE17" s="4" t="s">
-        <v>264</v>
+        <v>171</v>
       </c>
       <c r="AF17" s="4" t="s">
-        <v>172</v>
+        <v>304</v>
       </c>
     </row>
     <row r="18" spans="1:32" ht="170">
@@ -3495,10 +3488,10 @@
         <v>25</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G18" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>68</v>
@@ -3510,7 +3503,7 @@
         <v>4</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L18" s="4" t="s">
         <v>4</v>
@@ -3519,61 +3512,61 @@
         <v>4</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>4</v>
+        <v>168</v>
       </c>
       <c r="R18" s="4" t="s">
         <v>169</v>
       </c>
       <c r="S18" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="T18" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="U18" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="V18" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="W18" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="X18" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="Y18" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z18" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA18" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="AB18" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="T18" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="U18" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="V18" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="W18" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="X18" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y18" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z18" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA18" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="AB18" s="4" t="s">
-        <v>251</v>
-      </c>
       <c r="AC18" s="4" t="s">
-        <v>171</v>
+        <v>271</v>
       </c>
       <c r="AD18" s="4" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="AE18" s="4" t="s">
-        <v>264</v>
+        <v>172</v>
       </c>
       <c r="AF18" s="4" t="s">
-        <v>173</v>
+        <v>305</v>
       </c>
     </row>
     <row r="19" spans="1:32" ht="153">
@@ -3593,10 +3586,10 @@
         <v>25</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G19" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>71</v>
@@ -3608,7 +3601,7 @@
         <v>4</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L19" s="4" t="s">
         <v>4</v>
@@ -3617,61 +3610,61 @@
         <v>115</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>249</v>
+        <v>174</v>
       </c>
       <c r="R19" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="S19" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="T19" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="V19" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="W19" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="X19" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="Y19" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z19" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA19" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB19" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="S19" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="T19" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="U19" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="V19" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="W19" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="X19" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y19" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z19" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA19" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="AB19" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="AC19" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="AD19" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE19" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="AD19" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="AE19" s="4" t="s">
-        <v>261</v>
-      </c>
       <c r="AF19" s="4" t="s">
-        <v>177</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:32" ht="204">
@@ -3691,10 +3684,10 @@
         <v>25</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G20" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>75</v>
@@ -3703,7 +3696,7 @@
         <v>4</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>4</v>
@@ -3718,58 +3711,58 @@
         <v>4</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Q20" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="R20" s="4" t="s">
+      <c r="Q20" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="R20" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="S20" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="V20" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="W20" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="X20" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y20" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="Z20" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA20" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB20" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC20" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD20" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE20" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="S20" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="T20" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="U20" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="V20" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="W20" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="X20" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y20" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z20" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="AA20" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="AB20" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC20" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AD20" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="AE20" s="4" t="s">
-        <v>264</v>
-      </c>
       <c r="AF20" s="4" t="s">
-        <v>180</v>
+        <v>308</v>
       </c>
     </row>
     <row r="21" spans="1:32" ht="170">
@@ -3789,10 +3782,10 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G21" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>77</v>
@@ -3801,7 +3794,7 @@
         <v>4</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>4</v>
@@ -3816,58 +3809,58 @@
         <v>4</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>4</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>249</v>
+        <v>181</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="S21" s="6" t="s">
+      <c r="S21" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="T21" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="U21" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="V21" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="W21" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="X21" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y21" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z21" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA21" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB21" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="T21" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="U21" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="V21" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="W21" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="X21" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="Y21" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z21" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA21" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="AB21" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="AC21" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="AD21" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="AE21" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="AD21" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="AE21" s="4" t="s">
-        <v>264</v>
-      </c>
       <c r="AF21" s="4" t="s">
-        <v>185</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" spans="1:32" s="3" customFormat="1" ht="204">
@@ -3887,7 +3880,7 @@
         <v>81</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>126</v>
@@ -3902,70 +3895,70 @@
         <v>4</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="M22" s="5" t="s">
         <v>4</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="P22" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="Q22" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="R22" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="S22" s="5" t="s">
-        <v>235</v>
+      <c r="Q22" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="R22" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="S22" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>83</v>
+        <v>258</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="V22" s="4" t="s">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="W22" s="4" t="s">
         <v>115</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>115</v>
+        <v>246</v>
       </c>
       <c r="Y22" s="4" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="Z22" s="4" t="s">
-        <v>251</v>
+        <v>115</v>
       </c>
       <c r="AA22" s="4" t="s">
         <v>115</v>
       </c>
       <c r="AB22" s="4" t="s">
-        <v>115</v>
+        <v>230</v>
       </c>
       <c r="AC22" s="4" t="s">
-        <v>234</v>
+        <v>273</v>
       </c>
       <c r="AD22" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="AE22" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="AF22" s="5" t="s">
-        <v>282</v>
+        <v>257</v>
+      </c>
+      <c r="AE22" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="AF22" s="4" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="23" spans="1:32" ht="221">
@@ -3982,13 +3975,13 @@
         <v>85</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>86</v>
@@ -4012,37 +4005,37 @@
         <v>4</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="P23" s="5" t="s">
         <v>4</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>4</v>
+        <v>233</v>
       </c>
       <c r="R23" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="S23" s="5" t="s">
-        <v>238</v>
+        <v>234</v>
+      </c>
+      <c r="S23" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>87</v>
+        <v>263</v>
       </c>
       <c r="U23" s="4" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="V23" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="W23" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="X23" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="Y23" s="4" t="s">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="Z23" s="4" t="s">
         <v>115</v>
@@ -4051,19 +4044,19 @@
         <v>115</v>
       </c>
       <c r="AB23" s="4" t="s">
-        <v>115</v>
+        <v>235</v>
       </c>
       <c r="AC23" s="4" t="s">
-        <v>239</v>
+        <v>3</v>
       </c>
       <c r="AD23" s="4" t="s">
-        <v>3</v>
+        <v>264</v>
       </c>
       <c r="AE23" s="4" t="s">
-        <v>272</v>
+        <v>236</v>
       </c>
       <c r="AF23" s="4" t="s">
-        <v>240</v>
+        <v>311</v>
       </c>
     </row>
     <row r="24" spans="1:32" ht="221">
@@ -4083,85 +4076,85 @@
         <v>25</v>
       </c>
       <c r="F24" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="N24" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="O24" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="P24" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="R24" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="S24" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="T24" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="U24" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="V24" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="W24" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="X24" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y24" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="Z24" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA24" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB24" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="AC24" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD24" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="AE24" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="L24" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="M24" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="N24" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="O24" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="P24" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q24" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="R24" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="S24" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="T24" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="U24" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="V24" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="W24" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="X24" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y24" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z24" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="AA24" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="AB24" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC24" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="AD24" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="AE24" s="4" t="s">
-        <v>273</v>
-      </c>
       <c r="AF24" s="4" t="s">
-        <v>231</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" spans="1:32" s="3" customFormat="1" ht="221">
@@ -4169,7 +4162,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C25" s="3">
         <v>2022</v>
@@ -4178,88 +4171,88 @@
         <v>121</v>
       </c>
       <c r="E25" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q25" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="S25" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="T25" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="U25" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="V25" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="W25" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="X25" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="Y25" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="Z25" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA25" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="AB25" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="AC25" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="AD25" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="AE25" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="M25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="N25" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="O25" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="P25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q25" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="R25" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="T25" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="U25" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="V25" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="W25" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="X25" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y25" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z25" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="AA25" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="AB25" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="AC25" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="AD25" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="AE25" s="4" t="s">
-        <v>264</v>
-      </c>
       <c r="AF25" s="4" t="s">
-        <v>226</v>
+        <v>315</v>
       </c>
     </row>
     <row r="26" spans="1:32" s="3" customFormat="1" ht="272">
@@ -4279,110 +4272,110 @@
         <v>25</v>
       </c>
       <c r="F26" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="N26" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="P26" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="R26" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="S26" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="U26" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="V26" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="W26" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="X26" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y26" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="Z26" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="AA26" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB26" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="H26" s="5" t="s">
+      <c r="AC26" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="AD26" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="AE26" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="I26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="M26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="N26" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="O26" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="P26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="R26" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="S26" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="T26" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="U26" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="V26" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="W26" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="X26" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y26" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z26" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="AA26" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="AB26" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC26" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="AD26" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="AE26" s="5" t="s">
-        <v>264</v>
-      </c>
       <c r="AF26" s="4" t="s">
-        <v>219</v>
+        <v>316</v>
       </c>
     </row>
     <row r="27" spans="1:32">
       <c r="A27" s="3"/>
       <c r="D27" s="19"/>
-      <c r="R27"/>
+      <c r="Q27"/>
     </row>
     <row r="28" spans="1:32">
-      <c r="R28"/>
+      <c r="Q28"/>
     </row>
     <row r="29" spans="1:32" ht="18">
       <c r="D29" s="8"/>
-      <c r="R29" s="23"/>
+      <c r="Q29" s="23"/>
     </row>
     <row r="30" spans="1:32" ht="18">
       <c r="D30" s="8"/>
-      <c r="R30" s="23"/>
+      <c r="Q30" s="23"/>
     </row>
     <row r="31" spans="1:32" ht="18">
       <c r="D31" s="8"/>
-      <c r="R31" s="23"/>
+      <c r="Q31" s="23"/>
     </row>
     <row r="32" spans="1:32" ht="18">
       <c r="D32" s="8"/>
-      <c r="R32" s="23"/>
+      <c r="Q32" s="23"/>
     </row>
     <row r="33" spans="4:4">
       <c r="D33" s="8"/>

--- a/data/Evidence_Table.xlsx
+++ b/data/Evidence_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramanaye/Documents/GitHub/cancer_nutrition_evidence_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD90B36-B2A7-2E42-A88B-BB7F2B4B4531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07ACB602-DE58-8244-A470-3C1C96C8AB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16300" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
   </bookViews>
   <sheets>
     <sheet name="Evidence Table" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="316">
   <si>
     <t>Year</t>
   </si>
@@ -1046,87 +1046,6 @@
     <t>Notes on optimal delivery</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">multimodal prehabilitation should </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>prioritize high-risk, sedentary patients</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, who are significantly more likely to see meaningful improvements in functional capacity (most significant benefits were seen in previously inactive and sedentary patients, particularly women, who were 7.07 times more likely to improve functional capacity through prehabilitation). Effective programs must integrate </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>aerobic and resistance exercise with nutritional support</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, specifically timing protein intake within the "anabolic window" for maximum benefit. To outperform standard home-based programs, practitioners should consider </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>increased exercise intensity or a higher frequency of supervised sessions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Finally, involving </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>qualified professionals for supervision</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is essential to promote patient confidence and ensure adherence to recommended clinical goals</t>
-    </r>
-  </si>
-  <si>
     <t>Author</t>
   </si>
   <si>
@@ -1203,19 +1122,10 @@
     <t xml:space="preserve">Because the qualitative component was introduced after the study began, most interviewed participants had experienced their prehabilitation during the peak of the COVID-19 pandemic, which may have influenced their feedback. Outcome assessors in this study were not blinded to group allotment causing detection bias. </t>
   </si>
   <si>
-    <t>Respiratory  Muscle Training</t>
-  </si>
-  <si>
-    <t>Complete  Oral Nutritional Supplement</t>
-  </si>
-  <si>
     <t>Micronutrients supplementation</t>
   </si>
   <si>
     <t>Psychological interventions</t>
-  </si>
-  <si>
-    <t>Quality of Recovery Score</t>
   </si>
   <si>
     <t>An optimal delivery model is a short-course (1-week) multimodal program, which balances clinical efficacy with the need for timely surgery to prevent tumor progression. A critical nutrition component involves achieving high protein (1.2–1.5 g/kg/day) and calorie (25–30 kcal/kg/day) targets using tumor-targeted immunonutrition to specifically address cancer-driven metabolic and immune derangements. To maximize results, this nutritional support must be synergistically paired with supervised physical training and psychological counseling to remove emotional barriers and physically prepare the patient for surgical stress</t>
@@ -1269,6 +1179,15 @@
   </si>
   <si>
     <t>Optimal delivery requires an individualized, supervised approach integrating aerobic and resistance exercise, nutritional optimization, and psychological support for at least 3 weeks to enhance functional reserve. The nutrition component is vital, specifically targeting a protein intake of 1.5 g/kg/day, which often necessitates high-quality whey protein supplementation consumed within one hour post-exercise to maximize muscle protein synthesis. Incorporating digital tracking tools (like calorie-counting apps) and structured home-based regimens with completion diaries can significantly boost patient adherence and self-management. Finally, while short durations of 2–3 weeks maximize compliance and prevent surgical delays, they may be insufficient to impact long-term quality of life or deep-seated psychological distress</t>
+  </si>
+  <si>
+    <t>Respiratory Muscle Training</t>
+  </si>
+  <si>
+    <t>Complete Oral Nutritional Supplement</t>
+  </si>
+  <si>
+    <t>multimodal prehabilitation should prioritize high-risk, sedentary patients, who are significantly more likely to see meaningful improvements in functional capacity (most significant benefits were seen in previously inactive and sedentary patients, particularly women, who were 7.07 times more likely to improve functional capacity through prehabilitation). Effective programs must integrate aerobic and resistance exercise with nutritional support, specifically timing protein intake within the "anabolic window" for maximum benefit. To outperform standard home-based programs, practitioners should consider increased exercise intensity or a higher frequency of supervised sessions. Finally, involving qualified professionals for supervision is essential to promote patient confidence and ensure adherence to recommended clinical goals</t>
   </si>
 </sst>
 </file>
@@ -1775,7 +1694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E6C0315-B915-B14D-AC51-9D3C9D78CEB9}">
-  <dimension ref="A1:AF45"/>
+  <dimension ref="A1:AE45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.5" style="3" customWidth="1"/>
@@ -1797,20 +1716,19 @@
     <col min="23" max="23" width="20.1640625" customWidth="1"/>
     <col min="24" max="24" width="18.5" customWidth="1"/>
     <col min="25" max="25" width="12.5" customWidth="1"/>
-    <col min="26" max="26" width="16.83203125" customWidth="1"/>
-    <col min="27" max="27" width="25.83203125" customWidth="1"/>
-    <col min="28" max="28" width="29.5" customWidth="1"/>
-    <col min="29" max="30" width="28.83203125" customWidth="1"/>
-    <col min="31" max="31" width="35.5" customWidth="1"/>
-    <col min="32" max="32" width="82.83203125" customWidth="1"/>
+    <col min="26" max="26" width="25.83203125" customWidth="1"/>
+    <col min="27" max="27" width="29.5" customWidth="1"/>
+    <col min="28" max="29" width="28.83203125" customWidth="1"/>
+    <col min="30" max="30" width="35.5" customWidth="1"/>
+    <col min="31" max="31" width="82.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="34">
+    <row r="1" spans="1:31" ht="34">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1837,7 +1755,7 @@
         <v>192</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>193</v>
@@ -1846,13 +1764,13 @@
         <v>250</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Q1" s="7" t="s">
         <v>93</v>
@@ -1882,28 +1800,25 @@
         <v>198</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>299</v>
+        <v>247</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>247</v>
+        <v>94</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>94</v>
+        <v>194</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="AF1" s="1" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="153">
+    <row r="2" spans="1:31" ht="153">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1980,28 +1895,25 @@
         <v>115</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>115</v>
+        <v>246</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>246</v>
+        <v>99</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>99</v>
+        <v>270</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="AD2" s="4" t="s">
-        <v>265</v>
+        <v>91</v>
       </c>
       <c r="AE2" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AF2" s="4" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" ht="255">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" ht="255">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2080,26 +1992,23 @@
       <c r="Z3" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="AA3" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB3" s="9" t="s">
+      <c r="AA3" s="9" t="s">
         <v>105</v>
       </c>
+      <c r="AB3" s="4" t="s">
+        <v>271</v>
+      </c>
       <c r="AC3" s="4" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AD3" s="4" t="s">
-        <v>265</v>
+        <v>106</v>
       </c>
       <c r="AE3" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="AF3" s="4" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" ht="221">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" ht="221">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2178,26 +2087,23 @@
       <c r="Z4" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="AA4" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB4" s="4" t="s">
+      <c r="AA4" s="4" t="s">
         <v>110</v>
       </c>
+      <c r="AB4" s="6" t="s">
+        <v>271</v>
+      </c>
       <c r="AC4" s="6" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AD4" s="6" t="s">
-        <v>265</v>
+        <v>111</v>
       </c>
       <c r="AE4" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF4" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" s="5" customFormat="1" ht="153">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" s="5" customFormat="1" ht="153">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -2276,26 +2182,23 @@
       <c r="Z5" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="AA5" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB5" s="2" t="s">
-        <v>115</v>
+      <c r="AA5" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>271</v>
       </c>
       <c r="AC5" s="4" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AD5" s="4" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="AE5" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="AF5" s="4" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" s="3" customFormat="1" ht="204">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" s="3" customFormat="1" ht="204">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2375,25 +2278,22 @@
         <v>115</v>
       </c>
       <c r="AA6" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AB6" s="4" t="s">
-        <v>119</v>
+        <v>272</v>
       </c>
       <c r="AC6" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="AD6" s="4" t="s">
-        <v>269</v>
+        <v>120</v>
       </c>
       <c r="AE6" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="AF6" s="4" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" ht="170">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" ht="170">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2452,46 +2352,43 @@
         <v>24</v>
       </c>
       <c r="T7" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="U7" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="V7" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="W7" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="X7" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="Y7" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="Z7" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA7" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB7" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="AC7" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="AD7" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE7" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="U7" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="V7" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="W7" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="X7" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="Y7" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="Z7" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA7" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB7" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="AC7" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="AD7" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="AE7" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="AF7" s="4" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" s="3" customFormat="1" ht="187">
+    </row>
+    <row r="8" spans="1:31" s="3" customFormat="1" ht="187">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2568,28 +2465,25 @@
         <v>245</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>115</v>
+        <v>245</v>
       </c>
       <c r="AA8" s="4" t="s">
-        <v>245</v>
+        <v>115</v>
       </c>
       <c r="AB8" s="4" t="s">
-        <v>115</v>
+        <v>271</v>
       </c>
       <c r="AC8" s="4" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="AD8" s="4" t="s">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="AE8" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="AF8" s="4" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" ht="204">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" ht="204">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2666,28 +2560,25 @@
         <v>246</v>
       </c>
       <c r="Z9" s="4" t="s">
-        <v>246</v>
+        <v>115</v>
       </c>
       <c r="AA9" s="4" t="s">
-        <v>115</v>
+        <v>283</v>
       </c>
       <c r="AB9" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="AC9" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="AD9" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="AE9" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="AC9" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="AD9" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="AE9" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="AF9" s="4" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" s="3" customFormat="1" ht="204">
+    </row>
+    <row r="10" spans="1:31" s="3" customFormat="1" ht="204">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -2770,22 +2661,19 @@
         <v>115</v>
       </c>
       <c r="AB10" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC10" s="4" t="s">
-        <v>116</v>
+        <v>257</v>
       </c>
       <c r="AD10" s="4" t="s">
-        <v>257</v>
+        <v>140</v>
       </c>
       <c r="AE10" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="AF10" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" ht="238">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" ht="238">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2864,26 +2752,23 @@
       <c r="Z11" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="AA11" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB11" s="20">
+      <c r="AA11" s="20">
         <v>0.83299999999999996</v>
       </c>
+      <c r="AB11" s="4" t="s">
+        <v>271</v>
+      </c>
       <c r="AC11" s="4" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AD11" s="4" t="s">
-        <v>265</v>
+        <v>145</v>
       </c>
       <c r="AE11" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="AF11" s="4" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" ht="187">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" ht="187">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2966,22 +2851,19 @@
         <v>115</v>
       </c>
       <c r="AB12" s="4" t="s">
-        <v>115</v>
+        <v>271</v>
       </c>
       <c r="AC12" s="4" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AD12" s="4" t="s">
-        <v>265</v>
+        <v>148</v>
       </c>
       <c r="AE12" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="AF12" s="4" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" ht="221">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" ht="221">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3058,28 +2940,25 @@
         <v>115</v>
       </c>
       <c r="Z13" s="4" t="s">
-        <v>245</v>
+        <v>115</v>
       </c>
       <c r="AA13" s="4" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="AB13" s="4" t="s">
-        <v>152</v>
+        <v>271</v>
       </c>
       <c r="AC13" s="4" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="AD13" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE13" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="AF13" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" ht="170">
+        <v>292</v>
+      </c>
+      <c r="AE13" s="5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" ht="170">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3159,25 +3038,22 @@
         <v>115</v>
       </c>
       <c r="AA14" s="4" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="AB14" s="4" t="s">
-        <v>156</v>
+        <v>272</v>
       </c>
       <c r="AC14" s="4" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="AD14" s="4" t="s">
-        <v>254</v>
+        <v>293</v>
       </c>
       <c r="AE14" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="AF14" s="4" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" ht="204">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" ht="204">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3254,28 +3130,25 @@
         <v>245</v>
       </c>
       <c r="Z15" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA15" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB15" s="21">
+        <v>115</v>
+      </c>
+      <c r="AA15" s="21">
         <v>0.873</v>
       </c>
+      <c r="AB15" s="4" t="s">
+        <v>273</v>
+      </c>
       <c r="AC15" s="4" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="AD15" s="4" t="s">
-        <v>257</v>
+        <v>160</v>
       </c>
       <c r="AE15" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="AF15" s="4" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" ht="204">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" ht="204">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3352,28 +3225,25 @@
         <v>245</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA16" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="AB16" s="20">
+        <v>245</v>
+      </c>
+      <c r="AA16" s="20">
         <v>0.84399999999999997</v>
       </c>
+      <c r="AB16" s="4" t="s">
+        <v>273</v>
+      </c>
       <c r="AC16" s="4" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="AD16" s="4" t="s">
-        <v>257</v>
+        <v>164</v>
       </c>
       <c r="AE16" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="AF16" s="4" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="17" spans="1:32" ht="170">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" ht="170">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3432,46 +3302,43 @@
         <v>66</v>
       </c>
       <c r="T17" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="U17" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="V17" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="Y17" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z17" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA17" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="AB17" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="AC17" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="U17" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="V17" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="W17" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="X17" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="Y17" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z17" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA17" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB17" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="AC17" s="4" t="s">
-        <v>271</v>
-      </c>
       <c r="AD17" s="4" t="s">
-        <v>306</v>
+        <v>171</v>
       </c>
       <c r="AE17" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="AF17" s="4" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="18" spans="1:32" ht="170">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" ht="170">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3548,28 +3415,25 @@
         <v>115</v>
       </c>
       <c r="Z18" s="4" t="s">
-        <v>115</v>
+        <v>246</v>
       </c>
       <c r="AA18" s="4" t="s">
-        <v>246</v>
+        <v>170</v>
       </c>
       <c r="AB18" s="4" t="s">
-        <v>170</v>
+        <v>271</v>
       </c>
       <c r="AC18" s="4" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="AD18" s="4" t="s">
-        <v>306</v>
+        <v>172</v>
       </c>
       <c r="AE18" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="AF18" s="4" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="19" spans="1:32" ht="153">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" ht="153">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3649,25 +3513,22 @@
         <v>115</v>
       </c>
       <c r="AA19" s="4" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
       <c r="AB19" s="4" t="s">
-        <v>175</v>
+        <v>272</v>
       </c>
       <c r="AC19" s="4" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="AD19" s="4" t="s">
-        <v>254</v>
+        <v>176</v>
       </c>
       <c r="AE19" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF19" s="4" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="20" spans="1:32" ht="204">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" ht="204">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3750,22 +3611,19 @@
         <v>115</v>
       </c>
       <c r="AB20" s="4" t="s">
-        <v>115</v>
+        <v>3</v>
       </c>
       <c r="AC20" s="4" t="s">
-        <v>3</v>
+        <v>254</v>
       </c>
       <c r="AD20" s="4" t="s">
-        <v>254</v>
+        <v>179</v>
       </c>
       <c r="AE20" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="AF20" s="4" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="21" spans="1:32" ht="170">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" ht="170">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3845,25 +3703,22 @@
         <v>115</v>
       </c>
       <c r="AA21" s="4" t="s">
-        <v>115</v>
+        <v>183</v>
       </c>
       <c r="AB21" s="4" t="s">
-        <v>183</v>
+        <v>271</v>
       </c>
       <c r="AC21" s="4" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="AD21" s="4" t="s">
-        <v>306</v>
+        <v>184</v>
       </c>
       <c r="AE21" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="AF21" s="4" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="22" spans="1:32" s="3" customFormat="1" ht="204">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" s="3" customFormat="1" ht="204">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -3943,25 +3798,22 @@
         <v>115</v>
       </c>
       <c r="AA22" s="4" t="s">
-        <v>115</v>
+        <v>230</v>
       </c>
       <c r="AB22" s="4" t="s">
-        <v>230</v>
+        <v>273</v>
       </c>
       <c r="AC22" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="AD22" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="AE22" s="5" t="s">
+      <c r="AD22" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="AF22" s="4" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="23" spans="1:32" ht="221">
+      <c r="AE22" s="4" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" ht="221">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -4041,25 +3893,22 @@
         <v>115</v>
       </c>
       <c r="AA23" s="4" t="s">
-        <v>115</v>
+        <v>235</v>
       </c>
       <c r="AB23" s="4" t="s">
-        <v>235</v>
+        <v>3</v>
       </c>
       <c r="AC23" s="4" t="s">
-        <v>3</v>
+        <v>264</v>
       </c>
       <c r="AD23" s="4" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="AE23" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="AF23" s="4" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="24" spans="1:32" ht="221">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" ht="221">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -4139,25 +3988,22 @@
         <v>115</v>
       </c>
       <c r="AA24" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB24" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="AC24" s="6" t="s">
+      <c r="AB24" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="AC24" s="4" t="s">
+        <v>265</v>
+      </c>
       <c r="AD24" s="4" t="s">
-        <v>265</v>
+        <v>227</v>
       </c>
       <c r="AE24" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="AF24" s="4" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="25" spans="1:32" s="3" customFormat="1" ht="221">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" s="3" customFormat="1" ht="221">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -4174,7 +4020,7 @@
         <v>218</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>210</v>
@@ -4216,7 +4062,7 @@
         <v>220</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="U25" s="4" t="s">
         <v>245</v>
@@ -4234,28 +4080,25 @@
         <v>245</v>
       </c>
       <c r="Z25" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA25" s="4" t="s">
-        <v>245</v>
+        <v>245</v>
+      </c>
+      <c r="AA25" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="AB25" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="AC25" s="5" t="s">
         <v>273</v>
       </c>
+      <c r="AC25" s="4" t="s">
+        <v>257</v>
+      </c>
       <c r="AD25" s="4" t="s">
-        <v>257</v>
+        <v>222</v>
       </c>
       <c r="AE25" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="AF25" s="4" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="26" spans="1:32" s="3" customFormat="1" ht="272">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" s="3" customFormat="1" ht="272">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -4332,48 +4175,45 @@
         <v>246</v>
       </c>
       <c r="Z26" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="AA26" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB26" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA26" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="AC26" s="4" t="s">
+      <c r="AB26" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="AD26" s="5" t="s">
+      <c r="AC26" s="5" t="s">
         <v>257</v>
       </c>
+      <c r="AD26" s="4" t="s">
+        <v>216</v>
+      </c>
       <c r="AE26" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="AF26" s="4" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="27" spans="1:32">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31">
       <c r="A27" s="3"/>
       <c r="D27" s="19"/>
       <c r="Q27"/>
     </row>
-    <row r="28" spans="1:32">
+    <row r="28" spans="1:31">
       <c r="Q28"/>
     </row>
-    <row r="29" spans="1:32" ht="18">
+    <row r="29" spans="1:31" ht="18">
       <c r="D29" s="8"/>
       <c r="Q29" s="23"/>
     </row>
-    <row r="30" spans="1:32" ht="18">
+    <row r="30" spans="1:31" ht="18">
       <c r="D30" s="8"/>
       <c r="Q30" s="23"/>
     </row>
-    <row r="31" spans="1:32" ht="18">
+    <row r="31" spans="1:31" ht="18">
       <c r="D31" s="8"/>
       <c r="Q31" s="23"/>
     </row>
-    <row r="32" spans="1:32" ht="18">
+    <row r="32" spans="1:31" ht="18">
       <c r="D32" s="8"/>
       <c r="Q32" s="23"/>
     </row>

--- a/data/Evidence_Table.xlsx
+++ b/data/Evidence_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramanaye/Documents/GitHub/cancer_nutrition_evidence_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07ACB602-DE58-8244-A470-3C1C96C8AB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805090BA-5B35-1647-9E31-AA6375ED02D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16300" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
   </bookViews>
   <sheets>
     <sheet name="Evidence Table" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="319">
   <si>
     <t>Year</t>
   </si>
@@ -645,9 +645,6 @@
     <t>Control group- received usual care</t>
   </si>
   <si>
-    <t>6 months</t>
-  </si>
-  <si>
     <t>Exercise - 41% were adherent to aerobic exercise and 26% were adherent to resistance training</t>
   </si>
   <si>
@@ -669,9 +666,6 @@
   </si>
   <si>
     <t>Control group -received standard care, following hospital's  ERAS  protocol</t>
-  </si>
-  <si>
-    <t>14.2 ± 3.6 weeks</t>
   </si>
   <si>
     <t>The study relied on self-reported logs rather than wearable device data and had a small sample size. It also lacked detailed daily nutritional intake data and was conducted at a single center, which may limit the generalizability of the findings</t>
@@ -750,9 +744,6 @@
   </si>
   <si>
     <t>3-6 weeks</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 92 (±33) days</t>
   </si>
   <si>
     <t>17 days</t>
@@ -917,9 +908,6 @@
 92% for psychological counseling</t>
   </si>
   <si>
-    <t>The study faced selection bias from excluding unwilling participants and variability in chemotherapy regimens which may affect generalizability. Additionally, the short follow-up period meant long-term outcomes like progression-free and overall survival were not assessed</t>
-  </si>
-  <si>
     <t>3 weeks</t>
   </si>
   <si>
@@ -971,17 +959,10 @@
     <t>Quality of Recovery-15 (QoR-15)</t>
   </si>
   <si>
-    <t>Performance bias
-Detection bias</t>
-  </si>
-  <si>
     <t>Feasibility</t>
   </si>
   <si>
     <t>Postoperative complications</t>
-  </si>
-  <si>
-    <t>Performance bias</t>
   </si>
   <si>
     <t>Functional capacity</t>
@@ -1003,14 +984,6 @@
 Nutritional status</t>
   </si>
   <si>
-    <t>Selection bias
-Performance bias</t>
-  </si>
-  <si>
-    <t>Performance bias
-Attrition bias</t>
-  </si>
-  <si>
     <t>30-day postoperative Comprehensive Complication Index (CCI)</t>
   </si>
   <si>
@@ -1019,12 +992,6 @@
   </si>
   <si>
     <t>Randomized Controlled Feasibility Trial</t>
-  </si>
-  <si>
-    <t>Performance bias
-Detection bias
-Reporting bias
-Attrition bias</t>
   </si>
   <si>
     <t xml:space="preserve">Some concerns </t>
@@ -1146,10 +1113,6 @@
     <t>For older patients, optimal delivery requires a synergistic approach, as the sources demonstrate that exercise alone is insufficient to increase skeletal muscle mass during chemotherapy. The nutrition component must specifically include leucine-rich amino acids to overcome the anabolic resistance common in the elderly, effectively stimulating muscle protein synthesis. To address the low compliance seen in this trial, delivery should involve a multidisciplinary team providing continuous monitoring and patient interviews. Furthermore, exercise should be individually tailored in intensity to accommodate the variable physical capacities of older adults, which can enhance overall adherence and clinical outcomes.</t>
   </si>
   <si>
-    <t>Performance bias
-Unclear Detection bias</t>
-  </si>
-  <si>
     <t>a synergistic multidisciplinary approach is required where resistance training provides the mechanical stimulus and targeted nutrition - specifically leucine-rich amino acids or HMB which overcomes anabolic resistance in older adults. The  nutrition component must be carefully monitored to ensure high adherence, as the preservation of lean body mass is significantly greater in patients who strictly follow both the exercise and supplement protocols. To be most effective, programs should be risk-adapted, focusing on vulnerable populations (such as women or those with low baseline muscle mass) who demonstrate the highest potential for measurable improvement. Furthermore, a duration longer than the average 17 days may be necessary to build a durable physiological reserve that can withstand the intense catabolic stress of major surgery</t>
   </si>
   <si>
@@ -1188,13 +1151,61 @@
   </si>
   <si>
     <t>multimodal prehabilitation should prioritize high-risk, sedentary patients, who are significantly more likely to see meaningful improvements in functional capacity (most significant benefits were seen in previously inactive and sedentary patients, particularly women, who were 7.07 times more likely to improve functional capacity through prehabilitation). Effective programs must integrate aerobic and resistance exercise with nutritional support, specifically timing protein intake within the "anabolic window" for maximum benefit. To outperform standard home-based programs, practitioners should consider increased exercise intensity or a higher frequency of supervised sessions. Finally, involving qualified professionals for supervision is essential to promote patient confidence and ensure adherence to recommended clinical goals</t>
+  </si>
+  <si>
+    <t>The study faced selection bias from excluding unwilling participants and variability in chemotherapy regimens which may affect generalizability. Additionally, the short follow-up period meant long-term outcomes like progression-free and overall survival were not assessed. The use of quasi-randomization (odd-even method) place the study at a high risk for bias despite the blinding of outcome assessors</t>
+  </si>
+  <si>
+    <t>For the duration of NACT</t>
+  </si>
+  <si>
+    <t>32 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 92 days</t>
+  </si>
+  <si>
+    <t>14.2 weeks</t>
+  </si>
+  <si>
+    <t>Performance bias (Domain 2)</t>
+  </si>
+  <si>
+    <t>Performance bias (Domain 2)
+Attrition bias (Domain 3)</t>
+  </si>
+  <si>
+    <t>Performance bias (Domain 2)
+Attrition bias  (Domain 3)</t>
+  </si>
+  <si>
+    <t>Selection bias (Domain 1)
+Performance bias (Domain 2)</t>
+  </si>
+  <si>
+    <t>Performance bias (Domain 2)
+Unclear Detection bias (Domain 4)</t>
+  </si>
+  <si>
+    <t>Performance bias (Domain 2)
+Detection bias  (Domain 4)</t>
+  </si>
+  <si>
+    <t>Performance bias (Domain 2)
+Unclear Detection bias  (Domain 4)</t>
+  </si>
+  <si>
+    <t>Performance bias (Domain 2)
+Detection bias  (Domain 4)
+Reporting bias  (Domain 5)
+Attrition bias (Domain 3)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1277,12 +1288,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color rgb="FF222222"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -1350,7 +1355,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1359,7 +1363,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1698,7 +1703,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
     <col min="4" max="4" width="37" style="6" customWidth="1"/>
     <col min="5" max="6" width="22.5" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
@@ -1728,7 +1733,7 @@
         <v>6</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1746,31 +1751,31 @@
         <v>1</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="Q1" s="7" t="s">
         <v>93</v>
@@ -1782,40 +1787,40 @@
         <v>2</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>94</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>95</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="153">
@@ -1850,7 +1855,7 @@
         <v>4</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>4</v>
@@ -1859,34 +1864,34 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="O2" s="6" t="s">
         <v>115</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="Q2" s="6" t="s">
         <v>98</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="S2" s="4" t="s">
         <v>90</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="X2" s="4" t="s">
         <v>115</v>
@@ -1895,22 +1900,22 @@
         <v>115</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="AA2" s="4" t="s">
         <v>99</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>265</v>
+        <v>312</v>
       </c>
       <c r="AD2" s="4" t="s">
         <v>91</v>
       </c>
       <c r="AE2" s="4" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="255">
@@ -1933,7 +1938,7 @@
         <v>103</v>
       </c>
       <c r="G3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>101</v>
@@ -1945,7 +1950,7 @@
         <v>4</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>4</v>
@@ -1954,10 +1959,10 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="P3" s="6" t="s">
         <v>4</v>
@@ -1966,22 +1971,22 @@
         <v>104</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>151</v>
+        <v>308</v>
       </c>
       <c r="S3" s="4" t="s">
         <v>102</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="X3" s="4" t="s">
         <v>115</v>
@@ -1996,16 +2001,16 @@
         <v>105</v>
       </c>
       <c r="AB3" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AC3" s="4" t="s">
-        <v>265</v>
+        <v>313</v>
       </c>
       <c r="AD3" s="4" t="s">
         <v>106</v>
       </c>
       <c r="AE3" s="4" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="221">
@@ -2028,7 +2033,7 @@
         <v>107</v>
       </c>
       <c r="G4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>108</v>
@@ -2040,7 +2045,7 @@
         <v>4</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>4</v>
@@ -2049,10 +2054,10 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="P4" s="6" t="s">
         <v>4</v>
@@ -2061,28 +2066,28 @@
         <v>109</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="T4" s="6" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="U4" s="6" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="V4" s="6" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="W4" s="6" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="X4" s="6" t="s">
         <v>115</v>
       </c>
       <c r="Y4" s="6" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="Z4" s="6" t="s">
         <v>115</v>
@@ -2091,16 +2096,16 @@
         <v>110</v>
       </c>
       <c r="AB4" s="6" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AC4" s="6" t="s">
-        <v>265</v>
+        <v>312</v>
       </c>
       <c r="AD4" s="6" t="s">
         <v>111</v>
       </c>
       <c r="AE4" s="6" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:31" s="5" customFormat="1" ht="153">
@@ -2123,7 +2128,7 @@
         <v>113</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>112</v>
@@ -2132,7 +2137,7 @@
         <v>4</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>4</v>
@@ -2147,7 +2152,7 @@
         <v>4</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="P5" s="4" t="s">
         <v>4</v>
@@ -2156,28 +2161,28 @@
         <v>114</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="S5" s="4" t="s">
         <v>16</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="X5" s="4" t="s">
         <v>115</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="Z5" s="4" t="s">
         <v>115</v>
@@ -2186,16 +2191,16 @@
         <v>115</v>
       </c>
       <c r="AB5" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AC5" s="4" t="s">
-        <v>265</v>
+        <v>312</v>
       </c>
       <c r="AD5" s="4" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="AE5" s="4" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:31" s="3" customFormat="1" ht="204">
@@ -2212,13 +2217,13 @@
         <v>18</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>117</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>20</v>
@@ -2230,7 +2235,7 @@
         <v>4</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>4</v>
@@ -2257,10 +2262,10 @@
         <v>19</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="V6" s="4" t="s">
         <v>115</v>
@@ -2269,10 +2274,10 @@
         <v>115</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="Z6" s="4" t="s">
         <v>115</v>
@@ -2281,16 +2286,16 @@
         <v>119</v>
       </c>
       <c r="AB6" s="4" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="AC6" s="4" t="s">
-        <v>269</v>
+        <v>318</v>
       </c>
       <c r="AD6" s="4" t="s">
         <v>120</v>
       </c>
       <c r="AE6" s="4" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="170">
@@ -2313,7 +2318,7 @@
         <v>127</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>23</v>
@@ -2325,7 +2330,7 @@
         <v>4</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>4</v>
@@ -2352,22 +2357,22 @@
         <v>24</v>
       </c>
       <c r="T7" s="8" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="U7" s="8" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="V7" s="8" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="W7" s="8" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="X7" s="8" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="Y7" s="8" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="Z7" s="8" t="s">
         <v>115</v>
@@ -2376,16 +2381,16 @@
         <v>129</v>
       </c>
       <c r="AB7" s="8" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AC7" s="8" t="s">
-        <v>265</v>
+        <v>312</v>
       </c>
       <c r="AD7" s="4" t="s">
         <v>130</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:31" s="3" customFormat="1" ht="187">
@@ -2408,7 +2413,7 @@
         <v>131</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>28</v>
@@ -2432,7 +2437,7 @@
         <v>4</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>4</v>
@@ -2441,46 +2446,46 @@
         <v>132</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>188</v>
+        <v>309</v>
       </c>
       <c r="S8" s="4" t="s">
         <v>29</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="X8" s="4" t="s">
         <v>115</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="AA8" s="4" t="s">
         <v>115</v>
       </c>
       <c r="AB8" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AC8" s="4" t="s">
-        <v>257</v>
+        <v>311</v>
       </c>
       <c r="AD8" s="4" t="s">
         <v>133</v>
       </c>
       <c r="AE8" s="4" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="204">
@@ -2527,7 +2532,7 @@
         <v>4</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="P9" s="6" t="s">
         <v>4</v>
@@ -2542,40 +2547,40 @@
         <v>44</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="X9" s="4" t="s">
         <v>115</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="Z9" s="4" t="s">
         <v>115</v>
       </c>
       <c r="AA9" s="4" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="AB9" s="4" t="s">
         <v>116</v>
       </c>
       <c r="AC9" s="4" t="s">
-        <v>257</v>
+        <v>311</v>
       </c>
       <c r="AD9" s="4" t="s">
         <v>136</v>
       </c>
       <c r="AE9" s="4" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:31" s="3" customFormat="1" ht="204">
@@ -2598,7 +2603,7 @@
         <v>138</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>47</v>
@@ -2625,7 +2630,7 @@
         <v>4</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>139</v>
@@ -2637,16 +2642,16 @@
         <v>48</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="X10" s="4" t="s">
         <v>115</v>
@@ -2664,13 +2669,13 @@
         <v>116</v>
       </c>
       <c r="AC10" s="4" t="s">
-        <v>257</v>
+        <v>311</v>
       </c>
       <c r="AD10" s="4" t="s">
         <v>140</v>
       </c>
       <c r="AE10" s="4" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="238">
@@ -2693,7 +2698,7 @@
         <v>141</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>49</v>
@@ -2705,7 +2710,7 @@
         <v>4</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>4</v>
@@ -2714,10 +2719,10 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>4</v>
@@ -2732,40 +2737,40 @@
         <v>50</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="W11" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="X11" s="4" t="s">
         <v>115</v>
       </c>
       <c r="Y11" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="Z11" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="AA11" s="20">
+      <c r="AA11" s="19">
         <v>0.83299999999999996</v>
       </c>
       <c r="AB11" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AC11" s="4" t="s">
-        <v>265</v>
+        <v>312</v>
       </c>
       <c r="AD11" s="4" t="s">
         <v>145</v>
       </c>
       <c r="AE11" s="4" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="187">
@@ -2788,7 +2793,7 @@
         <v>146</v>
       </c>
       <c r="G12" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>52</v>
@@ -2821,22 +2826,22 @@
         <v>147</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="X12" s="4" t="s">
         <v>115</v>
@@ -2851,16 +2856,16 @@
         <v>115</v>
       </c>
       <c r="AB12" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AC12" s="4" t="s">
-        <v>265</v>
+        <v>312</v>
       </c>
       <c r="AD12" s="4" t="s">
         <v>148</v>
       </c>
       <c r="AE12" s="4" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="221">
@@ -2883,7 +2888,7 @@
         <v>149</v>
       </c>
       <c r="G13" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>54</v>
@@ -2895,7 +2900,7 @@
         <v>4</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>4</v>
@@ -2904,13 +2909,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>4</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="Q13" s="6" t="s">
         <v>150</v>
@@ -2919,22 +2924,22 @@
         <v>151</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="V13" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="X13" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="Y13" s="4" t="s">
         <v>115</v>
@@ -2946,16 +2951,16 @@
         <v>152</v>
       </c>
       <c r="AB13" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AC13" s="4" t="s">
-        <v>254</v>
+        <v>316</v>
       </c>
       <c r="AD13" s="4" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="AE13" s="5" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="170">
@@ -2978,7 +2983,7 @@
         <v>153</v>
       </c>
       <c r="G14" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>57</v>
@@ -2990,7 +2995,7 @@
         <v>4</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>115</v>
@@ -3011,16 +3016,16 @@
         <v>154</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>155</v>
+        <v>307</v>
       </c>
       <c r="S14" s="4" t="s">
         <v>58</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="V14" s="4" t="s">
         <v>115</v>
@@ -3029,28 +3034,28 @@
         <v>115</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="Y14" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="Z14" s="4" t="s">
         <v>115</v>
       </c>
       <c r="AA14" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AB14" s="4" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="AC14" s="4" t="s">
-        <v>254</v>
+        <v>316</v>
       </c>
       <c r="AD14" s="4" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="AE14" s="4" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="204">
@@ -3070,10 +3075,10 @@
         <v>25</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G15" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>60</v>
@@ -3103,49 +3108,49 @@
         <v>4</v>
       </c>
       <c r="Q15" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="R15" s="5" t="s">
         <v>158</v>
-      </c>
-      <c r="R15" s="5" t="s">
-        <v>159</v>
       </c>
       <c r="S15" s="4" t="s">
         <v>61</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="Z15" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="AA15" s="21">
+      <c r="AA15" s="20">
         <v>0.873</v>
       </c>
       <c r="AB15" s="4" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="AC15" s="4" t="s">
-        <v>257</v>
+        <v>311</v>
       </c>
       <c r="AD15" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AE15" s="4" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="204">
@@ -3165,10 +3170,10 @@
         <v>25</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G16" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>62</v>
@@ -3180,7 +3185,7 @@
         <v>4</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>115</v>
@@ -3198,49 +3203,49 @@
         <v>4</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>163</v>
+        <v>310</v>
       </c>
       <c r="S16" s="4" t="s">
         <v>63</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="V16" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="W16" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA16" s="20">
+        <v>241</v>
+      </c>
+      <c r="AA16" s="19">
         <v>0.84399999999999997</v>
       </c>
       <c r="AB16" s="4" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="AC16" s="4" t="s">
-        <v>257</v>
+        <v>311</v>
       </c>
       <c r="AD16" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AE16" s="4" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="170">
@@ -3260,10 +3265,10 @@
         <v>25</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G17" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>65</v>
@@ -3275,7 +3280,7 @@
         <v>4</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="L17" s="9" t="s">
         <v>4</v>
@@ -3290,10 +3295,10 @@
         <v>4</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="R17" s="9" t="s">
         <v>135</v>
@@ -3302,19 +3307,19 @@
         <v>66</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="V17" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="W17" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="Y17" s="4" t="s">
         <v>115</v>
@@ -3323,19 +3328,19 @@
         <v>115</v>
       </c>
       <c r="AA17" s="4" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="AB17" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AC17" s="4" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="AD17" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AE17" s="4" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" spans="1:31" ht="170">
@@ -3355,10 +3360,10 @@
         <v>25</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G18" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>68</v>
@@ -3370,7 +3375,7 @@
         <v>4</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="L18" s="4" t="s">
         <v>4</v>
@@ -3379,58 +3384,58 @@
         <v>4</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="S18" s="4" t="s">
         <v>69</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="U18" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="V18" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="W18" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="X18" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="Y18" s="4" t="s">
         <v>115</v>
       </c>
       <c r="Z18" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="AA18" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB18" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="AC18" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="AD18" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="AB18" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="AC18" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="AD18" s="4" t="s">
-        <v>172</v>
-      </c>
       <c r="AE18" s="4" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" spans="1:31" ht="153">
@@ -3450,10 +3455,10 @@
         <v>25</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G19" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>71</v>
@@ -3465,7 +3470,7 @@
         <v>4</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="L19" s="4" t="s">
         <v>4</v>
@@ -3474,37 +3479,37 @@
         <v>115</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="S19" s="4" t="s">
         <v>72</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="U19" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="V19" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="W19" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="X19" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="Y19" s="4" t="s">
         <v>115</v>
@@ -3513,19 +3518,19 @@
         <v>115</v>
       </c>
       <c r="AA19" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AB19" s="4" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="AC19" s="4" t="s">
-        <v>254</v>
+        <v>316</v>
       </c>
       <c r="AD19" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AE19" s="4" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20" spans="1:31" ht="204">
@@ -3545,10 +3550,10 @@
         <v>25</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G20" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>75</v>
@@ -3557,7 +3562,7 @@
         <v>4</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>4</v>
@@ -3572,13 +3577,13 @@
         <v>4</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>4</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>135</v>
@@ -3587,13 +3592,13 @@
         <v>74</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="V20" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="W20" s="4" t="s">
         <v>115</v>
@@ -3602,7 +3607,7 @@
         <v>115</v>
       </c>
       <c r="Y20" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="Z20" s="4" t="s">
         <v>115</v>
@@ -3614,13 +3619,13 @@
         <v>3</v>
       </c>
       <c r="AC20" s="4" t="s">
-        <v>254</v>
+        <v>316</v>
       </c>
       <c r="AD20" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AE20" s="4" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" spans="1:31" ht="170">
@@ -3640,10 +3645,10 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G21" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>77</v>
@@ -3652,7 +3657,7 @@
         <v>4</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>4</v>
@@ -3667,31 +3672,31 @@
         <v>4</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>4</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S21" s="4" t="s">
         <v>78</v>
       </c>
       <c r="T21" s="4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="U21" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="V21" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="W21" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="X21" s="4" t="s">
         <v>115</v>
@@ -3703,19 +3708,19 @@
         <v>115</v>
       </c>
       <c r="AA21" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AB21" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AC21" s="4" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="AD21" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AE21" s="4" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
     </row>
     <row r="22" spans="1:31" s="3" customFormat="1" ht="204">
@@ -3735,7 +3740,7 @@
         <v>81</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>126</v>
@@ -3750,37 +3755,37 @@
         <v>4</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="M22" s="5" t="s">
         <v>4</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="P22" s="5" t="s">
         <v>4</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="S22" s="4" t="s">
         <v>83</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="V22" s="4" t="s">
         <v>115</v>
@@ -3789,28 +3794,28 @@
         <v>115</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="Y22" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="Z22" s="4" t="s">
         <v>115</v>
       </c>
       <c r="AA22" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AB22" s="4" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="AC22" s="4" t="s">
-        <v>257</v>
+        <v>311</v>
       </c>
       <c r="AD22" s="5" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="AE22" s="4" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
     </row>
     <row r="23" spans="1:31" ht="221">
@@ -3827,13 +3832,13 @@
         <v>85</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>86</v>
@@ -3857,34 +3862,34 @@
         <v>4</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="P23" s="5" t="s">
         <v>4</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="R23" s="5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="S23" s="4" t="s">
         <v>87</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="U23" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="V23" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="W23" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="X23" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="Y23" s="4" t="s">
         <v>115</v>
@@ -3893,19 +3898,19 @@
         <v>115</v>
       </c>
       <c r="AA23" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AB23" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AC23" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="AD23" s="4" t="s">
-        <v>236</v>
+        <v>314</v>
+      </c>
+      <c r="AD23" s="5" t="s">
+        <v>306</v>
       </c>
       <c r="AE23" s="4" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
     </row>
     <row r="24" spans="1:31" ht="221">
@@ -3925,82 +3930,82 @@
         <v>25</v>
       </c>
       <c r="F24" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="K24" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="N24" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="O24" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="P24" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="R24" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="S24" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="T24" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="U24" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="V24" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="W24" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="X24" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y24" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="Z24" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA24" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="L24" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="M24" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="N24" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="O24" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="P24" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q24" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="R24" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="S24" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="T24" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="U24" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="V24" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="W24" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="X24" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y24" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="Z24" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA24" s="4" t="s">
-        <v>226</v>
       </c>
       <c r="AB24" s="6" t="s">
         <v>3</v>
       </c>
       <c r="AC24" s="4" t="s">
-        <v>265</v>
+        <v>312</v>
       </c>
       <c r="AD24" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AE24" s="4" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
     </row>
     <row r="25" spans="1:31" s="3" customFormat="1" ht="221">
@@ -4008,7 +4013,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C25" s="3">
         <v>2022</v>
@@ -4017,85 +4022,85 @@
         <v>121</v>
       </c>
       <c r="E25" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q25" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="S25" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="T25" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="U25" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="V25" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="W25" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="X25" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="Y25" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="Z25" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="AA25" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="H25" s="4" t="s">
+      <c r="AB25" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="AC25" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="AD25" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="I25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="M25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="N25" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="O25" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="P25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q25" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="S25" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="T25" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="U25" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="V25" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="W25" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="X25" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="Y25" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="Z25" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA25" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="AB25" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="AC25" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="AD25" s="4" t="s">
-        <v>222</v>
-      </c>
       <c r="AE25" s="4" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
     </row>
     <row r="26" spans="1:31" s="3" customFormat="1" ht="272">
@@ -4115,87 +4120,87 @@
         <v>25</v>
       </c>
       <c r="F26" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="N26" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="P26" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="R26" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="S26" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="U26" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="V26" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="W26" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="X26" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y26" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="Z26" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA26" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="H26" s="5" t="s">
+      <c r="AB26" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="AC26" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="AD26" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="I26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="M26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="N26" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="O26" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="P26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q26" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="R26" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="S26" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="T26" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="U26" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="V26" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="W26" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="X26" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y26" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="Z26" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA26" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB26" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="AC26" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="AD26" s="4" t="s">
-        <v>216</v>
-      </c>
       <c r="AE26" s="4" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
     </row>
     <row r="27" spans="1:31">
       <c r="A27" s="3"/>
-      <c r="D27" s="19"/>
+      <c r="D27" s="18"/>
       <c r="Q27"/>
     </row>
     <row r="28" spans="1:31">
@@ -4203,57 +4208,63 @@
     </row>
     <row r="29" spans="1:31" ht="18">
       <c r="D29" s="8"/>
-      <c r="Q29" s="23"/>
+      <c r="Q29" s="22"/>
     </row>
     <row r="30" spans="1:31" ht="18">
       <c r="D30" s="8"/>
-      <c r="Q30" s="23"/>
+      <c r="Q30" s="22"/>
     </row>
     <row r="31" spans="1:31" ht="18">
       <c r="D31" s="8"/>
-      <c r="Q31" s="23"/>
+      <c r="Q31" s="22"/>
     </row>
     <row r="32" spans="1:31" ht="18">
       <c r="D32" s="8"/>
-      <c r="Q32" s="23"/>
-    </row>
-    <row r="33" spans="4:4">
+      <c r="Q32" s="22"/>
+    </row>
+    <row r="33" spans="3:4">
       <c r="D33" s="8"/>
     </row>
-    <row r="34" spans="4:4" ht="20">
-      <c r="D34" s="18"/>
-    </row>
-    <row r="35" spans="4:4">
-      <c r="D35" s="8"/>
-    </row>
-    <row r="36" spans="4:4">
-      <c r="D36" s="8"/>
-    </row>
-    <row r="37" spans="4:4">
-      <c r="D37" s="8"/>
-    </row>
-    <row r="38" spans="4:4">
-      <c r="D38" s="8"/>
-    </row>
-    <row r="39" spans="4:4">
-      <c r="D39" s="8"/>
-    </row>
-    <row r="40" spans="4:4">
+    <row r="34" spans="3:4">
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" spans="3:4">
+      <c r="C35" s="1"/>
+      <c r="D35" s="23"/>
+    </row>
+    <row r="36" spans="3:4">
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+    </row>
+    <row r="37" spans="3:4">
+      <c r="C37" s="1"/>
+      <c r="D37" s="23"/>
+    </row>
+    <row r="38" spans="3:4">
+      <c r="C38" s="1"/>
+      <c r="D38" s="23"/>
+    </row>
+    <row r="39" spans="3:4">
+      <c r="C39" s="1"/>
+      <c r="D39" s="23"/>
+    </row>
+    <row r="40" spans="3:4">
       <c r="D40" s="8"/>
     </row>
-    <row r="41" spans="4:4">
+    <row r="41" spans="3:4">
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="4:4">
+    <row r="42" spans="3:4">
       <c r="D42" s="8"/>
     </row>
-    <row r="43" spans="4:4">
+    <row r="43" spans="3:4">
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="4:4">
+    <row r="44" spans="3:4">
       <c r="D44" s="4"/>
     </row>
-    <row r="45" spans="4:4">
+    <row r="45" spans="3:4">
       <c r="D45" s="5"/>
     </row>
   </sheetData>

--- a/data/Evidence_Table.xlsx
+++ b/data/Evidence_Table.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramanaye/Documents/GitHub/cancer_nutrition_evidence_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805090BA-5B35-1647-9E31-AA6375ED02D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8018A002-653D-D146-B839-CF1F264EE4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
   </bookViews>
   <sheets>
     <sheet name="Evidence Table" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="303">
   <si>
     <t>Year</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>Key Findings</t>
-  </si>
-  <si>
-    <t>High</t>
   </si>
   <si>
     <t>Yes</t>
@@ -515,9 +512,6 @@
     <t>Not reported</t>
   </si>
   <si>
-    <t>Low Risk</t>
-  </si>
-  <si>
     <t>Prehab -24 (6)
 Control -10 (2)</t>
   </si>
@@ -759,12 +753,6 @@
   </si>
   <si>
     <t>Protein supplementation</t>
-  </si>
-  <si>
-    <t>Overall Risk of bias</t>
-  </si>
-  <si>
-    <t>Concerning domain(s)</t>
   </si>
   <si>
     <t>Post-operative complications</t>
@@ -992,18 +980,6 @@
   </si>
   <si>
     <t>Randomized Controlled Feasibility Trial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Some concerns </t>
-  </si>
-  <si>
-    <t>Some concerns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High </t>
-  </si>
-  <si>
-    <t>Low</t>
   </si>
   <si>
     <t>The study had a small sample size with a risk of Type 2 error and lacked complete participant blinding.
@@ -1166,39 +1142,6 @@
   </si>
   <si>
     <t>14.2 weeks</t>
-  </si>
-  <si>
-    <t>Performance bias (Domain 2)</t>
-  </si>
-  <si>
-    <t>Performance bias (Domain 2)
-Attrition bias (Domain 3)</t>
-  </si>
-  <si>
-    <t>Performance bias (Domain 2)
-Attrition bias  (Domain 3)</t>
-  </si>
-  <si>
-    <t>Selection bias (Domain 1)
-Performance bias (Domain 2)</t>
-  </si>
-  <si>
-    <t>Performance bias (Domain 2)
-Unclear Detection bias (Domain 4)</t>
-  </si>
-  <si>
-    <t>Performance bias (Domain 2)
-Detection bias  (Domain 4)</t>
-  </si>
-  <si>
-    <t>Performance bias (Domain 2)
-Unclear Detection bias  (Domain 4)</t>
-  </si>
-  <si>
-    <t>Performance bias (Domain 2)
-Detection bias  (Domain 4)
-Reporting bias  (Domain 5)
-Attrition bias (Domain 3)</t>
   </si>
 </sst>
 </file>
@@ -1699,7 +1642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E6C0315-B915-B14D-AC51-9D3C9D78CEB9}">
-  <dimension ref="A1:AE45"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.5" style="3" customWidth="1"/>
@@ -1723,2502 +1666,2345 @@
     <col min="25" max="25" width="12.5" customWidth="1"/>
     <col min="26" max="26" width="25.83203125" customWidth="1"/>
     <col min="27" max="27" width="29.5" customWidth="1"/>
-    <col min="28" max="29" width="28.83203125" customWidth="1"/>
-    <col min="30" max="30" width="35.5" customWidth="1"/>
-    <col min="31" max="31" width="82.83203125" customWidth="1"/>
+    <col min="28" max="28" width="35.5" customWidth="1"/>
+    <col min="29" max="29" width="82.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="34">
+    <row r="1" spans="1:29" ht="34">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="I1" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="L1" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>190</v>
-      </c>
       <c r="M1" s="7" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="AA1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="AB1" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="AC1" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" ht="153">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" ht="153">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>2018</v>
       </c>
       <c r="D2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
       <c r="F2" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q2" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H2" s="6" t="s">
+      <c r="R2" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="S2" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q2" s="6" t="s">
+      <c r="T2" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="AA2" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="R2" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="S2" s="4" t="s">
+      <c r="AB2" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="T2" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>261</v>
-      </c>
       <c r="AC2" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="AD2" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE2" s="4" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" ht="255">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="255">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>2018</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G3" t="s">
+        <v>192</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="G3" t="s">
-        <v>196</v>
-      </c>
-      <c r="H3" s="6" t="s">
+      <c r="R3" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="S3" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="I3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q3" s="6" t="s">
+      <c r="T3" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA3" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="R3" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA3" s="9" t="s">
+      <c r="AB3" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="AB3" s="4" t="s">
-        <v>262</v>
-      </c>
       <c r="AC3" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="AD3" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="AE3" s="4" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" ht="221">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="221">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>2020</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" t="s">
+        <v>192</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="G4" t="s">
-        <v>196</v>
-      </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="K4" s="6" t="s">
+      <c r="R4" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="S4" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="L4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q4" s="4" t="s">
+      <c r="T4" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="U4" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="W4" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="X4" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y4" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA4" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="R4" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="T4" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="U4" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="V4" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="W4" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="X4" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y4" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z4" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA4" s="4" t="s">
+      <c r="AB4" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="AB4" s="6" t="s">
-        <v>262</v>
-      </c>
       <c r="AC4" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="AD4" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="AE4" s="6" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" s="5" customFormat="1" ht="153">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" s="5" customFormat="1" ht="153">
       <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="4">
         <v>2021</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="S5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="T5" s="4" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AB5" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AC5" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="AD5" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="AE5" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" s="3" customFormat="1" ht="204">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" s="3" customFormat="1" ht="204">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3">
         <v>2021</v>
       </c>
       <c r="D6" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="S6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="T6" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="X6" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="Y6" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z6" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA6" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q6" s="17" t="s">
+      <c r="AB6" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="R6" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="S6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="T6" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="U6" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="V6" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="W6" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="X6" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="Y6" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z6" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA6" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB6" s="4" t="s">
-        <v>263</v>
-      </c>
       <c r="AC6" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="AD6" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="AE6" s="4" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" ht="170">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="170">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3">
         <v>2023</v>
       </c>
       <c r="D7" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="4" t="s">
+      <c r="I7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="S7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="T7" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="U7" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="V7" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="W7" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="X7" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="Y7" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z7" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA7" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q7" s="9" t="s">
+      <c r="AB7" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="R7" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="S7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="T7" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="U7" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="V7" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="W7" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="X7" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="Y7" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z7" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA7" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="AB7" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="AC7" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="AD7" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE7" s="4" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" s="3" customFormat="1" ht="187">
+      <c r="AC7" s="4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" s="3" customFormat="1" ht="187">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="3">
         <v>2023</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="4" t="s">
+      <c r="I8" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="X8" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y8" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z8" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="AA8" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB8" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="R8" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="T8" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="U8" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="V8" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="W8" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="X8" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y8" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="Z8" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="AA8" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB8" s="4" t="s">
-        <v>262</v>
-      </c>
       <c r="AC8" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="AD8" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="AE8" s="4" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" ht="204">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="204">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3">
         <v>2020</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="P9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="V9" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="X9" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y9" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z9" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA9" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="AB9" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="O9" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="P9" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q9" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="R9" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="S9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="T9" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="U9" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="V9" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="W9" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="X9" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y9" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z9" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA9" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="AB9" s="4" t="s">
-        <v>116</v>
-      </c>
       <c r="AC9" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="AD9" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE9" s="4" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" s="3" customFormat="1" ht="204">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" s="3" customFormat="1" ht="204">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C10" s="3">
         <v>2019</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="V10" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="W10" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="X10" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y10" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z10" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA10" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB10" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="S10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T10" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="U10" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="V10" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="W10" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="X10" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y10" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z10" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA10" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB10" s="4" t="s">
-        <v>116</v>
-      </c>
       <c r="AC10" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="AD10" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="AE10" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" ht="238">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="238">
       <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F11" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="R11" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="H11" s="6" t="s">
+      <c r="S11" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="P11" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q11" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="R11" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="S11" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="T11" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="W11" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Y11" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="Z11" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AA11" s="19">
         <v>0.83299999999999996</v>
       </c>
       <c r="AB11" s="4" t="s">
-        <v>262</v>
+        <v>143</v>
       </c>
       <c r="AC11" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="AD11" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="AE11" s="4" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" ht="187">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="187">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12">
         <v>2023</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F12" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="G12" t="s">
+        <v>197</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="S12" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="T12" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="U12" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="V12" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="W12" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="X12" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y12" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z12" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA12" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB12" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="G12" t="s">
-        <v>201</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q12" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="R12" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="S12" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="T12" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="U12" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="V12" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="W12" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="X12" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y12" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z12" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA12" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB12" s="4" t="s">
-        <v>262</v>
-      </c>
       <c r="AC12" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="AD12" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="AE12" s="4" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" ht="221">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="221">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13">
         <v>2023</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="G13" t="s">
+        <v>197</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="R13" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="G13" t="s">
-        <v>201</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="P13" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q13" s="6" t="s">
+      <c r="S13" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="T13" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="V13" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="W13" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="X13" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="Y13" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z13" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA13" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="R13" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="S13" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="T13" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="U13" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="V13" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="W13" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="X13" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y13" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z13" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA13" s="4" t="s">
-        <v>152</v>
-      </c>
       <c r="AB13" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="AC13" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="AD13" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="AE13" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" ht="170">
+        <v>275</v>
+      </c>
+      <c r="AC13" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="170">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C14">
         <v>2024</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G14" t="s">
+        <v>198</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="I14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="S14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T14" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="U14" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="V14" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="W14" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="X14" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="Y14" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z14" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA14" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="G14" t="s">
-        <v>202</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="R14" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="S14" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="T14" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="U14" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="V14" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="W14" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="X14" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="Y14" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="Z14" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA14" s="4" t="s">
-        <v>155</v>
-      </c>
       <c r="AB14" s="4" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="AC14" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="AD14" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="AE14" s="4" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" ht="204">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="204">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C15">
         <v>2026</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F15" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G15" t="s">
+        <v>199</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="P15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="R15" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="G15" t="s">
-        <v>203</v>
-      </c>
-      <c r="H15" s="5" t="s">
+      <c r="S15" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="P15" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="R15" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="S15" s="4" t="s">
-        <v>61</v>
-      </c>
       <c r="T15" s="4" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="Z15" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AA15" s="20">
         <v>0.873</v>
       </c>
       <c r="AB15" s="4" t="s">
-        <v>264</v>
+        <v>157</v>
       </c>
       <c r="AC15" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="AD15" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="AE15" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" ht="204">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="204">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16">
         <v>2026</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G16" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H16" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R16" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="S16" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="I16" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="M16" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="O16" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q16" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="R16" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="S16" s="4" t="s">
-        <v>63</v>
-      </c>
       <c r="T16" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="V16" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="W16" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="AA16" s="19">
         <v>0.84399999999999997</v>
       </c>
       <c r="AB16" s="4" t="s">
-        <v>264</v>
+        <v>160</v>
       </c>
       <c r="AC16" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="AD16" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="AE16" s="4" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31" ht="170">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" ht="170">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C17">
         <v>2025</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G17" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="H17" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q17" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="R17" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="S17" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="I17" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N17" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="O17" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="P17" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q17" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="R17" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="S17" s="4" t="s">
-        <v>66</v>
-      </c>
       <c r="T17" s="4" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="V17" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="W17" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Z17" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AA17" s="4" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="AB17" s="4" t="s">
-        <v>262</v>
+        <v>167</v>
       </c>
       <c r="AC17" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="AD17" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE17" s="4" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="18" spans="1:31" ht="170">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" ht="170">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C18">
         <v>2025</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F18" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="G18" t="s">
+        <v>201</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q18" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="R18" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="G18" t="s">
-        <v>205</v>
-      </c>
-      <c r="H18" s="4" t="s">
+      <c r="S18" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="O18" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="P18" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q18" s="4" t="s">
+      <c r="T18" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="U18" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="V18" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="W18" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="X18" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="Y18" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z18" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="AA18" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="R18" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="S18" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="T18" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="U18" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="V18" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="W18" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="X18" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y18" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z18" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="AA18" s="4" t="s">
+      <c r="AB18" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="AB18" s="4" t="s">
-        <v>262</v>
-      </c>
       <c r="AC18" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="AD18" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="AE18" s="4" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="19" spans="1:31" ht="153">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" ht="153">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C19">
         <v>2026</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F19" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G19" t="s">
+        <v>194</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q19" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="R19" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="S19" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="T19" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="V19" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="W19" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="X19" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="Y19" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z19" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA19" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="G19" t="s">
-        <v>198</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="O19" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="P19" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q19" s="4" t="s">
+      <c r="AB19" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="R19" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="S19" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="T19" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="U19" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="V19" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="W19" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="X19" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y19" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z19" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA19" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="AB19" s="4" t="s">
-        <v>263</v>
-      </c>
       <c r="AC19" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="AD19" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="AE19" s="4" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31" ht="204">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" ht="204">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C20">
         <v>2025</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F20" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G20" t="s">
+        <v>202</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="R20" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="S20" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="V20" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="W20" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="X20" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y20" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z20" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA20" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB20" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="G20" t="s">
-        <v>206</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="K20" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="O20" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="P20" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q20" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="R20" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="S20" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="T20" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="U20" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="V20" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="W20" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="X20" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y20" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="Z20" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA20" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB20" s="4" t="s">
-        <v>3</v>
-      </c>
       <c r="AC20" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="AD20" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="AE20" s="4" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31" ht="170">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" ht="170">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C21">
         <v>2026</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F21" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G21" t="s">
+        <v>197</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="P21" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="R21" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="G21" t="s">
-        <v>201</v>
-      </c>
-      <c r="H21" s="6" t="s">
+      <c r="S21" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="I21" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="K21" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="L21" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="M21" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="N21" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="O21" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="P21" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q21" s="6" t="s">
+      <c r="T21" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="U21" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="V21" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="W21" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="X21" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y21" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z21" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA21" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="R21" s="6" t="s">
+      <c r="AB21" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="S21" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="T21" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="U21" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="V21" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="W21" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="X21" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y21" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z21" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA21" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="AB21" s="4" t="s">
-        <v>262</v>
-      </c>
       <c r="AC21" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="AD21" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="AE21" s="4" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31" s="3" customFormat="1" ht="204">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" s="3" customFormat="1" ht="204">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C22" s="3">
         <v>2022</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H22" s="5" t="s">
+      <c r="I22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="O22" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="P22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="R22" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="S22" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="I22" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="M22" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="O22" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="P22" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q22" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="R22" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="S22" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="T22" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="V22" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="W22" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="Y22" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="Z22" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AA22" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="AB22" s="4" t="s">
-        <v>264</v>
+        <v>223</v>
+      </c>
+      <c r="AB22" s="5" t="s">
+        <v>257</v>
       </c>
       <c r="AC22" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="AD22" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="AE22" s="4" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31" ht="221">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" ht="221">
       <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C23" s="3">
         <v>2024</v>
       </c>
       <c r="D23" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H23" s="5" t="s">
+      <c r="I23" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="P23" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="R23" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="S23" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="O23" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="P23" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q23" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="R23" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="S23" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="T23" s="4" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="U23" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="V23" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="W23" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="X23" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="Y23" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Z23" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AA23" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="AB23" s="4" t="s">
-        <v>3</v>
+        <v>228</v>
+      </c>
+      <c r="AB23" s="5" t="s">
+        <v>298</v>
       </c>
       <c r="AC23" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="AD23" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="AE23" s="4" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" ht="221">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" ht="221">
       <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C24" s="3">
         <v>2021</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F24" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="O24" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="P24" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="R24" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="S24" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="T24" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="U24" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="V24" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="W24" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="X24" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y24" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z24" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA24" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB24" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="L24" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="M24" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="N24" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="O24" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="P24" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q24" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="R24" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="S24" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="T24" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="U24" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="V24" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="W24" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="X24" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y24" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="Z24" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA24" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB24" s="6" t="s">
-        <v>3</v>
-      </c>
       <c r="AC24" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="AD24" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="AE24" s="4" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" s="3" customFormat="1" ht="221">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" s="3" customFormat="1" ht="221">
       <c r="A25" s="3">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C25" s="3">
         <v>2022</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E25" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q25" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="S25" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="T25" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="U25" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="V25" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="W25" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="X25" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="Y25" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z25" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="AA25" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="AB25" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="M25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="N25" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="O25" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="P25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q25" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="S25" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="T25" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="U25" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="V25" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="W25" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="X25" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y25" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="Z25" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="AA25" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="AB25" s="5" t="s">
-        <v>264</v>
-      </c>
       <c r="AC25" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="AD25" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="AE25" s="4" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="26" spans="1:31" s="3" customFormat="1" ht="272">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" s="3" customFormat="1" ht="272">
       <c r="A26" s="3">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C26" s="3">
         <v>2024</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F26" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="P26" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="R26" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="S26" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="U26" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="V26" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="W26" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="X26" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y26" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z26" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA26" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB26" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="M26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="N26" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="O26" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="P26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q26" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="R26" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="S26" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="T26" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="U26" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="V26" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="W26" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="X26" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y26" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z26" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA26" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="AB26" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="AC26" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="AD26" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="AE26" s="4" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31">
+      <c r="AC26" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29">
       <c r="A27" s="3"/>
       <c r="D27" s="18"/>
       <c r="Q27"/>
     </row>
-    <row r="28" spans="1:31">
+    <row r="28" spans="1:29">
       <c r="Q28"/>
     </row>
-    <row r="29" spans="1:31" ht="18">
+    <row r="29" spans="1:29" ht="18">
       <c r="D29" s="8"/>
       <c r="Q29" s="22"/>
     </row>
-    <row r="30" spans="1:31" ht="18">
+    <row r="30" spans="1:29" ht="18">
       <c r="D30" s="8"/>
       <c r="Q30" s="22"/>
     </row>
-    <row r="31" spans="1:31" ht="18">
+    <row r="31" spans="1:29" ht="18">
       <c r="D31" s="8"/>
       <c r="Q31" s="22"/>
     </row>
-    <row r="32" spans="1:31" ht="18">
+    <row r="32" spans="1:29" ht="18">
       <c r="D32" s="8"/>
       <c r="Q32" s="22"/>
     </row>

--- a/data/Evidence_Table.xlsx
+++ b/data/Evidence_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramanaye/Documents/GitHub/cancer_nutrition_evidence_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8018A002-653D-D146-B839-CF1F264EE4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD51FC2-294E-4043-AB32-0524728753BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16140" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
   </bookViews>
   <sheets>
     <sheet name="Evidence Table" sheetId="1" r:id="rId1"/>
@@ -965,9 +965,6 @@
     <t xml:space="preserve">No </t>
   </si>
   <si>
-    <t>Nutritional Status</t>
-  </si>
-  <si>
     <t>Functional capacity
 Nutritional status</t>
   </si>
@@ -1142,6 +1139,9 @@
   </si>
   <si>
     <t>14.2 weeks</t>
+  </si>
+  <si>
+    <t>Nutritional Status/Body composition</t>
   </si>
 </sst>
 </file>
@@ -1675,7 +1675,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1702,7 +1702,7 @@
         <v>187</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>188</v>
@@ -1711,13 +1711,13 @@
         <v>242</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O1" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="P1" s="7" t="s">
         <v>277</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>278</v>
       </c>
       <c r="Q1" s="7" t="s">
         <v>92</v>
@@ -1741,7 +1741,7 @@
         <v>190</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>252</v>
+        <v>302</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>191</v>
@@ -1756,7 +1756,7 @@
         <v>94</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="153">
@@ -1845,7 +1845,7 @@
         <v>90</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="255">
@@ -1901,7 +1901,7 @@
         <v>103</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="S3" s="4" t="s">
         <v>101</v>
@@ -1934,7 +1934,7 @@
         <v>105</v>
       </c>
       <c r="AC3" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="221">
@@ -2023,7 +2023,7 @@
         <v>110</v>
       </c>
       <c r="AC4" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" spans="1:29" s="5" customFormat="1" ht="153">
@@ -2085,7 +2085,7 @@
         <v>15</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="U5" s="4" t="s">
         <v>237</v>
@@ -2109,10 +2109,10 @@
         <v>114</v>
       </c>
       <c r="AB5" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AC5" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:29" s="3" customFormat="1" ht="204">
@@ -2129,7 +2129,7 @@
         <v>17</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>115</v>
@@ -2201,7 +2201,7 @@
         <v>118</v>
       </c>
       <c r="AC6" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="170">
@@ -2263,7 +2263,7 @@
         <v>23</v>
       </c>
       <c r="T7" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="U7" s="8" t="s">
         <v>237</v>
@@ -2290,7 +2290,7 @@
         <v>128</v>
       </c>
       <c r="AC7" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:29" s="3" customFormat="1" ht="187">
@@ -2346,7 +2346,7 @@
         <v>130</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="S8" s="4" t="s">
         <v>28</v>
@@ -2379,7 +2379,7 @@
         <v>131</v>
       </c>
       <c r="AC8" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="204">
@@ -2462,13 +2462,13 @@
         <v>114</v>
       </c>
       <c r="AA9" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AB9" s="4" t="s">
         <v>134</v>
       </c>
       <c r="AC9" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:29" s="3" customFormat="1" ht="204">
@@ -2557,7 +2557,7 @@
         <v>138</v>
       </c>
       <c r="AC10" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="238">
@@ -2646,7 +2646,7 @@
         <v>143</v>
       </c>
       <c r="AC11" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="187">
@@ -2735,7 +2735,7 @@
         <v>146</v>
       </c>
       <c r="AC12" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="221">
@@ -2821,10 +2821,10 @@
         <v>150</v>
       </c>
       <c r="AB13" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AC13" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="170">
@@ -2880,7 +2880,7 @@
         <v>152</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="S14" s="4" t="s">
         <v>57</v>
@@ -2910,10 +2910,10 @@
         <v>153</v>
       </c>
       <c r="AB14" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AC14" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="204">
@@ -3002,7 +3002,7 @@
         <v>157</v>
       </c>
       <c r="AC15" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="204">
@@ -3058,7 +3058,7 @@
         <v>159</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="S16" s="4" t="s">
         <v>62</v>
@@ -3091,7 +3091,7 @@
         <v>160</v>
       </c>
       <c r="AC16" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:29" ht="170">
@@ -3153,34 +3153,34 @@
         <v>65</v>
       </c>
       <c r="T17" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="U17" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="V17" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="Y17" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z17" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA17" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="U17" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="V17" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="W17" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="X17" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="Y17" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z17" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="AA17" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="AB17" s="4" t="s">
         <v>167</v>
       </c>
       <c r="AC17" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:29" ht="170">
@@ -3269,7 +3269,7 @@
         <v>168</v>
       </c>
       <c r="AC18" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:29" ht="153">
@@ -3358,7 +3358,7 @@
         <v>172</v>
       </c>
       <c r="AC19" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:29" ht="204">
@@ -3447,7 +3447,7 @@
         <v>175</v>
       </c>
       <c r="AC20" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:29" ht="170">
@@ -3536,7 +3536,7 @@
         <v>180</v>
       </c>
       <c r="AC21" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:29" s="3" customFormat="1" ht="204">
@@ -3622,10 +3622,10 @@
         <v>223</v>
       </c>
       <c r="AB22" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AC22" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:29" ht="221">
@@ -3687,7 +3687,7 @@
         <v>86</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="U23" s="4" t="s">
         <v>237</v>
@@ -3711,10 +3711,10 @@
         <v>228</v>
       </c>
       <c r="AB23" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AC23" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:29" ht="221">
@@ -3803,7 +3803,7 @@
         <v>220</v>
       </c>
       <c r="AC24" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:29" s="3" customFormat="1" ht="221">
@@ -3823,7 +3823,7 @@
         <v>211</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>203</v>
@@ -3865,7 +3865,7 @@
         <v>213</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="U25" s="4" t="s">
         <v>237</v>
@@ -3892,7 +3892,7 @@
         <v>215</v>
       </c>
       <c r="AC25" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:29" s="3" customFormat="1" ht="272">
@@ -3954,7 +3954,7 @@
         <v>207</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="U26" s="4" t="s">
         <v>237</v>
@@ -3981,7 +3981,7 @@
         <v>209</v>
       </c>
       <c r="AC26" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:29">

--- a/data/Evidence_Table.xlsx
+++ b/data/Evidence_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramanaye/Documents/GitHub/cancer_nutrition_evidence_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD51FC2-294E-4043-AB32-0524728753BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F005E70-7391-A64A-BAF2-36BF82EFB25B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16140" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="14720" windowHeight="16120" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
   </bookViews>
   <sheets>
     <sheet name="Evidence Table" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="277">
   <si>
     <t>Year</t>
   </si>
@@ -83,16 +83,10 @@
     <t>The effect of trimodal prehabilitation on the physical and psychological health of patients undergoing colorectal surgery: a randomised clinical trial</t>
   </si>
   <si>
-    <t>Significant improvement in functional capacity (6MWD) and incentive spirometry performance. Reduced anxiety and improved emotional well-being/general health scores. No overall reduction in postoperative morbidity, mortality, or hospital stay</t>
-  </si>
-  <si>
     <t>Ferreira et al.</t>
   </si>
   <si>
     <t>Feasibility of a novel mixed-nutrient supplement in a multimodal prehabilitation intervention for lung cancer patients awaiting surgery: A randomized controlled pilot trial</t>
-  </si>
-  <si>
-    <t>There was no statistically significant difference between groups in functional capacity (6MWT)  or quality of life (HRQoL), though the 37.7m improvement in 6MWT in the prehab group was considered clinically relevant</t>
   </si>
   <si>
     <t>1. Exercise- Weekly supervised hospital sessions (30 minutes of aerobic cycling and 30 minutes of resistance training ) + Home based exercises (30 minutes daily of aerobic activity and resistance training every second day)
@@ -131,9 +125,6 @@
 3. Psychology - Anxiety and depression assessment + relaxation techniques </t>
   </si>
   <si>
-    <t>60 per cent reduction number of patients with post-operative complications at 90 days after surgery and decreased rate of  non-compliance with neoadjuvant treatment. Patients showed improved physical capacity with a +31m 6-MWT  gain and boosted  quality of life scores</t>
-  </si>
-  <si>
     <t>Two-Week Multimodal Prehabilitation Program Improves Perioperative Functional Capability in Patients Undergoing Thoracoscopic Lobectomy for Lung Cancer: A Randomized Controlled Trial</t>
   </si>
   <si>
@@ -174,9 +165,6 @@
   </si>
   <si>
     <t>Evaluating the impact of a modified multi-modal prehabilitation program on perioperative outcomes in Chinese patients undergoing colorectal cancer surgery</t>
-  </si>
-  <si>
-    <t>Significant improvement in functional capacity with the prehabilitation group’s 6-minute walk distance (6MWD) being 60.9 m higher than the control group perioperatively. Forced vital capacity (FVC) was 0.35 L higher in the intervention group. No significant differences were found in length of stay, postoperative complications, or mortality.</t>
   </si>
   <si>
     <t>2-week, home-based multimodal program:
@@ -195,18 +183,12 @@
 Medical Optimization - Management of diabetes using Metformin or Insulin and mandatory administration of Pancreatic Enzyme Replacement Therapy (PERT)</t>
   </si>
   <si>
-    <t>No significant reduction in overall complications (33.3% in the prehabilitation group vs 54.5% in standard care, p=0.18). Significant reduction in Delayed Gastric Emptying (5.6% vs 40.9%, p=0.01). Patients achieved a 16-21% improvement across all physical and respiratory function tests, including FEV 1, FVC, hand strength, and the 10-meter walk test</t>
-  </si>
-  <si>
     <t>Trimodal home-based program:
 1. Exercise - Individualized, home-based training 3 times/week including 25 minutes of moderate-intensity aerobic activity (brisk walking, jogging, or cycling) and resistance training for eight main muscle groups (3 sets of 8–12 repetitions) using elastic bands.
 2. Nutritional support - Food-based intervention with a target daily protein intake of 1.5 g/kg of ideal body weight; whey protein supplements provided if needed to reach this goal. Caloric requirements estimated via the Harris-Benedict equation with a 1.2 stress factor.
 3. Psychology  - Single psychosocial counseling session teaching relaxation and imagery techniques (meditation, breathing exercises, and guided imagery) to be performed daily</t>
   </si>
   <si>
-    <t>Significant preservation of functional capacity at 4 weeks post-surgery; the prehabilitation group showed a much smaller decline in 6-minute walk distance (-15.4 m) compared to a significant decline in the control group (-97.9 m; p=0.014). While the prehabilitation group gained 40.8 m in the 6-MWT preoperatively (vs. 9.7 m in the control group), this difference was not statistically significant (p=0.250). No significant differences were observed in postoperative complication rates, length of hospital stay, or quality of life scores</t>
-  </si>
-  <si>
     <t>Triguero‑Cánovas et al.</t>
   </si>
   <si>
@@ -237,9 +219,6 @@
 3. Stress management—60–90 min individual psychoeducational session (CBT, relaxation techniques, and guided imagery) plus audio/written materials for self-directed practice</t>
   </si>
   <si>
-    <t>Trial demonstrated feasibility (53% recruitment, 13% attrition, no serious adverse events). Prehabilitation prevented decline in physical function: 49.4 m between-group difference in 6-MWT distance post-chemotherapy favoring prehabilitation. Prehabilitation participants reported significantly better quality of life (FACT-B), less fatigue (FACT-An), and higher physical activity levels (GLTEQ-LSI) compared to usual care</t>
-  </si>
-  <si>
     <t>Mu et al.</t>
   </si>
   <si>
@@ -249,18 +228,12 @@
 3. Psychology- 30-min individualized counseling sessions twice weekly; includes cognitive restructuring and assessment using the Hospital Anxiety and Depression Scale (HADS) and Fatigue Severity Scale (FFS)</t>
   </si>
   <si>
-    <t>Significant reduction in 30-day overall complication rate (9.1% vs. 26.2%), with the largest impact on pulmonary infections (6.1% vs. 21.5%). Accelerated recovery evidenced by earlier time to first flatus (58.32 vs. 89.55 h), shorter interval to oral intake (48.43 vs. 105.85 h), and reduced postoperative hospital stay (7.76 vs. 9.77 days). Patients demonstrated superior preoperative functional capacity with a higher 6-min walk distance (448.60m vs. 362.43m) and significantly improved quality of life (QoR-40c) and psychological scores</t>
-  </si>
-  <si>
     <t>Whole-course (10–16 weeks) supervised home-based multimodal program: 
 1. Exercise: Aerobic training (brisk walking 3 times/week, 30-minute sessions, intensity RPE 14–17) plus resistance and flexibility exercises.
 2. Nutritional support: Clinical dietitian assessment, increased dietary intake, oral nutritional supplements (ONS) with immune-boosting formulas/fiber, and supplementation of vitamins, minerals, or iron/rhEPO as needed. 
 3. Psychology: Family-based psychotherapy including daily meditation, breathing exercises, progressive muscle relaxation, and mandatory counseling for patients with HADS scores ≥ 8</t>
   </si>
   <si>
-    <t>Improved physical capacity prior to surgery with a +29.4 m 6-MWD gain compared to a -17.9 m loss in the control group. Higher adherence to neoadjuvant chemotherapy (NAC) with an 86.0% completion rate for all cycles at full dose vs. 64.3% in the control group. Significant reduction in postoperative complications, including a lower incidence of pneumonia (2.3% vs. 14.3%) and Clavien-Dindo grade II complications (7.0% vs. 23.8%). Patients also experienced shorter hospital stays, improved nutritional status, and superior quality of life scores</t>
-  </si>
-  <si>
     <t>Kawata et al.</t>
   </si>
   <si>
@@ -269,9 +242,6 @@
 2. Nutritional support - The m-prehab group received daily oral nutritional supplements (ONS) for 2 weeks preceding surgery, providing an additional 430 kcal and 47g of protein (rich in branched-chain amino acids and zinc)</t>
   </si>
   <si>
-    <t>The study found no significant difference between groups regarding the primary outcome of preoperative change in anaerobic threshold (AT) or the incidence of postoperative complications. However, the m-prehab group consumed significantly more protein (76.8 g/day vs. 61.6 g/day) and demonstrated a significant increase in quadriceps strength compared to the control group. A nonsignificant trend toward increased skeletal muscle index was also observed in the m-prehab group</t>
-  </si>
-  <si>
     <t>Sugimura et al.</t>
   </si>
   <si>
@@ -280,9 +250,6 @@
 2. Nutritional support: 250 mL/day (320 kcal/day) of branched-chain amino acid-rich nutritional supplements (leucine-rich) initiated immediately after baseline assessment and continued until surgery</t>
   </si>
   <si>
-    <t>Skeletal muscle mass increased by 1.7% in the combined intervention group, whereas it decreased by 1.1% in the control group (p=0.013). The intervention group also showed a significant increase in body weight (p=0.014), skeletal muscle mass index (p=0.044), and gait speed (p=0.031) compared to the control group. While not statistically significant, postoperative pneumonia incidence was lower in the prehabilitation group (3%) compared to the control group (14%) (p=0.187)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Yamamoto et al. </t>
   </si>
   <si>
@@ -291,13 +258,7 @@
 2. Nutritional support-Two daily packets of a supplement containing arginine, glutamine, and β-hydroxy-β-methylbutyrate (HMB), providing a total daily HMB dose of 2.4g</t>
   </si>
   <si>
-    <t>Prehabilitation was associated with significantly greater preservation of preoperative lean body mass (LBM) compared to standard care (mean difference 0.4 kg; P=0.043). Subgroup analysis showed that LBM preservation was more pronounced in women, patients with lower baseline C-reactive protein, and those with lower baseline skeletal muscle mass index. High adherence to both resistance training and HMB supplementation resulted in a significant LBM gain of +0.6 kg compared to the control group. No significant differences were observed between groups in functional capacity (6-minute walk distance) or postoperative complications</t>
-  </si>
-  <si>
     <t>Yuan and Chu</t>
-  </si>
-  <si>
-    <t>Significant reduction in severe (Grade III+) complications (4.76% vs. 23.91%) and pleural effusion (7.14% vs. 23.91%). Patients demonstrated clinically meaningful improvements in physical capacity with a +53.54m 6-MWT gain preoperatively and significantly better quality of life scores 30 days post-surgery. No significant impact was observed on anxiety or depression levels</t>
   </si>
   <si>
     <t>Triple prehabilitation program:
@@ -315,9 +276,6 @@
 3. Psychology - Educational booklet and videos regarding the clinical pathway + coping skills discussion + daily 20-minute sessions of deep breathing, meditation, and muscle relaxation</t>
   </si>
   <si>
-    <t>Experimental group showed significantly greater 6-MWT performance on the day before surgery (400.40 m vs. 383.25 m) and 30 days postoperatively (375.40 m vs. 336.85 m). The program led to a shorter postoperative hospital stay (7.91 days vs. 9.06 days) and earlier recovery milestones, including first flatus, ambulation, and drainage removal. While complications were lower in the experimental group (11 vs. 20), this difference was not statistically significant</t>
-  </si>
-  <si>
     <t>Prehabilitation with wearables versus standard of care before major abdominal cancer surgery: a randomised controlled pilot study</t>
   </si>
   <si>
@@ -333,49 +291,6 @@
 3. Psychology - Daily guided meditation using a mindfulness app for stress management and relaxation techniques</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Significantly greater improvement in functional capacity with a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>+85.6m 6-MWT gain</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (p = 0.014) compared to +13.2m in controls. Intervention group engaged in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>significantly more vigorous physical activity</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (36.1 min vs 17.5 min, p = 0.022). High compliance for exercise (84%) and food logging (82.9%), with 100% patient satisfaction for the overall programme. No significant changes were observed in HADS scores or body weight. </t>
-    </r>
-  </si>
-  <si>
     <t>Li et al.</t>
   </si>
   <si>
@@ -388,18 +303,12 @@
 3. Psychology - Success stories to boost confidence + counseling, meditation, and cognitive-behavioral training for those with anxiety or depression</t>
   </si>
   <si>
-    <t xml:space="preserve">Significant improvement in functional capacity (6MWD +39.2m pre-op and +75.4m post-op vs control). Enhanced nutritional status with higher serum albumin and prealbumin levels and reduced need for postoperative albumin supplementation. Lower incidence of major pulmonary infections (6/66 vs 16/65 in control) and significantly shorter postoperative hospital and ICU stays.	</t>
-  </si>
-  <si>
     <t>Multimodal Prehabilitation for Lung Cancer Surgery: A Randomized Controlled Trial</t>
   </si>
   <si>
     <t>Multimodal home-based program:
 1. Exercise-  Individualized training 4 times per week, including 30 minutes of aerobic exercise (brisk walking, jogging, or cycling) 3 days per week at moderate intensity (Borg 12–13) and 30 minutes of resistance training 1 day per week using elastic bands for 8 muscle groups (3 sets of 8–12 repetitions)
 2. Nutrition - Dietary habits assessment by a dietitian plus whey protein supplementation to ensure a daily protein intake of 1.2 to 1.5 g/kg of ideal body weight</t>
-  </si>
-  <si>
-    <t>Significant improvement in functional capacity before and after surgery. Preoperatively, the prehabilitation group showed a mean 6-minute walk distance (6MWD) increase of +36.9m, while the control group declined by 22.8m (P &lt; .001). Postoperatively (4–8 weeks), the prehabilitation group maintained a gain of +15.4m compared to a -81.8m decline in the control group (P &lt; .001). There were no statistically significant differences in the number or severity of postoperative complications, length of hospital stay, or neoadjuvant chemotherapy adherence</t>
   </si>
   <si>
     <t>Frail and high-risk patients (ASA classes 4 and 5) were excluded from the trial</t>
@@ -437,9 +346,6 @@
 1. Exercise- Personalized home-based aerobic (30 mins moderate intensity 3-4 days/week) + resistance training (8 exercises targeting major muscle groups, 2 sets of 8-15 reps, 3-4 days/week). The PREHAB+ group also attended a once-weekly supervised in-hospital session (30 mins aerobic + 25 mins resistance + 5 mins stretching).
 2. Nutritional support - Consultation with a registered dietitian + whey protein supplementation to meet ESPEN requirements of 1.2g/kg of body weight. Supplements were taken within one hour of exercise to utilize the 'anabolic window'.
 3. Psychology - 60-minute session with a psychology-trained researcher for anxiety reduction + personalized relaxation techniques (visualization and breathing exercises) practiced at home 2-3 times/week using audio tracks</t>
-  </si>
-  <si>
-    <t>PREHAB+ group showed slightly greater improvements in 6-minute walking distance  before and after surgery compared with the REHAB group, but no statistically significant differences were found between groups in functional walking capacity. No significant difference was detected between groups for postoperative walking capacity (6MWD). Both groups improved preoperatively: PREHAB+ (+21m) and REHAB (+10m). However, previously inactive patients in the PREHAB+ group were 7 times more likely to significantly improve functional capacity (OR 7.07). The program successfully increased the proportion of PREHAB+ patients meeting physical activity guidelines from 49% to 86%. Postoperative complication rates and length of stay were similar between groups</t>
   </si>
   <si>
     <t>PREHAB+ - 41 (4)
@@ -835,9 +741,6 @@
 3. Psychosocial (Medical Coaching): Six sessions (face-to-face or teleconference) with accredited medical coaches focusing on resilience, emotional management, and goal setting</t>
   </si>
   <si>
-    <t>No significant difference was observed in the primary outcome of anaerobic threshold (AT) between groups. However, the prehabilitation group showed a significantly attenuated decline in peak VO2 compared to controls (-0.4 vs. -2.5 mL/kg/min; p = 0.022). Prehabilitation also resulted in significantly less skeletal muscle loss (-11.6 vs. -15.6 cm2/m2; p = 0.049) and improved retention of hand-grip strength postoperatively (p = 0.009 at 6 weeks). Quality of life (global health status) and psychological markers (anxiety and depression) were significantly better in the intervention group at multiple preoperative and postoperative time points. Notably, more prehabilitation patients completed their full dose of neoadjuvant therapy (75% vs. 46%; p = 0.036). There were no significant differences in postoperative complications, length of stay, or 3-year mortality</t>
-  </si>
-  <si>
     <t>supervised exercise - 76 ± 14%, 
 home exercise - 65 ± 27%
 medical coaching adherence - 82 ± 20%</t>
@@ -857,9 +760,6 @@
 </t>
   </si>
   <si>
-    <t>No significant difference was observed in the primary outcome of functional capacity (6MWT) between groups at any time point. Both groups returned to baseline functional capacity by 8 weeks postoperatively. The PREHAB group showed significantly better health-related quality of life (SF-36) at 4 weeks postoperatively in Physical Summary (p = 0.006), General Health (p = 0.007), and Mental Health (p = 0.044) scores. Significantly more PREHAB patients were discharged by postoperative day 2 (42% vs. 16%; p = 0.007). There were no significant differences in 30-day emergency visits, readmissions, or postoperative complications</t>
-  </si>
-  <si>
     <t>Pre-op PREHAB: Exercise - 84.9 ± 25.3%, Nutrition - 89.5 ± 23.5%</t>
   </si>
   <si>
@@ -929,19 +829,10 @@
     <t>Neoadjuvant chemotherapy adherence</t>
   </si>
   <si>
-    <t>4-week multimodal prehabilitation program did not reduce 30-day postoperative complications (measured by the Comprehensive Complication Index) compared to postoperative rehabilitation. There were also no significant differences in length of stay, readmissions, or emergency department visits between the two groups. While the main analysis showed no benefit for functional capacity, a per-protocol analysis revealed that patients who adhered to ≥75% of the prehabilitation sessions walked an average of 29 meters farther than those in the rehabilitation group before surgery. However, this improved physical fitness did not translate into better clinical outcomes</t>
-  </si>
-  <si>
     <t>Functional Capacity</t>
   </si>
   <si>
     <t>Dietary councelling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reduction in overall postoperative complications (17.4% vs. 33.3%), and a shorter hospital stay (5.74 vs. 6.67 days),  although the difference was  not statistically significant. Patients achieved a significant improvement in the 6-MWT (+78.9 m pre-surgery and +68.9 m at 6 weeks post-surgery compared to diagnosis) and improved cardiorespiratory function </t>
-  </si>
-  <si>
-    <t>The intervention was associated with a 21.9 point higher Quality of Recovery-15 score during the first 3 postoperative days compared to the control group, exceeding the minimal clinically relevant difference (includes 15 questions related to common postoperative conditions, including pain, nausea/vomiting, exhaustion, anxiety, and overall well-being). No statistically significant differences in postoperative complication rates, length of stay, or reoperation were found between the groups. Study participants demonstrated a median adherence and compliance of 100% with the training intervention</t>
   </si>
   <si>
     <t>Quality of Recovery-15 (QoR-15)</t>
@@ -983,13 +874,7 @@
 The nutritional intervention window was short (2–3 weeks), and there was poor compliance with the psychological component</t>
   </si>
   <si>
-    <t>Notes on optimal delivery</t>
-  </si>
-  <si>
     <t>Author</t>
-  </si>
-  <si>
-    <t>For frail patients, a 4-to-5-week prehabilitation window may be insufficient to build the necessary physiological reserve; significant improvements in lean body mass, functional capacity, and muscle strength in elderly populations have typically been observed only after 12 weeks of more intense exercise and protein supplementation. Optimal nutrition is a cornerstone of this process, requiring high-target protein intake (1.5 g/kg) specifically timed within one hour of exercise to maximize muscle protein synthesis and counteract surgical stress. In environments already optimized by Enhanced Recovery Pathways (ERPs), prehabilitation may need to be more intensive or targeted toward patients undergoing major open surgeries where the potential for clinical improvement is greater</t>
   </si>
   <si>
     <r>
@@ -1016,46 +901,13 @@
     </r>
   </si>
   <si>
-    <t>The primary objective of this trial was to assess the feasibility of the intervention rather than to provide definitive evidence of clinical efficacy. The researchers emphasize that this "pilot trial provides feasibility data supporting the design of larger efficacy and implementation trials. Optimal prehabilitation should be multimodal and personalized, combining supervised exercise with targeted nutritional and psychological support to maximize functional reserves before surgery. The nutrition component is critical; it should go beyond basic advice to include anabolic-promoting supplements like whey protein (reaching ≥1.5 g/kg/d), leucine, and omega-3 fatty acids, which work synergistically with exercise to enhance muscle protein synthesis. Maintaining high adherence (ideally &gt;80%) through regular monitoring and palatable, nutrient-dense supplements is essential for the intervention's success. This integrated approach ensures patients are physiologically and mentally prepared to withstand the stress of surgery and recover more efficiently.</t>
-  </si>
-  <si>
     <t>Functional capacity
 Postoperative complications</t>
   </si>
   <si>
-    <t>Optimal delivery of multimodal prehabilitation requires a supervised, personalized program (ideally 4 weeks) that integrates high-intensity exercise, psychological resilience training, and robust nutritional support. The nutritional component is critical and should be dietitian-led, focusing on achieving a high protein goal of 1.5g/kg/day through targeted dietary counseling and whey protein supplementation. Furthermore, the inclusion of micronutrients (Vitamin D and multivitamins) is essential to correct underlying deficiencies and optimize the metabolic environment for recovery. This synergistic approach effectively increases a patient’s physiological reserve, enabling them to better withstand surgical stress and avoid severe medical complications</t>
-  </si>
-  <si>
-    <t>Consider introducing supervised training sessions, a consistent duration of the intervention, and better integration into medical treatment. The nutritional component should be individualized by a dietitian to adjust for the metabolic stress of surgery, providing support even to patients who do not show signs of baseline malnutrition. It is essential to ensure a high daily protein intake of 1.2 to 1.5 g/kg through whey protein supplementation, which is most effective when consumed immediately following exercise sessions. Finally, success is bolstered by active weekly telephone monitoring from both nutritionists and kinesiologists to address adherence barriers and provide corrective feedback throughout the care continuum</t>
-  </si>
-  <si>
     <t>Good (specific % not reported)</t>
   </si>
   <si>
-    <t>multimodal prehabilitation requires a multidisciplinary team to integrate exercise, nutrition, and psychological support into a cohesive, patient-centered plan. The nutrition component should focus on high-quality protein supplementation (such as 1.5 g/kg/d of whey protein) administered within one hour of exercise to specifically facilitate muscle synthesis. This synergistic approach, combined with individualized dietary counseling to correct unhealthy eating habits and ensure caloric needs are met, provides the physiological reserve necessary to withstand surgical stress and improve functional recovery</t>
-  </si>
-  <si>
-    <t>Optimal delivery should utilize a personalized, trimodal approach combining endurance/resistance exercise, nutritional optimization, and psychological support, ideally integrated throughout the neoadjuvant treatment phase to maximize physiological reserve. The nutritional component focuses on achieving high protein targets (1.5 g/kg) and using Oral Nutritional Supplements (ONS) to prevent sarcopenia and malnutrition often exacerbated by chemotherapy. Home-based, semi-supervised models are recommended as they are cost-effective, require minimal hospital visits, and improve patient participation compared to fully supervised hospital-based programs. Finally, using objective monitoring tools (such as wearables) is essential for accurately tracking adherence and ensuring the intervention's intensity is sufficient to drive clinical improvements</t>
-  </si>
-  <si>
-    <t>multimodal prehabilitation should be delivered over a 2-4 week preoperative window, integrating high-intensity aerobic/resistance training with targeted nutritional and psychological support. The nutrition component must begin with a formal assessment (such as the PG-SGA) to guide the delivery of protein-rich oral nutritional supplements (ONS) and micronutrients (specifically Vitamins A, D, and E) to combat cancer-related malnutrition and sarcopenia. In pancreatic cases, mandatory Pancreatic Enzyme Replacement Therapy (PERT) is critical to ensure the absorption of these nutrients, thereby maximizing the patient's physiological reserve before the surgical insult.</t>
-  </si>
-  <si>
-    <t>A synergistic, multidisciplinary approach combining exercise, nutrition, and psychological support is needed to mitigate the multifactorial stress of surgery. The nutritional component should be individualized by a dietitian to achieve a daily protein target of 1.5 g/kg of ideal body weight, ideally utilizing whey protein supplementation immediately post-exercise to maximize muscle protein synthesis. To overcome barriers like distance and "assessment fatigue," programs should integrate telemedicine for remote monitoring and align follow-up assessments with standard clinical surgical visits. This comprehensive strategy ensures that patients are not just physically active, but metabolically and mentally prepared for the catabolic demands of major surgery</t>
-  </si>
-  <si>
-    <t>Optimal delivery involves an individualized approach that tailors exercise intensity to a patient's baseline fitness to ensure both safety and adherence. The nutrition component is critical, specifically requiring hyperproteic supplementation (1.2–1.5 g/kg/day), often combined with Vitamin D and CaHMB, to provide the necessary substrate for muscle synthesis and counteract surgical catabolism. Integrating these with psychological relaxation and aerobic/resistance training creates a synergistic effect that significantly attenuates the loss of functional capacity. For maximum efficacy, this multimodal program should be maintained throughout the entire perioperative window, from diagnosis until several weeks after surgery.</t>
-  </si>
-  <si>
-    <t>Multimodal prehabilitation should involve supervised, individualized exercise programs combined with comprehensive medical optimization and nutritional support. The nutritional component requires early dietician consultation and high-dose protein supplementation (e.g., 60g daily) alongside micronutrients like Vitamin D to counteract anabolic resistance in older or vulnerable patients. Ensuring high adherence and compliance through supervised sessions and regular follow-ups is critical for achieving significant improvements in early postoperative recovery. When delivered as an adjunct to a rigorous ERAS pathway, these interventions can effectively bridge the gap between low baseline functional capacity and the physiological demands of surgery.</t>
-  </si>
-  <si>
-    <t>Prehabilitation requires a minimum window of 4 weeks to successfully translate physiological training into measurable functional gains. The nutrition component should be individualized based on screening tools like MUST, utilizing dietary fortification and ONS to counteract the metabolic stress of the tumor and surgery. To maximize efficacy, this must be paired with psychological support to reduce pre-operative anxiety, which otherwise serves as a major barrier to patient adherence. In resource-limited settings, "walk/breathing" protocols are a feasible and cost-effective alternative to expensive supervised gym programs</t>
-  </si>
-  <si>
-    <t>multimodal prehabilitation requires a personalized, home-based approach supported by biweekly professional check-ins to foster accountability and address barriers like treatment-related fatigue. A critical nutrition component should focus on early individualized assessment and counseling to optimize nutrient intake and manage chemotherapy-induced side effects such as nausea and food aversions. Integrating these services immediately at diagnosis helps patients regain a sense of control and provides essential health education that often persists into the long-term survivorship period. Furthermore, delivery must be sensitive to the patient's emotional state, as the diagnosis period is frequently described as extremely overwhelming, which can hinder initial enrollment</t>
-  </si>
-  <si>
     <t>Small sample size. Since the primary outcome (QoR-15) is a self-reported questionnaire, the knowledge of group assignment could have introduced  bias, potentially inflating the scores in the intervention group.</t>
   </si>
   <si>
@@ -1068,40 +920,10 @@
     <t>Psychological interventions</t>
   </si>
   <si>
-    <t>An optimal delivery model is a short-course (1-week) multimodal program, which balances clinical efficacy with the need for timely surgery to prevent tumor progression. A critical nutrition component involves achieving high protein (1.2–1.5 g/kg/day) and calorie (25–30 kcal/kg/day) targets using tumor-targeted immunonutrition to specifically address cancer-driven metabolic and immune derangements. To maximize results, this nutritional support must be synergistically paired with supervised physical training and psychological counseling to remove emotional barriers and physically prepare the patient for surgical stress</t>
-  </si>
-  <si>
-    <t>Optimal delivery requires a  supervised multimodal approach initiated at the start of neoadjuvant therapy to counteract the hypercatabolic state and physical decline induced by chemotherapy. The nutrition component utilizing regular dietitian assessments and  immune-enhancing ONS to prevent skeletal muscle loss and enhance surgical resilience. Success depends on the synergy between exercise and nutrition, where structured physical activity stimulates anabolic pathways to optimize the utilization of provided nutrients. This comprehensive, "whole-course" strategy is essential for reducing postoperative complications and ensuring high chemotherapy completion rates</t>
-  </si>
-  <si>
     <t>Change in anerobic thershold</t>
   </si>
   <si>
     <t xml:space="preserve">92% for protein intake </t>
-  </si>
-  <si>
-    <t>Optimal delivery requires a supervised, synergistic approach combining exercise and nutrition for a duration typically exceeding 4 weeks, as shorter programs (like the 2-week version in this study) may fail to improve cardiopulmonary reserves. The nutrition component must provide high-dose protein, ideally ≥1.5 g/kg/day—alongside branched-chain amino acids and micronutrients like zinc to effectively counteract sarcopenia and stimulate muscle synthesis. Success depends on high-intensity physical activity (monitored via step counts or wearable devices) to ensure the body utilizes these nutrients to build functional reserve rather than just increasing intake. Ultimately, a multidisciplinary team approach is essential to provide the feedback and motivation necessary to achieve meaningful improvements in surgical resilience</t>
-  </si>
-  <si>
-    <t>For older patients, optimal delivery requires a synergistic approach, as the sources demonstrate that exercise alone is insufficient to increase skeletal muscle mass during chemotherapy. The nutrition component must specifically include leucine-rich amino acids to overcome the anabolic resistance common in the elderly, effectively stimulating muscle protein synthesis. To address the low compliance seen in this trial, delivery should involve a multidisciplinary team providing continuous monitoring and patient interviews. Furthermore, exercise should be individually tailored in intensity to accommodate the variable physical capacities of older adults, which can enhance overall adherence and clinical outcomes.</t>
-  </si>
-  <si>
-    <t>a synergistic multidisciplinary approach is required where resistance training provides the mechanical stimulus and targeted nutrition - specifically leucine-rich amino acids or HMB which overcomes anabolic resistance in older adults. The  nutrition component must be carefully monitored to ensure high adherence, as the preservation of lean body mass is significantly greater in patients who strictly follow both the exercise and supplement protocols. To be most effective, programs should be risk-adapted, focusing on vulnerable populations (such as women or those with low baseline muscle mass) who demonstrate the highest potential for measurable improvement. Furthermore, a duration longer than the average 17 days may be necessary to build a durable physiological reserve that can withstand the intense catabolic stress of major surgery</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> multidisciplinary approach typically lasting at least 2 weeks is needed, though 4–8 weeks is ideal if surgery can be safely delayed. The nutrition component should involve personalized counseling to hit targets of 25–30 kcal/kg of energy and 1.2–2.0 g/kg of protein, using whey protein or ONS when natural intake is insufficient. For high-risk patients (NRS-2002 ≥ 5), early oral or enteral support is preferred to boost physiological reserves before the stress of surgery. Integration of structured resistance training alongside aerobic and respiratory exercises is also recommended to counteract cancer-related cachexia and further optimize metabolic resilience</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Provision of high-quality protein (like the 1,000 ml/d ONS used in this study) during the post-exercise "window of synergy"maximizes protein synthesis and attenuate surgical catabolism. For short-course programs, high intervention intensity and frequency (e.g., supervised daily sessions) are necessary to compensate for the limited duration and ensure clinical effectiveness. Finally, psychological modulation acts as a catalyst by reducing anxiety-induced stress and securing the high behavioral adherence needed for the other components to succeed.</t>
-  </si>
-  <si>
-    <t>Optimal multimodal prehabilitation should begin with a baseline nutritional screening using validated tools like the NRS-2002 to identify patients at risk of malnutrition who require Oral Nutritional Supplementation (ONS) alongside dietary counseling to effectively preserve muscle mass. Integrating exercise, nutrition, and psychological support into a single, user-friendly digital platform can enhance adherence, particularly for components that typically see lower engagement. Furthermore, the intervention should ideally span at least three to four weeks to ensure sufficient time for physiological improvements to translate into better post-operative outcomes. Focus should remain on individualized targets, such as specific protein goals and tailored exercise intensities, to maximize functional gains prior to surgery</t>
-  </si>
-  <si>
-    <t>multimodal prehabilitation involves a structured, home-based program lasting at least 7–9 weeks, ideally synchronized with neoadjuvant chemotherapy to maximize physiological gains without delaying surgery. A robust nutritional component is critical, prioritizing high-quality protein supplementation (1.2–1.5 g/kg) and targeted oral nutritional supplementation (400–900 kcal/d) supervised by professional dietitians to counteract the catabolic effects of chemotherapy. This multidisciplinary approach effectively preserves and enhances functional and nutritional reserves, leading to fewer pulmonary complications and faster postoperative recovery</t>
-  </si>
-  <si>
-    <t>multimodal prehabilitation should be highly personalized, ideally integrating supervised exercise sessions to improve patient engagement and ensure physiological gains. The nutrition component is critical; it must provide adequate protein (e.g., 1.5 g/kg ideal body weight) and energy to serve as a substrate for the anabolic effects of exercise and to counteract surgical catabolism. For maximum benefit, whey protein should be ingested within one hour of exercise sessions. Finally, incorporating psychological support not only reduces perioperative anxiety but also serves as a motivational tool to enhance adherence to the exercise and diet protocols.</t>
   </si>
   <si>
     <t>Prehabilitation – 26 (2)
@@ -1111,21 +933,12 @@
     <t>Change in anaerobic thershold</t>
   </si>
   <si>
-    <t>Optimal delivery should span the entire 15-week neoadjuvant period to counteract the toxic effects of chemotherapy and preserve physiological reserve. Nutritional intervention must involve frequent, tailored input from specialist dieticians rather than generic advice, focusing on optimizing calorie and protein intake to support muscle synthesis during exercise. Combining supervised aerobic/resistance sessions with flexible home-based exercises and psychological coaching ensures high adherence and builds the resilience necessary for patients to complete their full dose of neoadjuvant therapy</t>
-  </si>
-  <si>
-    <t>Optimal delivery requires an individualized, supervised approach integrating aerobic and resistance exercise, nutritional optimization, and psychological support for at least 3 weeks to enhance functional reserve. The nutrition component is vital, specifically targeting a protein intake of 1.5 g/kg/day, which often necessitates high-quality whey protein supplementation consumed within one hour post-exercise to maximize muscle protein synthesis. Incorporating digital tracking tools (like calorie-counting apps) and structured home-based regimens with completion diaries can significantly boost patient adherence and self-management. Finally, while short durations of 2–3 weeks maximize compliance and prevent surgical delays, they may be insufficient to impact long-term quality of life or deep-seated psychological distress</t>
-  </si>
-  <si>
     <t>Respiratory Muscle Training</t>
   </si>
   <si>
     <t>Complete Oral Nutritional Supplement</t>
   </si>
   <si>
-    <t>multimodal prehabilitation should prioritize high-risk, sedentary patients, who are significantly more likely to see meaningful improvements in functional capacity (most significant benefits were seen in previously inactive and sedentary patients, particularly women, who were 7.07 times more likely to improve functional capacity through prehabilitation). Effective programs must integrate aerobic and resistance exercise with nutritional support, specifically timing protein intake within the "anabolic window" for maximum benefit. To outperform standard home-based programs, practitioners should consider increased exercise intensity or a higher frequency of supervised sessions. Finally, involving qualified professionals for supervision is essential to promote patient confidence and ensure adherence to recommended clinical goals</t>
-  </si>
-  <si>
     <t>The study faced selection bias from excluding unwilling participants and variability in chemotherapy regimens which may affect generalizability. Additionally, the short follow-up period meant long-term outcomes like progression-free and overall survival were not assessed. The use of quasi-randomization (odd-even method) place the study at a high risk for bias despite the blinding of outcome assessors</t>
   </si>
   <si>
@@ -1142,6 +955,75 @@
   </si>
   <si>
     <t>Nutritional Status/Body composition</t>
+  </si>
+  <si>
+    <t>Significant improvement in functional capacity before surgery (+36.9 m vs −22.8 m; P&lt;0.001) and after surgery (+15.4 m vs −81.8 m; P&lt;0.001). There were no statistically significant differences in postoperative complications, length of hospital stay, or neoadjuvant chemotherapy adherence.</t>
+  </si>
+  <si>
+    <t>PREHAB+ group showed slightly greater improvements in 6-minute walking distance  before and after surgery compared with the REHAB group, but no statistically significant differences were found between groups. Both groups improved preoperatively: PREHAB+ (+21m) and REHAB (+10m). However, previously inactive patients in the PREHAB+ group were 7 times more likely to significantly improve functional capacity (OR 7.07). Postoperative complication rates and length of stay were similar between groups</t>
+  </si>
+  <si>
+    <t>4-week multimodal prehabilitation program did not reduce 30-day postoperative complications (measured by the Comprehensive Complication Index) compared to postoperative rehabilitation. There were also no significant differences in functional capacity, length of stay, readmissions, or emergency department visits between the two groups. No significant differences between groups in physical or mental health scores. While the main analysis showed no benefit for functional capacity, a per-protocol analysis revealed that patients who adhered to ≥75% of the prehabilitation sessions walked an average of 29 meters farther than those in the rehabilitation group before surgery. However, this improved physical fitness did not translate into better clinical outcomes</t>
+  </si>
+  <si>
+    <t>Significant improvement in functional capacity (6MWD) and incentive spirometry performance (both p&lt;0.001). Significant improvement in anxiety and improved emotional well-being/general health scores. No overall reduction in postoperative morbidity, mortality, severe complications or hospital stay.</t>
+  </si>
+  <si>
+    <t>There was no statistically significant difference between groups in functional capacity (6MWT)  or quality of life (HRQoL), though the 37.7m improvement in 6MWT in the prehab group was considered clinically relevant. No significant improvement in nutritional status, body composition or quality of life.</t>
+  </si>
+  <si>
+    <t>Significant improvement in functional capacity with the prehabilitation group’s 6-minute walk distance (6MWD) being 60.9 m higher than the control group perioperatively (p&lt;0.001). Forced vital capacity (FVC) was 0.35 L higher in the intervention group. No significant differences were found in length of stay, postoperative complications, recovery quality or mortality.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Significant reduction in 90-day complications (23.7% vs 59.3%; RR 0.40). Minor complications were significantly reduced, while severe complications were similar between groups. Decreased rate of  non-compliance with neoadjuvant treatment (7.7% vs 37.3%, RR 0.20). Patients showed improved physical capacity with a +31m 6-MWT  gain (p=0.001) and boosted  quality of life scores. No signficant improvements in length of hospital stay. </t>
+  </si>
+  <si>
+    <t>Patients achieved a 16-21% improvement across all physical and respiratory function tests, including FEV 1, FVC, hand strength, and the 10-meter walk test. No significant reduction in overall complications (33.3% in the prehabilitation group vs 54.5% in standard care, p=0.18). Significant reduction noted in Delayed Gastric Emptying (5.6% vs 40.9%, p=0.01). No signficant improvement in length of stay.</t>
+  </si>
+  <si>
+    <t>Significant preservation of functional capacity (6MWD) at 4 weeks post-surgery (−15.4 m vs −97.9 m in controls, p = 0.014), indicating faster postoperative functional recovery. No significant preoperative improvement or difference at 8 weeks. No significant differences were observed in postoperative complication rates, length of hospital stay, or quality of life scores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patients achieved a significant improvement in 6MWT before surgery (+78.9 m), significant postoperative improvement (+68.9 m vs −27.2 m in controls, p=0.01), and improved CPET/METs (+0.79 vs −0.84 METs, p=0.001).Reduction in overall postoperative complications (17.4% vs. 33.3%), and a shorter hospital stay (5.74 vs. 6.67 days),  although the difference was  not statistically significant. </t>
+  </si>
+  <si>
+    <t>The intervention was associated with a 21.9 point higher Quality of Recovery-15 score during the first 3 postoperative days compared to the control group, exceeding the minimal clinically relevant difference (includes 15 questions related to common postoperative conditions, including pain, nausea/vomiting, exhaustion, anxiety, and overall well-being). No statistically significant differences in postoperative complication rates, length of stay, or reoperation were found between the groups. The intervention group showed a mean improvement of −2.4 points in their PG-SGA score.</t>
+  </si>
+  <si>
+    <t>Trial demonstrated feasibility (53% recruitment, 13% attrition, no serious adverse events). Functional capacity assessed using  6MWT and grip strength. Prehabilitation prevented decline in physical function: 49.4 m between-group difference in 6-MWT distance post-chemotherapy . Prehabilitation participants reported significantly better quality of life (FACT-B), less fatigue (FACT-An), and higher physical activity levels (GLTEQ-LSI) compared to usual care. No between-group differences in body weight, BMI and waist circumference.</t>
+  </si>
+  <si>
+    <t>Significant reduction in 30-day overall complication rate (9.1% vs. 26.2%, p=0.010), with the largest impact on pulmonary infections (6.1% vs. 21.5%). Accelerated recovery evidenced by earlier time to first flatus (58.32 vs. 89.55 h), shorter interval to oral intake (48.43 vs. 105.85 h), and reduced postoperative hospital stay (7.76 vs. 9.77 days, p&lt;0.001). Patients demonstrated superior preoperative functional capacity with a higher 6-min walk distance (448.60m vs. 362.43m), grip strength, gait speed, sit-to-stand performance, and pulmonary function (FVC, FEV1, PEF, MEP) and significantly improved quality of life (QoR-40c) and psychological scores. Intervention group had significantly higher caloric intake, protein intake, serum albumin, and prealbumin.</t>
+  </si>
+  <si>
+    <t>Improved physical capacity prior to surgery with a +29.4 m 6-MWD gain compared to a -17.9 m loss in the control group (p&lt;0.001). Higher adherence to neoadjuvant chemotherapy (NAC) with an 86.0% completion rate for all cycles at full dose vs. 64.3% in the control group. Significant reduction in postoperative complications, including a lower incidence of pneumonia (2.3% vs. 14.3%) and Clavien-Dindo grade II complications (7.0% vs. 23.8%). Patients also experienced shorter hospital stays ( p = 0.02)., improved nutritional status (greater weight gain, higher serum albumin and haemoglobin compared with control), and superior quality of life scores</t>
+  </si>
+  <si>
+    <t>No significant difference between groups in preoperative change in anaerobic threshold (AT),  incidence of postoperative complications or length of hospital stay. However, the m-prehab group consumed significantly more protein (76.8 g/day vs. 61.6 g/day) and demonstrated a significant increase in quadriceps strength (p=0.04) compared to the control group. A nonsignificant trend toward increased skeletal muscle index was also observed in the m-prehab group (p=0.09).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skeletal muscle mass increased by 1.7% in the combined intervention group, whereas it decreased by 1.1% in the control group (p=0.013). The intervention group also showed a significant increase in body weight (p=0.014), skeletal muscle mass index (p=0.044). Gait speed improved significantly in the exercise + nutrition group compared with control (p = 0.031).No significant between group differences in 6MWD, postoperative complications, length of stay or chemotherapy adherence. </t>
+  </si>
+  <si>
+    <t>Prehabilitation was associated with significantly greater preservation of preoperative lean body mass (LBM) compared to standard care (mean difference 0.4 kg; P=0.043). Subgroup analysis showed that LBM preservation was more pronounced in women, patients with lower baseline C-reactive protein, and those with lower baseline skeletal muscle mass index. No significant differences were observed between groups in functional capacity (6MWD), postoperative complications, length of stay.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patients demonstrated clinically meaningful improvements in physical capacity with a +53.54m 6-MWT gain preoperatively (p&lt;0.001) and significantly better quality of life scores (WHO Disability Assessment Schedule - WHODAS 2.0) 30 days post-surgery (p&lt;0.001). Significant reduction in severe (Grade III+) complications (4.76% vs. 23.91%, p=0.011) and pleural effusion (7.14% vs. 23.91%, p=0.032).  </t>
+  </si>
+  <si>
+    <t>Intervention group showed significantly greater 6-MWT performance on the day before surgery (400.40 m vs. 383.25 m) and 30 days postoperatively (375.40 m vs. 336.85 m). The program led to a shorter postoperative hospital stay (7.91 days vs. 9.06 days, p&lt;0.01) and earlier recovery milestones, including first flatus, ambulation, and drainage removal. While postoperative complications were lower in the intervention group (11 vs. 20), this difference was not statistically significant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Significantly greater improvement in functional capacity with a +85.6m 6-MWT gain (p = 0.014) compared to +13.2m in controls. Intervention group engaged in significantly more vigorous physical activity (36.1 min vs 17.5 min, p = 0.022). No significant changes were observed in body weight and HADS score. </t>
+  </si>
+  <si>
+    <t>Significant improvement in functional capacity (6MWD: +39.2m pre-op and +75.4m post-op) compared to control. Enhanced nutritional status with higher serum albumin and prealbumin levels and reduced need for postoperative albumin supplementation. Lower incidence of major pulmonary infections (6/66 vs 16/65 in control) and significantly shorter postoperative hospital (10.74 vs 13.24 days, P=0.003) and ICU stays. No significant difference in abdominal complications.</t>
+  </si>
+  <si>
+    <t>No significant difference was observed in the primary outcome of functional capacity (6MWT) between groups at any time point. Both groups returned to baseline functional capacity by 8 weeks postoperatively. The PREHAB group showed significantly better health-related quality of life (SF-36) at 4 weeks postoperatively in Physical Summary (p = 0.006), General Health (p = 0.007), and Mental Health (p = 0.044) scores. Median length of stay was similar (4 days in both groups), however, significantly more patients in the prehabilitation group were discharged by postoperative day 2 (42% vs 16%). There were no significant differences in 30-day emergency visits, readmissions, or postoperative complications.</t>
+  </si>
+  <si>
+    <t>No significant difference was observed in the primary outcome of anaerobic threshold (AT) between groups. However, the prehabilitation group showed a significantly attenuated decline in peak VO2 compared to controls  p = 0.022), indicating better preservation of cardiopulmonary fitness.  Prehabilitation also resulted in significantly less skeletal muscle loss (-11.6 vs. -15.6 cm2/m2; p = 0.049) and improved retention of hand-grip strength postoperatively (p = 0.009). Quality of life (global health status) and psychological markers (anxiety and depression) were significantly better in the intervention group at multiple time points. Notably, more prehabilitation patients completed their full dose of neoadjuvant therapy (75% vs. 46%; p = 0.036). There were no significant differences in postoperative complications, length of stay, or 3-year mortality.</t>
   </si>
 </sst>
 </file>
@@ -1220,11 +1102,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Google Sans Text"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF2E2E2E"/>
       <name val="Aptos Narrow"/>
@@ -1235,6 +1112,12 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Google Sans Text"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1281,8 +1164,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1303,11 +1185,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1650,7 +1533,7 @@
     <col min="4" max="4" width="37" style="6" customWidth="1"/>
     <col min="5" max="6" width="22.5" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="53.83203125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="54.83203125" style="6" customWidth="1"/>
     <col min="9" max="9" width="25" style="6" customWidth="1"/>
     <col min="10" max="11" width="25.6640625" style="6" customWidth="1"/>
     <col min="12" max="12" width="28.1640625" style="6" customWidth="1"/>
@@ -1666,7 +1549,7 @@
     <col min="25" max="25" width="12.5" customWidth="1"/>
     <col min="26" max="26" width="25.83203125" customWidth="1"/>
     <col min="27" max="27" width="29.5" customWidth="1"/>
-    <col min="28" max="28" width="35.5" customWidth="1"/>
+    <col min="28" max="28" width="69.1640625" customWidth="1"/>
     <col min="29" max="29" width="82.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1675,7 +1558,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1684,80 +1567,78 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>294</v>
+        <v>246</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>295</v>
+        <v>247</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>277</v>
+        <v>241</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>257</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="AC1" s="1"/>
     </row>
     <row r="2" spans="1:29" ht="153">
       <c r="A2">
@@ -1769,20 +1650,20 @@
       <c r="C2">
         <v>2018</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="13" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="G2" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>3</v>
@@ -1791,7 +1672,7 @@
         <v>3</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>3</v>
@@ -1800,53 +1681,51 @@
         <v>3</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>89</v>
+        <v>254</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="AC2" s="4" t="s">
-        <v>264</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="AC2" s="4"/>
     </row>
     <row r="3" spans="1:29" ht="255">
       <c r="A3">
@@ -1858,20 +1737,20 @@
       <c r="C3">
         <v>2018</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="G3" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>3</v>
@@ -1880,7 +1759,7 @@
         <v>3</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>3</v>
@@ -1889,53 +1768,51 @@
         <v>3</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="P3" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>299</v>
+        <v>250</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>101</v>
+        <v>255</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="AB3" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="AC3" s="4" t="s">
-        <v>296</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="AC3" s="4"/>
     </row>
     <row r="4" spans="1:29" ht="221">
       <c r="A4">
@@ -1947,20 +1824,20 @@
       <c r="C4">
         <v>2020</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="13" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="G4" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>3</v>
@@ -1969,7 +1846,7 @@
         <v>3</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>3</v>
@@ -1978,53 +1855,51 @@
         <v>3</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="P4" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="T4" s="6" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="U4" s="6" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="V4" s="6" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="W4" s="6" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="X4" s="6" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Y4" s="6" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="Z4" s="6" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AA4" s="4" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="AB4" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC4" s="6" t="s">
-        <v>259</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="AC4" s="6"/>
     </row>
     <row r="5" spans="1:29" s="5" customFormat="1" ht="153">
       <c r="A5" s="5">
@@ -2043,25 +1918,25 @@
         <v>8</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>3</v>
+        <v>216</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>3</v>
@@ -2070,76 +1945,74 @@
         <v>3</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="P5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>15</v>
+        <v>257</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AB5" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="AC5" s="4" t="s">
-        <v>272</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="AC5" s="4"/>
     </row>
     <row r="6" spans="1:29" s="3" customFormat="1" ht="204">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3">
         <v>2021</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="I6" s="4" t="s">
         <v>3</v>
       </c>
@@ -2147,7 +2020,7 @@
         <v>3</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>3</v>
@@ -2156,7 +2029,7 @@
         <v>3</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>3</v>
+        <v>216</v>
       </c>
       <c r="O6" s="4" t="s">
         <v>3</v>
@@ -2164,70 +2037,68 @@
       <c r="P6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="17" t="s">
-        <v>116</v>
+      <c r="Q6" s="16" t="s">
+        <v>98</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>18</v>
+        <v>258</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="Z6" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AA6" s="4" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="AB6" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC6" s="4" t="s">
-        <v>261</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="AC6" s="4"/>
     </row>
     <row r="7" spans="1:29" ht="170">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3">
         <v>2023</v>
       </c>
-      <c r="D7" s="15" t="s">
-        <v>21</v>
+      <c r="D7" s="14" t="s">
+        <v>19</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>3</v>
@@ -2236,87 +2107,85 @@
         <v>3</v>
       </c>
       <c r="K7" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="S7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="T7" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="L7" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="R7" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="S7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="T7" s="8" t="s">
-        <v>262</v>
-      </c>
       <c r="U7" s="8" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="V7" s="8" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="W7" s="8" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="X7" s="8" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="Y7" s="8" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="Z7" s="8" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AA7" s="4" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="AB7" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="AC7" s="4" t="s">
-        <v>263</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="AC7" s="4"/>
     </row>
     <row r="8" spans="1:29" s="3" customFormat="1" ht="187">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3">
         <v>2023</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>3</v>
@@ -2337,75 +2206,73 @@
         <v>3</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>300</v>
+        <v>251</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>28</v>
+        <v>260</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="AA8" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AB8" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AC8" s="4" t="s">
-        <v>267</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="AC8" s="4"/>
     </row>
     <row r="9" spans="1:29" ht="204">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3">
         <v>2020</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>29</v>
+      <c r="D9" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>3</v>
@@ -2423,78 +2290,76 @@
         <v>3</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>3</v>
+        <v>216</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="P9" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="17" t="s">
-        <v>135</v>
+      <c r="Q9" s="16" t="s">
+        <v>117</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>43</v>
+        <v>259</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="U9" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="V9" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="X9" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y9" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="Z9" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA9" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="V9" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="W9" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="X9" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="Y9" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="Z9" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="AA9" s="4" t="s">
-        <v>265</v>
-      </c>
       <c r="AB9" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="AC9" s="4" t="s">
-        <v>266</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="AC9" s="4"/>
     </row>
     <row r="10" spans="1:29" s="3" customFormat="1" ht="204">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3">
         <v>2019</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>3</v>
@@ -2506,7 +2371,7 @@
         <v>3</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="M10" s="5" t="s">
         <v>3</v>
@@ -2518,47 +2383,45 @@
         <v>3</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>47</v>
+        <v>261</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Y10" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Z10" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AA10" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AB10" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="AC10" s="4" t="s">
-        <v>268</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="AC10" s="4"/>
     </row>
     <row r="11" spans="1:29" ht="238">
       <c r="A11" s="3">
@@ -2571,19 +2434,19 @@
         <v>2021</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>3</v>
@@ -2592,7 +2455,7 @@
         <v>3</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>3</v>
@@ -2601,78 +2464,76 @@
         <v>3</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>49</v>
+        <v>262</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="W11" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Y11" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="Z11" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="AA11" s="19">
+        <v>96</v>
+      </c>
+      <c r="AA11" s="18">
         <v>0.83299999999999996</v>
       </c>
       <c r="AB11" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="AC11" s="4" t="s">
-        <v>269</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="AC11" s="4"/>
     </row>
     <row r="12" spans="1:29" ht="187">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C12">
         <v>2023</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="G12" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>3</v>
@@ -2699,69 +2560,67 @@
         <v>3</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Y12" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Z12" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AA12" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AB12" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="AC12" s="4" t="s">
-        <v>270</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="AC12" s="4"/>
     </row>
     <row r="13" spans="1:29" ht="221">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C13">
         <v>2023</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="G13" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>3</v>
@@ -2770,7 +2629,7 @@
         <v>3</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>3</v>
@@ -2779,78 +2638,76 @@
         <v>3</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>3</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="U13" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="V13" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="W13" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="X13" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y13" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z13" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA13" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="AB13" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="V13" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="W13" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="X13" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="Y13" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z13" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="AA13" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="AB13" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="AC13" s="5" t="s">
-        <v>271</v>
-      </c>
+      <c r="AC13" s="5"/>
     </row>
     <row r="14" spans="1:29" ht="170">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C14">
         <v>2024</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="G14" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>3</v>
@@ -2859,87 +2716,85 @@
         <v>3</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="P14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>298</v>
+        <v>249</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>57</v>
+        <v>265</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="Y14" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Z14" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AA14" s="4" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="AB14" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="AC14" s="4" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" ht="204">
+        <v>239</v>
+      </c>
+      <c r="AC14" s="4"/>
+    </row>
+    <row r="15" spans="1:29" ht="187">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C15">
         <v>2026</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="G15" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>3</v>
@@ -2954,81 +2809,79 @@
         <v>3</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>114</v>
+        <v>3</v>
       </c>
       <c r="N15" s="5" t="s">
         <v>3</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="P15" s="5" t="s">
         <v>3</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>60</v>
+        <v>266</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Z15" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="AA15" s="20">
+        <v>96</v>
+      </c>
+      <c r="AA15" s="19">
         <v>0.873</v>
       </c>
       <c r="AB15" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC15" s="4" t="s">
-        <v>278</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="AC15" s="4"/>
     </row>
     <row r="16" spans="1:29" ht="204">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C16">
         <v>2026</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="G16" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>3</v>
@@ -3037,10 +2890,10 @@
         <v>3</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>3</v>
@@ -3055,69 +2908,67 @@
         <v>3</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>301</v>
+        <v>252</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>62</v>
+        <v>267</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="V16" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="W16" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="AA16" s="19">
+        <v>217</v>
+      </c>
+      <c r="AA16" s="18">
         <v>0.84399999999999997</v>
       </c>
       <c r="AB16" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="AC16" s="4" t="s">
-        <v>279</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="AC16" s="4"/>
     </row>
     <row r="17" spans="1:29" ht="170">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C17">
         <v>2025</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="G17" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="I17" s="9" t="s">
         <v>3</v>
@@ -3126,7 +2977,7 @@
         <v>3</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="L17" s="9" t="s">
         <v>3</v>
@@ -3141,72 +2992,70 @@
         <v>3</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="R17" s="9" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>65</v>
+        <v>268</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>280</v>
+        <v>242</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="V17" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="W17" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Z17" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AA17" s="4" t="s">
-        <v>281</v>
+        <v>243</v>
       </c>
       <c r="AB17" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="AC17" s="4" t="s">
-        <v>282</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="AC17" s="4"/>
     </row>
     <row r="18" spans="1:29" ht="170">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C18">
         <v>2025</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="G18" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>3</v>
@@ -3215,7 +3064,7 @@
         <v>3</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="L18" s="4" t="s">
         <v>3</v>
@@ -3224,78 +3073,76 @@
         <v>3</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>236</v>
+        <v>3</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>68</v>
+        <v>269</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="U18" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="V18" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="W18" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="X18" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Y18" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Z18" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="AA18" s="4" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="AB18" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="AC18" s="4" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29" ht="153">
+        <v>150</v>
+      </c>
+      <c r="AC18" s="4"/>
+    </row>
+    <row r="19" spans="1:29" ht="119">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C19">
         <v>2026</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="G19" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>3</v>
@@ -3304,93 +3151,91 @@
         <v>3</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="L19" s="4" t="s">
         <v>3</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>71</v>
+        <v>270</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="U19" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="V19" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="W19" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="X19" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Y19" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Z19" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AA19" s="4" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="AB19" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="AC19" s="4" t="s">
-        <v>284</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="AC19" s="4"/>
     </row>
     <row r="20" spans="1:29" ht="204">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C20">
         <v>2025</v>
       </c>
-      <c r="D20" s="16" t="s">
-        <v>41</v>
+      <c r="D20" s="15" t="s">
+        <v>38</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="G20" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>3</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>3</v>
@@ -3405,81 +3250,79 @@
         <v>3</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>73</v>
+        <v>271</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="V20" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="W20" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Y20" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Z20" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AA20" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AB20" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="AC20" s="4" t="s">
-        <v>285</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="AC20" s="4"/>
     </row>
     <row r="21" spans="1:29" ht="170">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="C21">
         <v>2026</v>
       </c>
-      <c r="D21" s="15" t="s">
-        <v>42</v>
+      <c r="D21" s="14" t="s">
+        <v>39</v>
       </c>
       <c r="E21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="G21" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>3</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>3</v>
@@ -3494,75 +3337,73 @@
         <v>3</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>77</v>
+        <v>272</v>
       </c>
       <c r="T21" s="4" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="U21" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="V21" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="W21" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="X21" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Y21" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Z21" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AA21" s="4" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="AB21" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="AC21" s="4" t="s">
-        <v>286</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="AC21" s="4"/>
     </row>
     <row r="22" spans="1:29" s="3" customFormat="1" ht="204">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C22" s="3">
         <v>2022</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>3</v>
@@ -3571,87 +3412,85 @@
         <v>3</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="M22" s="5" t="s">
         <v>3</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="P22" s="5" t="s">
         <v>3</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="V22" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="W22" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="Y22" s="4" t="s">
-        <v>238</v>
+        <v>96</v>
       </c>
       <c r="Z22" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AA22" s="4" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="AB22" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="AC22" s="4" t="s">
-        <v>287</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="AC22" s="4"/>
     </row>
     <row r="23" spans="1:29" ht="221">
       <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C23" s="3">
         <v>2024</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>3</v>
@@ -3672,253 +3511,247 @@
         <v>3</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="P23" s="5" t="s">
         <v>3</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="R23" s="5" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>86</v>
+        <v>274</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="U23" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="V23" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="W23" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="X23" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Y23" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Z23" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AA23" s="4" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="AB23" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="AC23" s="4" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29" ht="221">
+        <v>248</v>
+      </c>
+      <c r="AC23" s="4"/>
+    </row>
+    <row r="24" spans="1:29" s="3" customFormat="1" ht="222">
       <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C24" s="3">
         <v>2021</v>
       </c>
-      <c r="D24" s="12" t="s">
-        <v>87</v>
+      <c r="D24" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="L24" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="N24" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="O24" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="P24" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="O24" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="P24" s="22" t="s">
         <v>3</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="R24" s="11" t="s">
-        <v>182</v>
+        <v>213</v>
+      </c>
+      <c r="R24" s="23" t="s">
+        <v>164</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>218</v>
+        <v>275</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="W24" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="X24" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Y24" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Z24" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AA24" s="4" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="AB24" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="AC24" s="4" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29" s="3" customFormat="1" ht="221">
+        <v>200</v>
+      </c>
+      <c r="AC24" s="4"/>
+    </row>
+    <row r="25" spans="1:29" s="3" customFormat="1" ht="187">
       <c r="A25" s="3">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="C25" s="3">
         <v>2022</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="E25" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q25" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="H25" s="4" t="s">
+      <c r="R25" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="I25" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="M25" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="N25" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="O25" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="P25" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q25" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="S25" s="4" t="s">
-        <v>213</v>
+        <v>276</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>291</v>
+        <v>245</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="V25" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="W25" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="X25" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Y25" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Z25" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="AA25" s="5" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="AB25" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC25" s="4" t="s">
-        <v>292</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="AC25" s="4"/>
     </row>
     <row r="26" spans="1:29" s="3" customFormat="1" ht="272">
       <c r="A26" s="3">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C26" s="3">
         <v>2024</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>3</v>
@@ -3936,57 +3769,55 @@
         <v>3</v>
       </c>
       <c r="N26" s="5" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="O26" s="5" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="P26" s="5" t="s">
         <v>3</v>
       </c>
       <c r="Q26" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="R26" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="S26" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="T26" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="R26" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="S26" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="T26" s="2" t="s">
-        <v>253</v>
-      </c>
       <c r="U26" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="V26" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="W26" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="X26" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Y26" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="Z26" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AA26" s="5" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="AB26" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="AC26" s="4" t="s">
-        <v>293</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="AC26" s="4"/>
     </row>
     <row r="27" spans="1:29">
       <c r="A27" s="3"/>
-      <c r="D27" s="18"/>
+      <c r="D27" s="17"/>
       <c r="Q27"/>
     </row>
     <row r="28" spans="1:29">
@@ -3994,19 +3825,19 @@
     </row>
     <row r="29" spans="1:29" ht="18">
       <c r="D29" s="8"/>
-      <c r="Q29" s="22"/>
+      <c r="Q29" s="20"/>
     </row>
     <row r="30" spans="1:29" ht="18">
       <c r="D30" s="8"/>
-      <c r="Q30" s="22"/>
+      <c r="Q30" s="20"/>
     </row>
     <row r="31" spans="1:29" ht="18">
       <c r="D31" s="8"/>
-      <c r="Q31" s="22"/>
+      <c r="Q31" s="20"/>
     </row>
     <row r="32" spans="1:29" ht="18">
       <c r="D32" s="8"/>
-      <c r="Q32" s="22"/>
+      <c r="Q32" s="20"/>
     </row>
     <row r="33" spans="3:4">
       <c r="D33" s="8"/>
@@ -4017,7 +3848,7 @@
     </row>
     <row r="35" spans="3:4">
       <c r="C35" s="1"/>
-      <c r="D35" s="23"/>
+      <c r="D35" s="21"/>
     </row>
     <row r="36" spans="3:4">
       <c r="C36" s="1"/>
@@ -4025,15 +3856,15 @@
     </row>
     <row r="37" spans="3:4">
       <c r="C37" s="1"/>
-      <c r="D37" s="23"/>
+      <c r="D37" s="21"/>
     </row>
     <row r="38" spans="3:4">
       <c r="C38" s="1"/>
-      <c r="D38" s="23"/>
+      <c r="D38" s="21"/>
     </row>
     <row r="39" spans="3:4">
       <c r="C39" s="1"/>
-      <c r="D39" s="23"/>
+      <c r="D39" s="21"/>
     </row>
     <row r="40" spans="3:4">
       <c r="D40" s="8"/>

--- a/data/Evidence_Table.xlsx
+++ b/data/Evidence_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramanaye/Documents/GitHub/cancer_nutrition_evidence_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F005E70-7391-A64A-BAF2-36BF82EFB25B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C99C443-794A-AF4F-9E1E-D47D77FB7CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="14720" windowHeight="16120" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
   </bookViews>
   <sheets>
     <sheet name="Evidence Table" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="252">
   <si>
     <t>Year</t>
   </si>
@@ -311,9 +311,6 @@
 2. Nutrition - Dietary habits assessment by a dietitian plus whey protein supplementation to ensure a daily protein intake of 1.2 to 1.5 g/kg of ideal body weight</t>
   </si>
   <si>
-    <t>Frail and high-risk patients (ASA classes 4 and 5) were excluded from the trial</t>
-  </si>
-  <si>
     <t>Study Design</t>
   </si>
   <si>
@@ -321,9 +318,6 @@
   </si>
   <si>
     <t>Adherence/Compliance</t>
-  </si>
-  <si>
-    <t>Limitations</t>
   </si>
   <si>
     <t>Sample size (dropouts)</t>
@@ -334,9 +328,6 @@
   </si>
   <si>
     <t>Control group - received standardized perioperative care  instead of the structured prehabilitation program</t>
-  </si>
-  <si>
-    <t>63% with the prehabilitation program</t>
   </si>
   <si>
     <t>Duration of Intervention</t>
@@ -359,30 +350,6 @@
 &gt;70% for both groups in postoperative phase</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Unexpectedly, the REHAB (control) group also improved their walking capacity during the preoperative period, even though they were not prescribed exercise. The researchers suggest this could be due to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>behavioral bias</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, where patients became more active on their own or sought outside help because they knew they were participating in an exercise study</t>
-    </r>
-  </si>
-  <si>
     <t>Prehab-60 (5)
 Rehab - 60 (5)</t>
   </si>
@@ -399,9 +366,6 @@
     <t>Prehab group: 68% for hospital sessions, 80% overall self-reported. Rehab group: 14% for hospital sessions, 30% overall self-reported</t>
   </si>
   <si>
-    <t>High rate of missing data  because many patients failed to attend their follow-up appointments - at the four-week postoperative visit, attendance was only 70.9% in the prehabilitation group and 56.4% in the rehabilitation group. While the researchers used multiple imputation to handle these gaps, the high volume of missing data remains a methodological concern</t>
-  </si>
-  <si>
     <t>4-week trimodal program: 
 1. Exercise- Home-based aerobic (walking/jogging) and breathing exercises with weekly supervised sessions 
 2. Nutrition- Individualised nutritional support with oral nutritional supplements based on ESPEN guidelines as necessary
@@ -425,14 +389,6 @@
     <t>Control group- received standard hospital care</t>
   </si>
   <si>
-    <t xml:space="preserve">Nutritional component -93.2%
-Exercises- 88.2% (home-based) and 84.1% (supervised)
-</t>
-  </si>
-  <si>
-    <t>The study's open-label design and retrospective registration increased risks of performance, detection, and outcome reporting bias. Furthermore, the COVID-19 pandemic caused significant missing data and a 38.2% dropout rate for preoperative assessments, necessitating the use of statistical imputations</t>
-  </si>
-  <si>
     <t>Multimodal Prehabilitation During Neoadjuvant Therapy Prior to Esophagogastric Cancer Resection: Effect on Cardiopulmonary Exercise Test Performance, Muscle Mass and Quality of Life—A Pilot Randomized Clinical Trial</t>
   </si>
   <si>
@@ -462,9 +418,6 @@
 Not reported for other components</t>
   </si>
   <si>
-    <t>Early termination and open-label design</t>
-  </si>
-  <si>
     <t>Prehabilitation – 64 (5)
 Control– 64 (5)</t>
   </si>
@@ -472,9 +425,6 @@
     <t>Control group- received standard preoperative care</t>
   </si>
   <si>
-    <t>Low (43%) participation rate, a lack of participant blinding, and the absence of objective tools to monitor intervention adherence</t>
-  </si>
-  <si>
     <t>Prehabilitation – 43 (6) 
 Control – 42 (6)</t>
   </si>
@@ -482,9 +432,6 @@
     <t>2 weeks</t>
   </si>
   <si>
-    <t>The study featured a relatively small sample size from a single center, potentially limiting generalizability. Additionally, the follow-up period was limited to 30 days, leaving long-term recovery effects unknown</t>
-  </si>
-  <si>
     <t>Control group-  received usual clinical care</t>
   </si>
   <si>
@@ -495,9 +442,6 @@
     <t>control group -received standard care which consisted of nutritional counseling, physical activity recommendations, and advice on smoking cessation</t>
   </si>
   <si>
-    <t>The study was underpowered due to a small sample size and a potential bias from the control group receiving "partial prehabilitation" through standard preoperative advice</t>
-  </si>
-  <si>
     <t>Prehabilitation – 35 (16) 
 Control – 35 (14)</t>
   </si>
@@ -511,9 +455,6 @@
     <t xml:space="preserve">12.6 days </t>
   </si>
   <si>
-    <t>The study had a significant loss to follow-up at post-surgical assessment points, primarily due to logistic challenges like the long distance between patients' homes and the hospital,. These factors hinder the generalizability of the results</t>
-  </si>
-  <si>
     <t>Prehabilitation – 30 (7) 
 Control – 30 (9)</t>
   </si>
@@ -521,9 +462,6 @@
     <t>Standard care group- received no specific education or recommendations regarding physical activity, nutrition, or relaxation beyond the standard ERAS protocols</t>
   </si>
   <si>
-    <t>The study is primarily limited by its small sample size as a pilot study and a high loss to follow-up rate (over 25%) largely driven by the COVID-19 pandemic</t>
-  </si>
-  <si>
     <t>Prehabilitation – 19 (3) 
 Control– 21 (1)</t>
   </si>
@@ -558,17 +496,11 @@
     <t>1 week</t>
   </si>
   <si>
-    <t xml:space="preserve"> Single-center design and short follow-up period that lacks long-term survival data</t>
-  </si>
-  <si>
     <t>Prehabilitation – 45 (2) 
 Control – 45 (3)</t>
   </si>
   <si>
     <t>Control group -received standard care, following hospital's  ERAS  protocol</t>
-  </si>
-  <si>
-    <t>The study relied on self-reported logs rather than wearable device data and had a small sample size. It also lacked detailed daily nutritional intake data and was conducted at a single center, which may limit the generalizability of the findings</t>
   </si>
   <si>
     <t xml:space="preserve">Control group received one initial session of exercise instruction from a physical therapist, but no specific exercise routine was set, did not receive additional instructions, feedback, or oral nutritional supplements </t>
@@ -592,12 +524,6 @@
     <t>76% for the exercise program, 62% for walking steps, 160% for handgrip training, and 45% for nutritional supplementation.</t>
   </si>
   <si>
-    <t>Small-scale, single-center, open-label trial, which may limit generalizability and introduce participant bias. Exercise therapy and non-supplement dietary intake were largely unsupervised and left to the patients' own motivation</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Single-center design, small sample size, and low compliance with nutritional supplements. Also, it lacked long-term evaluation of oncological outcomes and physical performance</t>
-  </si>
-  <si>
     <t>Prehabilitation – 54 (5)
  Control – 56 (4)</t>
   </si>
@@ -608,9 +534,6 @@
     <t>76% for walking, 77% for resistance training, and 73% for HMB supplementation</t>
   </si>
   <si>
-    <t>The study was a single-center trial with a small sample size not powered to detect differences in postoperative clinical outcomes. Its open-label design and reliance on patient-reported diaries for adherence may have also introduced bias</t>
-  </si>
-  <si>
     <t>Prehabilitation – 52 (10) 
 Control – 52 (6)</t>
   </si>
@@ -618,9 +541,6 @@
     <t>Control group received standard preoperative care, which included dietary guidance, advice on maintaining warmth, and precautions to prevent respiratory infections</t>
   </si>
   <si>
-    <t>study was limited by its single-center design and lack of blinding, It excluded structured resistance training and relied on the 6-minute walk test rather than more sensitive cardiorespiratory fitness measures</t>
-  </si>
-  <si>
     <t>Prehabilitation – 100 (0)
  Control – 100 (0)</t>
   </si>
@@ -632,9 +552,6 @@
   </si>
   <si>
     <t>100% for inspiratory muscle training, 98.5% for aerobic exercise, 96% for prescribed nutritional supplements, and 94% for psychological-related activities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Study's short intervention duration (7 days) and single-center design may limit the generalizability and full physiological impact of the findings. </t>
   </si>
   <si>
     <t>36  days</t>
@@ -726,9 +643,6 @@
     <t>High, with 85% of participants completing 3 weekly aerobic sessions, 83% performing at least 2 resistance sessions, 92% adherence to respiratory training, and 100% adherence to protein supplementation</t>
   </si>
   <si>
-    <t>The single-center design and small sample size may limit generalizability and increase the risk of false-positive or false-negative results. Findings may be limited to centers with well-established ERAS protocols and a high prevalence of minimally invasive surgery</t>
-  </si>
-  <si>
     <t>Allen et al.</t>
   </si>
   <si>
@@ -744,9 +658,6 @@
     <t>supervised exercise - 76 ± 14%, 
 home exercise - 65 ± 27%
 medical coaching adherence - 82 ± 20%</t>
-  </si>
-  <si>
-    <t>Small sample size and single-center design limit generalizability. The study was powered for physiological (AT) rather than clinical outcomes. There was variability in the neoadjuvant chemotherapy regimens prescribed to participant</t>
   </si>
   <si>
     <t>Prehabilitation – 52 (14) 
@@ -763,9 +674,6 @@
     <t>Pre-op PREHAB: Exercise - 84.9 ± 25.3%, Nutrition - 89.5 ± 23.5%</t>
   </si>
   <si>
-    <t>Significant loss to follow-up and missing data, which reached 48% at eight weeks post-operation, limit the generalizability and power of the results. The study was not powered for clinical postoperative outcomes and faced potential performance bias, as control participants may have increased activity levels before surgery</t>
-  </si>
-  <si>
     <t>Prehabilitation – 11 (0) 
 Control – 11 (0)</t>
   </si>
@@ -791,11 +699,6 @@
     <t>7-9 weeks</t>
   </si>
   <si>
-    <t>83.8% for physical training
- 92.6% for nutritional support
-92% for psychological counseling</t>
-  </si>
-  <si>
     <t>3 weeks</t>
   </si>
   <si>
@@ -870,35 +773,7 @@
     <t>Randomized Controlled Feasibility Trial</t>
   </si>
   <si>
-    <t>The study had a small sample size with a risk of Type 2 error and lacked complete participant blinding.
-The nutritional intervention window was short (2–3 weeks), and there was poor compliance with the psychological component</t>
-  </si>
-  <si>
     <t>Author</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The study was primarily powered for functional outcomes, making it potentially </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>underpowered</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to detect significant differences in secondary clinical endpoints like morbidity or mortality. ~19% dropout/exclusion rate and missed follow-up visits introduce attrition bias</t>
-    </r>
   </si>
   <si>
     <t>Functional capacity
@@ -908,12 +783,6 @@
     <t>Good (specific % not reported)</t>
   </si>
   <si>
-    <t>Small sample size. Since the primary outcome (QoR-15) is a self-reported questionnaire, the knowledge of group assignment could have introduced  bias, potentially inflating the scores in the intervention group.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Because the qualitative component was introduced after the study began, most interviewed participants had experienced their prehabilitation during the peak of the COVID-19 pandemic, which may have influenced their feedback. Outcome assessors in this study were not blinded to group allotment causing detection bias. </t>
-  </si>
-  <si>
     <t>Micronutrients supplementation</t>
   </si>
   <si>
@@ -939,9 +808,6 @@
     <t>Complete Oral Nutritional Supplement</t>
   </si>
   <si>
-    <t>The study faced selection bias from excluding unwilling participants and variability in chemotherapy regimens which may affect generalizability. Additionally, the short follow-up period meant long-term outcomes like progression-free and overall survival were not assessed. The use of quasi-randomization (odd-even method) place the study at a high risk for bias despite the blinding of outcome assessors</t>
-  </si>
-  <si>
     <t>For the duration of NACT</t>
   </si>
   <si>
@@ -1024,6 +890,21 @@
   </si>
   <si>
     <t>No significant difference was observed in the primary outcome of anaerobic threshold (AT) between groups. However, the prehabilitation group showed a significantly attenuated decline in peak VO2 compared to controls  p = 0.022), indicating better preservation of cardiopulmonary fitness.  Prehabilitation also resulted in significantly less skeletal muscle loss (-11.6 vs. -15.6 cm2/m2; p = 0.049) and improved retention of hand-grip strength postoperatively (p = 0.009). Quality of life (global health status) and psychological markers (anxiety and depression) were significantly better in the intervention group at multiple time points. Notably, more prehabilitation patients completed their full dose of neoadjuvant therapy (75% vs. 46%; p = 0.036). There were no significant differences in postoperative complications, length of stay, or 3-year mortality.</t>
+  </si>
+  <si>
+    <t>2021a</t>
+  </si>
+  <si>
+    <t>2021b</t>
+  </si>
+  <si>
+    <t>Nutrition -93.2%
+Exercises- 88.2% (home-based) and 84.1% (supervised)</t>
+  </si>
+  <si>
+    <t>83.8% for physical training
+92.6% for nutritional support
+92% for psychological counseling</t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1021,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1181,16 +1062,21 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1558,7 +1444,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1567,77 +1453,75 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>247</v>
+        <v>219</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>253</v>
+        <v>224</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>77</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
     </row>
     <row r="2" spans="1:29" ht="153">
@@ -1657,10 +1541,10 @@
         <v>8</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>72</v>
@@ -1672,7 +1556,7 @@
         <v>3</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>3</v>
@@ -1681,50 +1565,48 @@
         <v>3</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>254</v>
+        <v>225</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>73</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="AA2" s="22">
+        <v>0.63</v>
+      </c>
+      <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
     </row>
     <row r="3" spans="1:29" ht="255">
@@ -1744,74 +1626,72 @@
         <v>22</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="H3" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA3" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA3" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB3" s="4" t="s">
-        <v>87</v>
-      </c>
+      <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
     </row>
     <row r="4" spans="1:29" ht="221">
@@ -1831,13 +1711,13 @@
         <v>8</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G4" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>3</v>
@@ -1846,7 +1726,7 @@
         <v>3</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>3</v>
@@ -1855,53 +1735,51 @@
         <v>3</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="P4" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="T4" s="6" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="U4" s="6" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="V4" s="6" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="W4" s="6" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="X4" s="6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Y4" s="6" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="Z4" s="6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AA4" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AB4" s="6" t="s">
-        <v>92</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="AB4" s="6"/>
       <c r="AC4" s="6"/>
     </row>
-    <row r="5" spans="1:29" s="5" customFormat="1" ht="153">
+    <row r="5" spans="1:29" s="5" customFormat="1" ht="136">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1918,25 +1796,25 @@
         <v>8</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>3</v>
@@ -1945,47 +1823,45 @@
         <v>3</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="P5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>257</v>
+        <v>228</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB5" s="4" t="s">
-        <v>235</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
     </row>
     <row r="6" spans="1:29" s="3" customFormat="1" ht="204">
@@ -1995,20 +1871,20 @@
       <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="3">
-        <v>2021</v>
+      <c r="C6" s="3" t="s">
+        <v>248</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>17</v>
@@ -2020,7 +1896,7 @@
         <v>3</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>3</v>
@@ -2029,7 +1905,7 @@
         <v>3</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="O6" s="4" t="s">
         <v>3</v>
@@ -2038,44 +1914,42 @@
         <v>3</v>
       </c>
       <c r="Q6" s="16" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>258</v>
+        <v>229</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="Z6" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AA6" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="AB6" s="4" t="s">
-        <v>100</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
     </row>
-    <row r="7" spans="1:29" ht="170">
+    <row r="7" spans="1:29" ht="153">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2092,10 +1966,10 @@
         <v>8</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>20</v>
@@ -2107,7 +1981,7 @@
         <v>3</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>3</v>
@@ -2116,7 +1990,7 @@
         <v>3</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="O7" s="9" t="s">
         <v>3</v>
@@ -2125,41 +1999,39 @@
         <v>3</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="R7" s="9" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="S7" s="8" t="s">
         <v>21</v>
       </c>
       <c r="T7" s="8" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="U7" s="8" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="V7" s="8" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="W7" s="8" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="X7" s="8" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="Y7" s="8" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="Z7" s="8" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AA7" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB7" s="4" t="s">
-        <v>110</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
     </row>
     <row r="8" spans="1:29" s="3" customFormat="1" ht="187">
@@ -2179,10 +2051,10 @@
         <v>22</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>25</v>
@@ -2206,50 +2078,48 @@
         <v>3</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>251</v>
+        <v>222</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>260</v>
+        <v>231</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="AA8" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB8" s="4" t="s">
-        <v>113</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB8" s="4"/>
       <c r="AC8" s="4"/>
     </row>
-    <row r="9" spans="1:29" ht="204">
+    <row r="9" spans="1:29" ht="187">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2266,10 +2136,10 @@
         <v>22</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>40</v>
@@ -2290,50 +2160,48 @@
         <v>3</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="P9" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q9" s="16" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>259</v>
+        <v>230</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="Z9" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AA9" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="AB9" s="4" t="s">
-        <v>116</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
     </row>
     <row r="10" spans="1:29" s="3" customFormat="1" ht="204">
@@ -2353,10 +2221,10 @@
         <v>22</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>42</v>
@@ -2371,7 +2239,7 @@
         <v>3</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="M10" s="5" t="s">
         <v>3</v>
@@ -2383,47 +2251,45 @@
         <v>3</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>261</v>
+        <v>232</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Y10" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Z10" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AA10" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB10" s="4" t="s">
-        <v>120</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB10" s="4"/>
       <c r="AC10" s="4"/>
     </row>
-    <row r="11" spans="1:29" ht="238">
+    <row r="11" spans="1:29" ht="221">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2440,10 +2306,10 @@
         <v>22</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>43</v>
@@ -2455,7 +2321,7 @@
         <v>3</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>3</v>
@@ -2464,50 +2330,48 @@
         <v>3</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="W11" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Y11" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="Z11" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA11" s="18">
+        <v>91</v>
+      </c>
+      <c r="AA11" s="23">
         <v>0.83299999999999996</v>
       </c>
-      <c r="AB11" s="4" t="s">
-        <v>125</v>
-      </c>
+      <c r="AB11" s="4"/>
       <c r="AC11" s="4"/>
     </row>
     <row r="12" spans="1:29" ht="187">
@@ -2527,10 +2391,10 @@
         <v>22</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="G12" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>45</v>
@@ -2560,41 +2424,39 @@
         <v>3</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>263</v>
+        <v>234</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Y12" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Z12" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AA12" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB12" s="4" t="s">
-        <v>128</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
     </row>
     <row r="13" spans="1:29" ht="221">
@@ -2614,10 +2476,10 @@
         <v>22</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="G13" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>47</v>
@@ -2629,7 +2491,7 @@
         <v>3</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>3</v>
@@ -2638,50 +2500,48 @@
         <v>3</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>3</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="V13" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="X13" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="Y13" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Z13" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AA13" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="AB13" s="4" t="s">
-        <v>238</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="AB13" s="4"/>
       <c r="AC13" s="5"/>
     </row>
     <row r="14" spans="1:29" ht="170">
@@ -2701,10 +2561,10 @@
         <v>49</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="G14" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>50</v>
@@ -2716,59 +2576,57 @@
         <v>3</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>249</v>
+        <v>220</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>265</v>
+        <v>236</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="Y14" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="Z14" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AA14" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="AB14" s="4" t="s">
-        <v>239</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="AB14" s="4"/>
       <c r="AC14" s="4"/>
     </row>
     <row r="15" spans="1:29" ht="187">
@@ -2788,10 +2646,10 @@
         <v>22</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="G15" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>52</v>
@@ -2815,47 +2673,45 @@
         <v>3</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P15" s="5" t="s">
         <v>3</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>266</v>
+        <v>237</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="Z15" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA15" s="19">
+        <v>91</v>
+      </c>
+      <c r="AA15" s="24">
         <v>0.873</v>
       </c>
-      <c r="AB15" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="AB15" s="4"/>
       <c r="AC15" s="4"/>
     </row>
     <row r="16" spans="1:29" ht="204">
@@ -2875,10 +2731,10 @@
         <v>22</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G16" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>53</v>
@@ -2890,10 +2746,10 @@
         <v>3</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>3</v>
@@ -2908,41 +2764,39 @@
         <v>3</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>252</v>
+        <v>223</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>267</v>
+        <v>238</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="V16" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="W16" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA16" s="18">
+        <v>193</v>
+      </c>
+      <c r="AA16" s="23">
         <v>0.84399999999999997</v>
       </c>
-      <c r="AB16" s="4" t="s">
-        <v>142</v>
-      </c>
+      <c r="AB16" s="4"/>
       <c r="AC16" s="4"/>
     </row>
     <row r="17" spans="1:29" ht="170">
@@ -2962,10 +2816,10 @@
         <v>22</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="G17" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>55</v>
@@ -2977,7 +2831,7 @@
         <v>3</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="L17" s="9" t="s">
         <v>3</v>
@@ -2992,44 +2846,42 @@
         <v>3</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="R17" s="9" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>268</v>
+        <v>239</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="V17" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="W17" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Z17" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AA17" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="AB17" s="4" t="s">
-        <v>149</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="AB17" s="4"/>
       <c r="AC17" s="4"/>
     </row>
     <row r="18" spans="1:29" ht="170">
@@ -3049,10 +2901,10 @@
         <v>22</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="G18" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>57</v>
@@ -3064,7 +2916,7 @@
         <v>3</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="L18" s="4" t="s">
         <v>3</v>
@@ -3076,47 +2928,45 @@
         <v>3</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>269</v>
+        <v>240</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="U18" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="V18" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="W18" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="X18" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="Y18" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Z18" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="AA18" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="AB18" s="4" t="s">
-        <v>150</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
     </row>
     <row r="19" spans="1:29" ht="119">
@@ -3136,10 +2986,10 @@
         <v>22</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="G19" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>59</v>
@@ -3151,59 +3001,57 @@
         <v>3</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="L19" s="4" t="s">
         <v>3</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="U19" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="V19" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="W19" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="X19" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="Y19" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Z19" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AA19" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="AB19" s="4" t="s">
-        <v>154</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="AB19" s="4"/>
       <c r="AC19" s="4"/>
     </row>
     <row r="20" spans="1:29" ht="204">
@@ -3223,10 +3071,10 @@
         <v>22</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="G20" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>61</v>
@@ -3235,7 +3083,7 @@
         <v>3</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>3</v>
@@ -3250,47 +3098,45 @@
         <v>3</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="V20" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="W20" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Y20" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="Z20" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AA20" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB20" s="4" t="s">
-        <v>157</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB20" s="4"/>
       <c r="AC20" s="4"/>
     </row>
     <row r="21" spans="1:29" ht="170">
@@ -3310,10 +3156,10 @@
         <v>22</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="G21" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>63</v>
@@ -3322,7 +3168,7 @@
         <v>3</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>3</v>
@@ -3337,47 +3183,45 @@
         <v>3</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>272</v>
+        <v>243</v>
       </c>
       <c r="T21" s="4" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="U21" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="V21" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="W21" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="X21" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Y21" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Z21" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AA21" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="AB21" s="4" t="s">
-        <v>162</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="AB21" s="4"/>
       <c r="AC21" s="4"/>
     </row>
     <row r="22" spans="1:29" s="3" customFormat="1" ht="204">
@@ -3397,10 +3241,10 @@
         <v>66</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>67</v>
@@ -3412,59 +3256,57 @@
         <v>3</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="M22" s="5" t="s">
         <v>3</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="P22" s="5" t="s">
         <v>3</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>273</v>
+        <v>244</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="V22" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="W22" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="Y22" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Z22" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AA22" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="AB22" s="5" t="s">
-        <v>233</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="AB22" s="5"/>
       <c r="AC22" s="4"/>
     </row>
     <row r="23" spans="1:29" ht="221">
@@ -3481,13 +3323,13 @@
         <v>69</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>70</v>
@@ -3511,47 +3353,45 @@
         <v>3</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="P23" s="5" t="s">
         <v>3</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="R23" s="5" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="U23" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="V23" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="W23" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="X23" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="Y23" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Z23" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AA23" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="AB23" s="5" t="s">
-        <v>248</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="AB23" s="5"/>
       <c r="AC23" s="4"/>
     </row>
     <row r="24" spans="1:29" s="3" customFormat="1" ht="222">
@@ -3561,8 +3401,8 @@
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="3">
-        <v>2021</v>
+      <c r="C24" s="3" t="s">
+        <v>249</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>71</v>
@@ -3571,74 +3411,72 @@
         <v>22</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="22" t="s">
-        <v>216</v>
-      </c>
-      <c r="L24" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="N24" s="22" t="s">
-        <v>216</v>
-      </c>
-      <c r="O24" s="22" t="s">
-        <v>216</v>
-      </c>
-      <c r="P24" s="22" t="s">
+      <c r="J24" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="O24" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="P24" s="20" t="s">
         <v>3</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="R24" s="23" t="s">
-        <v>164</v>
+        <v>189</v>
+      </c>
+      <c r="R24" s="21" t="s">
+        <v>144</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="W24" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="X24" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Y24" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="Z24" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AA24" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="AB24" s="4" t="s">
-        <v>200</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="AB24" s="4"/>
       <c r="AC24" s="4"/>
     </row>
     <row r="25" spans="1:29" s="3" customFormat="1" ht="187">
@@ -3646,25 +3484,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="C25" s="3">
         <v>2022</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>3</v>
@@ -3673,59 +3511,57 @@
         <v>3</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="M25" s="4" t="s">
         <v>3</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="P25" s="4" t="s">
         <v>3</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>276</v>
+        <v>247</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="V25" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="W25" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="X25" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="Y25" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="Z25" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="AA25" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="AB25" s="4" t="s">
-        <v>196</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="AB25" s="4"/>
       <c r="AC25" s="4"/>
     </row>
     <row r="26" spans="1:29" s="3" customFormat="1" ht="272">
@@ -3733,25 +3569,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C26" s="3">
         <v>2024</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>3</v>
@@ -3769,50 +3605,48 @@
         <v>3</v>
       </c>
       <c r="N26" s="5" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="O26" s="5" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="P26" s="5" t="s">
         <v>3</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="R26" s="5" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="S26" s="4" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="U26" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="V26" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="W26" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="X26" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="Y26" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="Z26" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AA26" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="AB26" s="4" t="s">
-        <v>191</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="AB26" s="4"/>
       <c r="AC26" s="4"/>
     </row>
     <row r="27" spans="1:29">
@@ -3825,19 +3659,19 @@
     </row>
     <row r="29" spans="1:29" ht="18">
       <c r="D29" s="8"/>
-      <c r="Q29" s="20"/>
+      <c r="Q29" s="18"/>
     </row>
     <row r="30" spans="1:29" ht="18">
       <c r="D30" s="8"/>
-      <c r="Q30" s="20"/>
+      <c r="Q30" s="18"/>
     </row>
     <row r="31" spans="1:29" ht="18">
       <c r="D31" s="8"/>
-      <c r="Q31" s="20"/>
+      <c r="Q31" s="18"/>
     </row>
     <row r="32" spans="1:29" ht="18">
       <c r="D32" s="8"/>
-      <c r="Q32" s="20"/>
+      <c r="Q32" s="18"/>
     </row>
     <row r="33" spans="3:4">
       <c r="D33" s="8"/>
@@ -3848,7 +3682,7 @@
     </row>
     <row r="35" spans="3:4">
       <c r="C35" s="1"/>
-      <c r="D35" s="21"/>
+      <c r="D35" s="19"/>
     </row>
     <row r="36" spans="3:4">
       <c r="C36" s="1"/>
@@ -3856,15 +3690,15 @@
     </row>
     <row r="37" spans="3:4">
       <c r="C37" s="1"/>
-      <c r="D37" s="21"/>
+      <c r="D37" s="19"/>
     </row>
     <row r="38" spans="3:4">
       <c r="C38" s="1"/>
-      <c r="D38" s="21"/>
+      <c r="D38" s="19"/>
     </row>
     <row r="39" spans="3:4">
       <c r="C39" s="1"/>
-      <c r="D39" s="21"/>
+      <c r="D39" s="19"/>
     </row>
     <row r="40" spans="3:4">
       <c r="D40" s="8"/>

--- a/data/Evidence_Table.xlsx
+++ b/data/Evidence_Table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramanaye/Documents/GitHub/cancer_nutrition_evidence_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C99C443-794A-AF4F-9E1E-D47D77FB7CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21E85D6-0482-E342-828A-37377D77106F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
   </bookViews>

--- a/data/Evidence_Table.xlsx
+++ b/data/Evidence_Table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramanaye/Documents/GitHub/cancer_nutrition_evidence_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21E85D6-0482-E342-828A-37377D77106F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FAA694-0EDC-A544-AAAC-9BAFD87591F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="242">
   <si>
     <t>Year</t>
   </si>
@@ -291,18 +291,6 @@
 3. Psychology - Daily guided meditation using a mindfulness app for stress management and relaxation techniques</t>
   </si>
   <si>
-    <t>Li et al.</t>
-  </si>
-  <si>
-    <t>Clinical Study of Preoperative Prehabilitation Synchronized Neoadjuvant Chemotherapy for Gastric Cancer Patients</t>
-  </si>
-  <si>
-    <t>Trimodal program synchronized with neoadjuvant chemotherapy (NAC) for 7–9 weeks:
-1. Exercise - Individualized home-based training 4 times/week including aerobic exercise (brisk walking/jogging/cycling 3 days/week), strengthening exercises (elastic bands 1 day/week), and respiratory training (abdominal breathing and deep inspiration).
-2. Nutritional support - Daily whey protein (1.2–1.5 g/kg ideal body weight) + oral nutritional supplementation (400–900 kcal/d) + dietitian supervision via weekly calls.
-3. Psychology - Success stories to boost confidence + counseling, meditation, and cognitive-behavioral training for those with anxiety or depression</t>
-  </si>
-  <si>
     <t>Multimodal Prehabilitation for Lung Cancer Surgery: A Randomized Controlled Trial</t>
   </si>
   <si>
@@ -689,16 +677,6 @@
     <t>30.5 days</t>
   </si>
   <si>
-    <t>Prehabilitation – 68 (6) 
-Control– 68 (10)</t>
-  </si>
-  <si>
-    <t>control group - intervention included routine preoperative preparation, such as smoking and alcohol cessation advice and pulmonary function exercises, but they received no additional structured exercise or nutritional interventions</t>
-  </si>
-  <si>
-    <t>7-9 weeks</t>
-  </si>
-  <si>
     <t>3 weeks</t>
   </si>
   <si>
@@ -717,9 +695,6 @@
     <t>Primary Outcome</t>
   </si>
   <si>
-    <t>Randomized Clinical Trial (quasi-randomisation)</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -757,10 +732,6 @@
   </si>
   <si>
     <t xml:space="preserve">No </t>
-  </si>
-  <si>
-    <t>Functional capacity
-Nutritional status</t>
   </si>
   <si>
     <t>30-day postoperative Comprehensive Complication Index (CCI)</t>
@@ -883,9 +854,6 @@
     <t xml:space="preserve">Significantly greater improvement in functional capacity with a +85.6m 6-MWT gain (p = 0.014) compared to +13.2m in controls. Intervention group engaged in significantly more vigorous physical activity (36.1 min vs 17.5 min, p = 0.022). No significant changes were observed in body weight and HADS score. </t>
   </si>
   <si>
-    <t>Significant improvement in functional capacity (6MWD: +39.2m pre-op and +75.4m post-op) compared to control. Enhanced nutritional status with higher serum albumin and prealbumin levels and reduced need for postoperative albumin supplementation. Lower incidence of major pulmonary infections (6/66 vs 16/65 in control) and significantly shorter postoperative hospital (10.74 vs 13.24 days, P=0.003) and ICU stays. No significant difference in abdominal complications.</t>
-  </si>
-  <si>
     <t>No significant difference was observed in the primary outcome of functional capacity (6MWT) between groups at any time point. Both groups returned to baseline functional capacity by 8 weeks postoperatively. The PREHAB group showed significantly better health-related quality of life (SF-36) at 4 weeks postoperatively in Physical Summary (p = 0.006), General Health (p = 0.007), and Mental Health (p = 0.044) scores. Median length of stay was similar (4 days in both groups), however, significantly more patients in the prehabilitation group were discharged by postoperative day 2 (42% vs 16%). There were no significant differences in 30-day emergency visits, readmissions, or postoperative complications.</t>
   </si>
   <si>
@@ -900,11 +868,6 @@
   <si>
     <t>Nutrition -93.2%
 Exercises- 88.2% (home-based) and 84.1% (supervised)</t>
-  </si>
-  <si>
-    <t>83.8% for physical training
-92.6% for nutritional support
-92% for psychological counseling</t>
   </si>
 </sst>
 </file>
@@ -1411,7 +1374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E6C0315-B915-B14D-AC51-9D3C9D78CEB9}">
-  <dimension ref="A1:AC45"/>
+  <dimension ref="A1:AC44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.5" style="3" customWidth="1"/>
@@ -1444,7 +1407,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1453,73 +1416,73 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
@@ -1541,13 +1504,13 @@
         <v>8</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>3</v>
@@ -1556,7 +1519,7 @@
         <v>3</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>3</v>
@@ -1565,43 +1528,43 @@
         <v>3</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="AA2" s="22">
         <v>0.63</v>
@@ -1626,70 +1589,70 @@
         <v>22</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H3" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA3" s="9" t="s">
         <v>80</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA3" s="9" t="s">
-        <v>83</v>
       </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
@@ -1711,70 +1674,70 @@
         <v>8</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" t="s">
+        <v>151</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="U4" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="W4" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="X4" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y4" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA4" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="G4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="R4" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="T4" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="U4" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="V4" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="W4" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="X4" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y4" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z4" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA4" s="4" t="s">
-        <v>87</v>
       </c>
       <c r="AB4" s="6"/>
       <c r="AC4" s="6"/>
@@ -1796,25 +1759,25 @@
         <v>8</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>3</v>
@@ -1823,43 +1786,43 @@
         <v>3</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="P5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
@@ -1872,19 +1835,19 @@
         <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>17</v>
@@ -1896,55 +1859,55 @@
         <v>3</v>
       </c>
       <c r="K6" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="T6" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="L6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q6" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="R6" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="S6" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="T6" s="4" t="s">
-        <v>199</v>
-      </c>
       <c r="U6" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="Z6" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AA6" s="4" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
@@ -1966,10 +1929,10 @@
         <v>8</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>20</v>
@@ -1981,7 +1944,7 @@
         <v>3</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>3</v>
@@ -1990,7 +1953,7 @@
         <v>3</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O7" s="9" t="s">
         <v>3</v>
@@ -1999,37 +1962,37 @@
         <v>3</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="R7" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="S7" s="8" t="s">
         <v>21</v>
       </c>
       <c r="T7" s="8" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="U7" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="V7" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="W7" s="8" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="X7" s="8" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="Y7" s="8" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="Z7" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AA7" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
@@ -2051,10 +2014,10 @@
         <v>22</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>25</v>
@@ -2078,43 +2041,43 @@
         <v>3</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="AA8" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AB8" s="4"/>
       <c r="AC8" s="4"/>
@@ -2136,10 +2099,10 @@
         <v>22</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>40</v>
@@ -2160,46 +2123,46 @@
         <v>3</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="P9" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q9" s="16" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="Z9" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AA9" s="4" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
@@ -2221,10 +2184,10 @@
         <v>22</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>42</v>
@@ -2239,7 +2202,7 @@
         <v>3</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M10" s="5" t="s">
         <v>3</v>
@@ -2251,40 +2214,40 @@
         <v>3</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Y10" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Z10" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AA10" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AB10" s="4"/>
       <c r="AC10" s="4"/>
@@ -2306,10 +2269,10 @@
         <v>22</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>43</v>
@@ -2321,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>3</v>
@@ -2330,43 +2293,43 @@
         <v>3</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="W11" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Y11" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="Z11" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AA11" s="23">
         <v>0.83299999999999996</v>
@@ -2391,10 +2354,10 @@
         <v>22</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G12" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>45</v>
@@ -2424,37 +2387,37 @@
         <v>3</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Y12" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Z12" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AA12" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
@@ -2476,10 +2439,10 @@
         <v>22</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G13" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>47</v>
@@ -2491,7 +2454,7 @@
         <v>3</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>3</v>
@@ -2500,46 +2463,46 @@
         <v>3</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>3</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="V13" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="X13" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Y13" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Z13" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AA13" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="AB13" s="4"/>
       <c r="AC13" s="5"/>
@@ -2561,10 +2524,10 @@
         <v>49</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G14" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>50</v>
@@ -2576,55 +2539,55 @@
         <v>3</v>
       </c>
       <c r="K14" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="S14" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="T14" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="L14" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="R14" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="S14" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="T14" s="4" t="s">
-        <v>199</v>
-      </c>
       <c r="U14" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="Y14" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Z14" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AA14" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="AB14" s="4"/>
       <c r="AC14" s="4"/>
@@ -2646,10 +2609,10 @@
         <v>22</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G15" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>52</v>
@@ -2673,40 +2636,40 @@
         <v>3</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="P15" s="5" t="s">
         <v>3</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Z15" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AA15" s="24">
         <v>0.873</v>
@@ -2731,10 +2694,10 @@
         <v>22</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G16" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>53</v>
@@ -2746,10 +2709,10 @@
         <v>3</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>3</v>
@@ -2764,34 +2727,34 @@
         <v>3</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="V16" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="W16" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="AA16" s="23">
         <v>0.84399999999999997</v>
@@ -2816,10 +2779,10 @@
         <v>22</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G17" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>55</v>
@@ -2831,7 +2794,7 @@
         <v>3</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="L17" s="9" t="s">
         <v>3</v>
@@ -2846,40 +2809,40 @@
         <v>3</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="R17" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="V17" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="W17" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Z17" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AA17" s="4" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="AB17" s="4"/>
       <c r="AC17" s="4"/>
@@ -2901,10 +2864,10 @@
         <v>22</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G18" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>57</v>
@@ -2916,7 +2879,7 @@
         <v>3</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="L18" s="4" t="s">
         <v>3</v>
@@ -2928,43 +2891,43 @@
         <v>3</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="U18" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="V18" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="W18" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="X18" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Y18" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Z18" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="AA18" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
@@ -2986,10 +2949,10 @@
         <v>22</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G19" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>59</v>
@@ -3001,55 +2964,55 @@
         <v>3</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="L19" s="4" t="s">
         <v>3</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="U19" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="V19" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="W19" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="X19" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Y19" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Z19" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AA19" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AB19" s="4"/>
       <c r="AC19" s="4"/>
@@ -3071,10 +3034,10 @@
         <v>22</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G20" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>61</v>
@@ -3083,7 +3046,7 @@
         <v>3</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>3</v>
@@ -3098,43 +3061,43 @@
         <v>3</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="V20" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="W20" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Y20" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Z20" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AA20" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AB20" s="4"/>
       <c r="AC20" s="4"/>
@@ -3156,10 +3119,10 @@
         <v>22</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G21" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>63</v>
@@ -3168,7 +3131,7 @@
         <v>3</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>3</v>
@@ -3183,43 +3146,43 @@
         <v>3</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="T21" s="4" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="U21" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="V21" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="W21" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="X21" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Y21" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Z21" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AA21" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AB21" s="4"/>
       <c r="AC21" s="4"/>
@@ -3241,10 +3204,10 @@
         <v>66</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>67</v>
@@ -3256,406 +3219,325 @@
         <v>3</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="M22" s="5" t="s">
         <v>3</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="P22" s="5" t="s">
         <v>3</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="V22" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="W22" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="Y22" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Z22" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AA22" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AB22" s="5"/>
       <c r="AC22" s="4"/>
     </row>
-    <row r="23" spans="1:29" ht="221">
+    <row r="23" spans="1:29" s="3" customFormat="1" ht="222">
       <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="E23" s="3" t="s">
-        <v>191</v>
+        <v>22</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>70</v>
+        <v>172</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>173</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="J23" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="P23" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="5" t="s">
+      <c r="J23" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="O23" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="P23" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="R23" s="5" t="s">
-        <v>184</v>
+      <c r="R23" s="21" t="s">
+        <v>141</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="U23" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="V23" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="W23" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="X23" s="4" t="s">
-        <v>193</v>
+        <v>88</v>
       </c>
       <c r="Y23" s="4" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="Z23" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AA23" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="AB23" s="5"/>
+        <v>174</v>
+      </c>
+      <c r="AB23" s="4"/>
       <c r="AC23" s="4"/>
     </row>
-    <row r="24" spans="1:29" s="3" customFormat="1" ht="222">
+    <row r="24" spans="1:29" s="3" customFormat="1" ht="187">
       <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>71</v>
+        <v>168</v>
+      </c>
+      <c r="C24" s="3">
+        <v>2022</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>22</v>
+        <v>169</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>155</v>
+        <v>208</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="L24" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="N24" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="O24" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="P24" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="P24" s="4" t="s">
         <v>3</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="R24" s="21" t="s">
-        <v>144</v>
+        <v>181</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>182</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="W24" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="X24" s="4" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="Y24" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Z24" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA24" s="4" t="s">
-        <v>177</v>
+        <v>186</v>
+      </c>
+      <c r="AA24" s="5" t="s">
+        <v>171</v>
       </c>
       <c r="AB24" s="4"/>
       <c r="AC24" s="4"/>
     </row>
-    <row r="25" spans="1:29" s="3" customFormat="1" ht="187">
+    <row r="25" spans="1:29" s="3" customFormat="1" ht="272">
       <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>171</v>
+      <c r="B25" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="C25" s="3">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>172</v>
+        <v>22</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
       <c r="G25" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="H25" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="M25" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="N25" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="O25" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="P25" s="4" t="s">
+      <c r="I25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="O25" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="P25" s="5" t="s">
         <v>3</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>188</v>
+        <v>180</v>
+      </c>
+      <c r="R25" s="5" t="s">
+        <v>179</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="T25" s="4" t="s">
-        <v>217</v>
+        <v>166</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>198</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="V25" s="4" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="W25" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="X25" s="4" t="s">
-        <v>193</v>
+        <v>88</v>
       </c>
       <c r="Y25" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="Z25" s="4" t="s">
-        <v>193</v>
+        <v>88</v>
       </c>
       <c r="AA25" s="5" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="AB25" s="4"/>
       <c r="AC25" s="4"/>
     </row>
-    <row r="26" spans="1:29" s="3" customFormat="1" ht="272">
-      <c r="A26" s="3">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="O26" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="P26" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="R26" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="S26" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="T26" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="U26" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="V26" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="W26" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="X26" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y26" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z26" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA26" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="AB26" s="4"/>
-      <c r="AC26" s="4"/>
+    <row r="26" spans="1:29">
+      <c r="A26" s="3"/>
+      <c r="D26" s="17"/>
+      <c r="Q26"/>
     </row>
     <row r="27" spans="1:29">
-      <c r="A27" s="3"/>
-      <c r="D27" s="17"/>
       <c r="Q27"/>
     </row>
-    <row r="28" spans="1:29">
-      <c r="Q28"/>
+    <row r="28" spans="1:29" ht="18">
+      <c r="D28" s="8"/>
+      <c r="Q28" s="18"/>
     </row>
     <row r="29" spans="1:29" ht="18">
       <c r="D29" s="8"/>
@@ -3669,24 +3551,24 @@
       <c r="D31" s="8"/>
       <c r="Q31" s="18"/>
     </row>
-    <row r="32" spans="1:29" ht="18">
+    <row r="32" spans="1:29">
       <c r="D32" s="8"/>
-      <c r="Q32" s="18"/>
     </row>
     <row r="33" spans="3:4">
-      <c r="D33" s="8"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
     </row>
     <row r="34" spans="3:4">
       <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
+      <c r="D34" s="19"/>
     </row>
     <row r="35" spans="3:4">
       <c r="C35" s="1"/>
-      <c r="D35" s="19"/>
+      <c r="D35" s="1"/>
     </row>
     <row r="36" spans="3:4">
       <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
+      <c r="D36" s="19"/>
     </row>
     <row r="37" spans="3:4">
       <c r="C37" s="1"/>
@@ -3697,8 +3579,7 @@
       <c r="D38" s="19"/>
     </row>
     <row r="39" spans="3:4">
-      <c r="C39" s="1"/>
-      <c r="D39" s="19"/>
+      <c r="D39" s="8"/>
     </row>
     <row r="40" spans="3:4">
       <c r="D40" s="8"/>
@@ -3710,13 +3591,10 @@
       <c r="D42" s="8"/>
     </row>
     <row r="43" spans="3:4">
-      <c r="D43" s="8"/>
+      <c r="D43" s="4"/>
     </row>
     <row r="44" spans="3:4">
-      <c r="D44" s="4"/>
-    </row>
-    <row r="45" spans="3:4">
-      <c r="D45" s="5"/>
+      <c r="D44" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Evidence_Table.xlsx
+++ b/data/Evidence_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramanaye/Documents/GitHub/cancer_nutrition_evidence_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FAA694-0EDC-A544-AAAC-9BAFD87591F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BF9A19-CD80-8D40-AD89-B252DEBFB24E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="14600" windowHeight="16140" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
   </bookViews>
   <sheets>
     <sheet name="Evidence Table" sheetId="1" r:id="rId1"/>
@@ -327,10 +327,6 @@
 3. Psychology - 60-minute session with a psychology-trained researcher for anxiety reduction + personalized relaxation techniques (visualization and breathing exercises) practiced at home 2-3 times/week using audio tracks</t>
   </si>
   <si>
-    <t>PREHAB+ - 41 (4)
-REHAB - 32  (6)</t>
-  </si>
-  <si>
     <t>REHAB group- received standard post-surgical rehabilitation</t>
   </si>
   <si>
@@ -370,10 +366,6 @@
     <t>Not reported</t>
   </si>
   <si>
-    <t>Prehab -24 (6)
-Control -10 (2)</t>
-  </si>
-  <si>
     <t>Control group- received standard hospital care</t>
   </si>
   <si>
@@ -421,10 +413,6 @@
   </si>
   <si>
     <t>Control group-  received usual clinical care</t>
-  </si>
-  <si>
-    <t>Prehabilitation – 18 (6) 
-Control – 22 (2)</t>
   </si>
   <si>
     <t>control group -received standard care which consisted of nutritional counseling, physical activity recommendations, and advice on smoking cessation</t>
@@ -648,10 +636,6 @@
 medical coaching adherence - 82 ± 20%</t>
   </si>
   <si>
-    <t>Prehabilitation – 52 (14) 
-Rehabilitation – 43 (15)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Multimodal program:
 1. Exercise: Home-based, unsupervised. Moderate-vigorous aerobic training for 30 minutes, 3 days/week. Resistance training with 10 exercises targeting major muscle groups, 2 sets of 8–12 repetitions, 3 days/week using elastic bands.
 2. Nutritional support: Individualized care from a registered dietitian. Target protein intake of 1.5 g/kg ideal body weight, supplemented with whey protein within 1 hour of exercise as needed.
@@ -868,6 +852,22 @@
   <si>
     <t>Nutrition -93.2%
 Exercises- 88.2% (home-based) and 84.1% (supervised)</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 66 (14) 
+Rehabilitation – 58 (15)</t>
+  </si>
+  <si>
+    <t>Prehabilitation – 24(6)
+Control – 24 (2)</t>
+  </si>
+  <si>
+    <t>PREHAB+ - 41 (4)
+REHAB - 39 (13)</t>
+  </si>
+  <si>
+    <t>Prehab -24 (10)
+Control -10 (3)</t>
   </si>
 </sst>
 </file>
@@ -1407,7 +1407,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1425,31 +1425,31 @@
         <v>1</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="Q1" s="7" t="s">
         <v>71</v>
@@ -1461,25 +1461,25 @@
         <v>2</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>72</v>
@@ -1507,7 +1507,7 @@
         <v>74</v>
       </c>
       <c r="G2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>69</v>
@@ -1519,7 +1519,7 @@
         <v>3</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>3</v>
@@ -1528,43 +1528,43 @@
         <v>3</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Q2" s="6" t="s">
         <v>75</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AA2" s="22">
         <v>0.63</v>
@@ -1589,10 +1589,10 @@
         <v>22</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>78</v>
+        <v>240</v>
       </c>
       <c r="G3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>77</v>
@@ -1604,7 +1604,7 @@
         <v>3</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>3</v>
@@ -1613,46 +1613,46 @@
         <v>3</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P3" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q3" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA3" s="9" t="s">
         <v>79</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA3" s="9" t="s">
-        <v>80</v>
       </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
@@ -1674,70 +1674,70 @@
         <v>8</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" t="s">
+        <v>148</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="G4" t="s">
-        <v>151</v>
-      </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q4" s="4" t="s">
+      <c r="R4" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="U4" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="W4" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="X4" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y4" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA4" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="R4" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="T4" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="U4" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="V4" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="W4" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="X4" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y4" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="Z4" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA4" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="AB4" s="6"/>
       <c r="AC4" s="6"/>
@@ -1759,70 +1759,70 @@
         <v>8</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="R5" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
@@ -1835,19 +1835,19 @@
         <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>89</v>
+        <v>241</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>17</v>
@@ -1859,7 +1859,7 @@
         <v>3</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>3</v>
@@ -1868,7 +1868,7 @@
         <v>3</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="O6" s="4" t="s">
         <v>3</v>
@@ -1877,37 +1877,37 @@
         <v>3</v>
       </c>
       <c r="Q6" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Z6" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AA6" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
@@ -1929,10 +1929,10 @@
         <v>8</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>20</v>
@@ -1944,7 +1944,7 @@
         <v>3</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>3</v>
@@ -1953,7 +1953,7 @@
         <v>3</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="O7" s="9" t="s">
         <v>3</v>
@@ -1962,37 +1962,37 @@
         <v>3</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="R7" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="S7" s="8" t="s">
         <v>21</v>
       </c>
       <c r="T7" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="U7" s="8" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="V7" s="8" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="W7" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="X7" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Y7" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Z7" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AA7" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
@@ -2014,10 +2014,10 @@
         <v>22</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>25</v>
@@ -2041,43 +2041,43 @@
         <v>3</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AA8" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AB8" s="4"/>
       <c r="AC8" s="4"/>
@@ -2099,10 +2099,10 @@
         <v>22</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>40</v>
@@ -2123,46 +2123,46 @@
         <v>3</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P9" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q9" s="16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Z9" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AA9" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
@@ -2184,10 +2184,10 @@
         <v>22</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>105</v>
+        <v>239</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>42</v>
@@ -2202,7 +2202,7 @@
         <v>3</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M10" s="5" t="s">
         <v>3</v>
@@ -2214,40 +2214,40 @@
         <v>3</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y10" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z10" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AA10" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AB10" s="4"/>
       <c r="AC10" s="4"/>
@@ -2269,10 +2269,10 @@
         <v>22</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>43</v>
@@ -2284,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>3</v>
@@ -2293,43 +2293,43 @@
         <v>3</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="W11" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y11" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Z11" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AA11" s="23">
         <v>0.83299999999999996</v>
@@ -2354,10 +2354,10 @@
         <v>22</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G12" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>45</v>
@@ -2387,37 +2387,37 @@
         <v>3</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y12" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z12" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AA12" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
@@ -2439,10 +2439,10 @@
         <v>22</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G13" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>47</v>
@@ -2454,7 +2454,7 @@
         <v>3</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>3</v>
@@ -2463,46 +2463,46 @@
         <v>3</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>3</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="V13" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="X13" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Y13" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z13" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AA13" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="AB13" s="4"/>
       <c r="AC13" s="5"/>
@@ -2524,10 +2524,10 @@
         <v>49</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G14" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>50</v>
@@ -2539,55 +2539,55 @@
         <v>3</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Y14" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Z14" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AA14" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="AB14" s="4"/>
       <c r="AC14" s="4"/>
@@ -2609,10 +2609,10 @@
         <v>22</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G15" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>52</v>
@@ -2636,40 +2636,40 @@
         <v>3</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P15" s="5" t="s">
         <v>3</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Z15" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AA15" s="24">
         <v>0.873</v>
@@ -2694,10 +2694,10 @@
         <v>22</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G16" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>53</v>
@@ -2709,10 +2709,10 @@
         <v>3</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>3</v>
@@ -2727,34 +2727,34 @@
         <v>3</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="V16" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="W16" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AA16" s="23">
         <v>0.84399999999999997</v>
@@ -2779,10 +2779,10 @@
         <v>22</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G17" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>55</v>
@@ -2794,7 +2794,7 @@
         <v>3</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L17" s="9" t="s">
         <v>3</v>
@@ -2809,40 +2809,40 @@
         <v>3</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="R17" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="V17" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="W17" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z17" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AA17" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AB17" s="4"/>
       <c r="AC17" s="4"/>
@@ -2864,10 +2864,10 @@
         <v>22</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G18" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>57</v>
@@ -2879,7 +2879,7 @@
         <v>3</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L18" s="4" t="s">
         <v>3</v>
@@ -2891,43 +2891,43 @@
         <v>3</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="U18" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="V18" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="W18" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="X18" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Y18" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z18" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AA18" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
@@ -2949,10 +2949,10 @@
         <v>22</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G19" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>59</v>
@@ -2964,55 +2964,55 @@
         <v>3</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L19" s="4" t="s">
         <v>3</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="U19" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="V19" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="W19" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="X19" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Y19" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z19" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AA19" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="AB19" s="4"/>
       <c r="AC19" s="4"/>
@@ -3034,10 +3034,10 @@
         <v>22</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G20" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>61</v>
@@ -3046,7 +3046,7 @@
         <v>3</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>3</v>
@@ -3061,43 +3061,43 @@
         <v>3</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="V20" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="W20" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y20" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Z20" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AA20" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AB20" s="4"/>
       <c r="AC20" s="4"/>
@@ -3119,10 +3119,10 @@
         <v>22</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G21" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>63</v>
@@ -3131,7 +3131,7 @@
         <v>3</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>3</v>
@@ -3146,43 +3146,43 @@
         <v>3</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="T21" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="U21" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="V21" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="W21" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="X21" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y21" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z21" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AA21" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AB21" s="4"/>
       <c r="AC21" s="4"/>
@@ -3204,10 +3204,10 @@
         <v>66</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>67</v>
@@ -3219,55 +3219,55 @@
         <v>3</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="M22" s="5" t="s">
         <v>3</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P22" s="5" t="s">
         <v>3</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="V22" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="W22" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Y22" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z22" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AA22" s="4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="AB22" s="5"/>
       <c r="AC22" s="4"/>
@@ -3280,7 +3280,7 @@
         <v>15</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>68</v>
@@ -3289,13 +3289,13 @@
         <v>22</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>172</v>
+        <v>238</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>3</v>
@@ -3304,7 +3304,7 @@
         <v>3</v>
       </c>
       <c r="K23" s="20" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L23" s="20" t="s">
         <v>3</v>
@@ -3313,46 +3313,46 @@
         <v>3</v>
       </c>
       <c r="N23" s="20" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="O23" s="20" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P23" s="20" t="s">
         <v>3</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="R23" s="21" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="U23" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="V23" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="W23" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="X23" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y23" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Z23" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AA23" s="4" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AB23" s="4"/>
       <c r="AC23" s="4"/>
@@ -3362,25 +3362,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C24" s="3">
         <v>2022</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>3</v>
@@ -3389,55 +3389,55 @@
         <v>3</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>3</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P24" s="4" t="s">
         <v>3</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="W24" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="X24" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Y24" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Z24" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AA24" s="5" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="AB24" s="4"/>
       <c r="AC24" s="4"/>
@@ -3447,82 +3447,82 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C25" s="3">
         <v>2024</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F25" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="O25" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="P25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q25" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="R25" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="S25" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="U25" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="V25" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="W25" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="X25" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y25" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z25" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA25" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="M25" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="N25" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="O25" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="P25" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q25" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="R25" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="S25" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="T25" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="U25" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="V25" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="W25" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="X25" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y25" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="Z25" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA25" s="5" t="s">
-        <v>167</v>
       </c>
       <c r="AB25" s="4"/>
       <c r="AC25" s="4"/>

--- a/data/Evidence_Table.xlsx
+++ b/data/Evidence_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramanaye/Documents/GitHub/cancer_nutrition_evidence_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BF9A19-CD80-8D40-AD89-B252DEBFB24E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D4EA6D-3C83-D547-88D6-0E96CD8D965E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="14600" windowHeight="16140" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="14600" windowHeight="16120" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
   </bookViews>
   <sheets>
     <sheet name="Evidence Table" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="241">
   <si>
     <t>Year</t>
   </si>
@@ -282,9 +282,6 @@
     <t>Waller et al.</t>
   </si>
   <si>
-    <t>Randomised controlled pilot study</t>
-  </si>
-  <si>
     <t>Tri-modal prehabilitation delivered via Fitbit smartwatch and smartphone apps:
 1. Exercise - Individualised aerobic exercise (3x/week) + resistance training with bands (2x/week) + 30 min of additional physical activity like walking or stairs (2x/week). Intensity tailored to 50–70% of predicted maximum heart rate and BORG scale 12–16.
 2. Nutrition - Written dietary advice and educational presentation focused on protein intake and avoiding weight loss + monitoring via Fitbit App food log.
@@ -725,9 +722,6 @@
 Psychological health</t>
   </si>
   <si>
-    <t>Randomized Controlled Feasibility Trial</t>
-  </si>
-  <si>
     <t>Author</t>
   </si>
   <si>
@@ -868,6 +862,9 @@
   <si>
     <t>Prehab -24 (10)
 Control -10 (3)</t>
+  </si>
+  <si>
+    <t>Pilot Randomised Controlled  Study</t>
   </si>
 </sst>
 </file>
@@ -1380,7 +1377,8 @@
     <col min="2" max="2" width="12.5" style="3" customWidth="1"/>
     <col min="3" max="3" width="19.33203125" customWidth="1"/>
     <col min="4" max="4" width="37" style="6" customWidth="1"/>
-    <col min="5" max="6" width="22.5" customWidth="1"/>
+    <col min="5" max="5" width="32.5" customWidth="1"/>
+    <col min="6" max="6" width="22.5" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
     <col min="8" max="8" width="54.83203125" style="6" customWidth="1"/>
     <col min="9" max="9" width="25" style="6" customWidth="1"/>
@@ -1407,7 +1405,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1416,73 +1414,73 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I1" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="L1" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="K1" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>144</v>
-      </c>
       <c r="M1" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="V1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="X1" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="Z1" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
@@ -1504,67 +1502,67 @@
         <v>8</v>
       </c>
       <c r="F2" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q2" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="G2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>75</v>
-      </c>
       <c r="R2" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AA2" s="22">
         <v>0.63</v>
@@ -1589,70 +1587,70 @@
         <v>22</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H3" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="I3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q3" s="6" t="s">
+      <c r="R3" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA3" s="9" t="s">
         <v>78</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA3" s="9" t="s">
-        <v>79</v>
       </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
@@ -1674,70 +1672,70 @@
         <v>8</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G4" t="s">
+        <v>147</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="G4" t="s">
-        <v>148</v>
-      </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q4" s="4" t="s">
+      <c r="R4" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="U4" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="W4" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="X4" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y4" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA4" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="R4" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="T4" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="U4" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="V4" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="W4" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="X4" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y4" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="Z4" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA4" s="4" t="s">
-        <v>83</v>
       </c>
       <c r="AB4" s="6"/>
       <c r="AC4" s="6"/>
@@ -1759,70 +1757,70 @@
         <v>8</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>86</v>
-      </c>
       <c r="R5" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
@@ -1835,19 +1833,19 @@
         <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>17</v>
@@ -1859,7 +1857,7 @@
         <v>3</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>3</v>
@@ -1868,7 +1866,7 @@
         <v>3</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O6" s="4" t="s">
         <v>3</v>
@@ -1877,37 +1875,37 @@
         <v>3</v>
       </c>
       <c r="Q6" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Z6" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AA6" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
@@ -1929,10 +1927,10 @@
         <v>8</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>20</v>
@@ -1944,7 +1942,7 @@
         <v>3</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>3</v>
@@ -1953,7 +1951,7 @@
         <v>3</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O7" s="9" t="s">
         <v>3</v>
@@ -1962,37 +1960,37 @@
         <v>3</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R7" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S7" s="8" t="s">
         <v>21</v>
       </c>
       <c r="T7" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="U7" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V7" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W7" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="X7" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Y7" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Z7" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AA7" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
@@ -2014,10 +2012,10 @@
         <v>22</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>25</v>
@@ -2041,43 +2039,43 @@
         <v>3</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AA8" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AB8" s="4"/>
       <c r="AC8" s="4"/>
@@ -2099,10 +2097,10 @@
         <v>22</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>40</v>
@@ -2123,46 +2121,46 @@
         <v>3</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P9" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q9" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Z9" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AA9" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
@@ -2184,10 +2182,10 @@
         <v>22</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>42</v>
@@ -2202,7 +2200,7 @@
         <v>3</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M10" s="5" t="s">
         <v>3</v>
@@ -2214,40 +2212,40 @@
         <v>3</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Y10" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z10" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AA10" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AB10" s="4"/>
       <c r="AC10" s="4"/>
@@ -2269,10 +2267,10 @@
         <v>22</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>43</v>
@@ -2284,7 +2282,7 @@
         <v>3</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>3</v>
@@ -2293,43 +2291,43 @@
         <v>3</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q11" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="R11" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="R11" s="6" t="s">
-        <v>106</v>
-      </c>
       <c r="S11" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W11" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Y11" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Z11" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AA11" s="23">
         <v>0.83299999999999996</v>
@@ -2351,13 +2349,13 @@
         <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>165</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>45</v>
@@ -2387,37 +2385,37 @@
         <v>3</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Y12" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z12" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AA12" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
@@ -2439,10 +2437,10 @@
         <v>22</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>47</v>
@@ -2454,7 +2452,7 @@
         <v>3</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>3</v>
@@ -2463,46 +2461,46 @@
         <v>3</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>3</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q13" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="R13" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="R13" s="6" t="s">
+      <c r="S13" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="T13" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="V13" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="W13" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="X13" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y13" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z13" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA13" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="S13" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="T13" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="U13" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="V13" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="W13" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="X13" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="Y13" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z13" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA13" s="4" t="s">
-        <v>113</v>
       </c>
       <c r="AB13" s="4"/>
       <c r="AC13" s="5"/>
@@ -2524,10 +2522,10 @@
         <v>49</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>50</v>
@@ -2539,55 +2537,55 @@
         <v>3</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="Q14" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="S14" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="T14" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="U14" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="V14" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="W14" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="X14" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y14" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z14" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA14" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="R14" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="S14" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="T14" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="U14" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="V14" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="W14" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="X14" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="Y14" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z14" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA14" s="4" t="s">
-        <v>116</v>
       </c>
       <c r="AB14" s="4"/>
       <c r="AC14" s="4"/>
@@ -2609,10 +2607,10 @@
         <v>22</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>52</v>
@@ -2636,40 +2634,40 @@
         <v>3</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P15" s="5" t="s">
         <v>3</v>
       </c>
       <c r="Q15" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="R15" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="R15" s="5" t="s">
-        <v>119</v>
-      </c>
       <c r="S15" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Z15" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AA15" s="24">
         <v>0.873</v>
@@ -2694,10 +2692,10 @@
         <v>22</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>53</v>
@@ -2709,10 +2707,10 @@
         <v>3</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>3</v>
@@ -2727,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V16" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W16" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AA16" s="23">
         <v>0.84399999999999997</v>
@@ -2779,10 +2777,10 @@
         <v>22</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>55</v>
@@ -2794,7 +2792,7 @@
         <v>3</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L17" s="9" t="s">
         <v>3</v>
@@ -2809,40 +2807,40 @@
         <v>3</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R17" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="V17" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W17" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z17" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AA17" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AB17" s="4"/>
       <c r="AC17" s="4"/>
@@ -2864,10 +2862,10 @@
         <v>22</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>57</v>
@@ -2879,7 +2877,7 @@
         <v>3</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L18" s="4" t="s">
         <v>3</v>
@@ -2891,43 +2889,43 @@
         <v>3</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q18" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="R18" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="R18" s="4" t="s">
+      <c r="S18" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="T18" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="U18" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="V18" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="W18" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="X18" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y18" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z18" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA18" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="S18" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="T18" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="U18" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="V18" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="W18" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="X18" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="Y18" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z18" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="AA18" s="4" t="s">
-        <v>127</v>
       </c>
       <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
@@ -2949,10 +2947,10 @@
         <v>22</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>59</v>
@@ -2964,55 +2962,55 @@
         <v>3</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L19" s="4" t="s">
         <v>3</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q19" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="R19" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="S19" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="T19" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="V19" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="W19" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="X19" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y19" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z19" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA19" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="R19" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="S19" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="T19" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="U19" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="V19" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="W19" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="X19" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="Y19" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z19" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA19" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="AB19" s="4"/>
       <c r="AC19" s="4"/>
@@ -3034,10 +3032,10 @@
         <v>22</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>61</v>
@@ -3046,7 +3044,7 @@
         <v>3</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>3</v>
@@ -3061,43 +3059,43 @@
         <v>3</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V20" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W20" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Y20" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Z20" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AA20" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AB20" s="4"/>
       <c r="AC20" s="4"/>
@@ -3119,10 +3117,10 @@
         <v>22</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>63</v>
@@ -3131,7 +3129,7 @@
         <v>3</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>3</v>
@@ -3146,43 +3144,43 @@
         <v>3</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q21" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="R21" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="R21" s="6" t="s">
+      <c r="S21" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="T21" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="U21" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="V21" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="W21" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="X21" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y21" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z21" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA21" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="S21" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="T21" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="U21" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="V21" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="W21" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="X21" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y21" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z21" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA21" s="4" t="s">
-        <v>136</v>
       </c>
       <c r="AB21" s="4"/>
       <c r="AC21" s="4"/>
@@ -3201,73 +3199,73 @@
         <v>64</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="I22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="O22" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="P22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="M22" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="O22" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="P22" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="4" t="s">
+      <c r="R22" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="S22" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="T22" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="U22" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="V22" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="W22" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="X22" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y22" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z22" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA22" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="R22" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="S22" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="T22" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="U22" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="V22" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="W22" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="X22" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="Y22" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z22" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA22" s="4" t="s">
-        <v>173</v>
       </c>
       <c r="AB22" s="5"/>
       <c r="AC22" s="4"/>
@@ -3280,79 +3278,79 @@
         <v>15</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H23" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="O23" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="P23" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="R23" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="S23" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="T23" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="U23" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="V23" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="W23" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="X23" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y23" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z23" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA23" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="L23" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="O23" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="P23" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="R23" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="S23" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="T23" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="U23" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="V23" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="W23" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="X23" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y23" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z23" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA23" s="4" t="s">
-        <v>170</v>
       </c>
       <c r="AB23" s="4"/>
       <c r="AC23" s="4"/>
@@ -3362,82 +3360,82 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C24" s="3">
         <v>2022</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="H24" s="4" t="s">
+      <c r="I24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="P24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="S24" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="T24" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="U24" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="V24" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="W24" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="X24" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y24" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z24" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="AA24" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="M24" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="N24" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="O24" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="P24" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="S24" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="T24" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="U24" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="V24" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="W24" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="X24" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="Y24" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z24" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="AA24" s="5" t="s">
-        <v>168</v>
       </c>
       <c r="AB24" s="4"/>
       <c r="AC24" s="4"/>
@@ -3447,82 +3445,82 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C25" s="3">
         <v>2024</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F25" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="H25" s="5" t="s">
+      <c r="I25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="O25" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="P25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q25" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="R25" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="S25" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="M25" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="N25" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="O25" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="P25" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q25" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="R25" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="S25" s="4" t="s">
+      <c r="T25" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="U25" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="V25" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="W25" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="X25" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y25" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z25" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA25" s="5" t="s">
         <v>163</v>
-      </c>
-      <c r="T25" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="U25" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="V25" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="W25" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="X25" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y25" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="Z25" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA25" s="5" t="s">
-        <v>164</v>
       </c>
       <c r="AB25" s="4"/>
       <c r="AC25" s="4"/>

--- a/data/Evidence_Table.xlsx
+++ b/data/Evidence_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramanaye/Documents/GitHub/cancer_nutrition_evidence_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D4EA6D-3C83-D547-88D6-0E96CD8D965E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47F7C08-6335-BA4F-8A26-00466FFFC647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="14600" windowHeight="16120" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
   </bookViews>
   <sheets>
     <sheet name="Evidence Table" sheetId="1" r:id="rId1"/>
@@ -2768,7 +2768,7 @@
         <v>54</v>
       </c>
       <c r="C17">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>35</v>
@@ -2853,7 +2853,7 @@
         <v>56</v>
       </c>
       <c r="C18">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>36</v>

--- a/data/Evidence_Table.xlsx
+++ b/data/Evidence_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramanaye/Documents/GitHub/cancer_nutrition_evidence_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47F7C08-6335-BA4F-8A26-00466FFFC647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E2DFD8-8BF4-6D4D-87DE-4EC81D5FCEF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
+    <workbookView xWindow="14260" yWindow="500" windowWidth="14540" windowHeight="16180" xr2:uid="{4D926D7D-19DF-E54A-9976-ED1795FE3A18}"/>
   </bookViews>
   <sheets>
     <sheet name="Evidence Table" sheetId="1" r:id="rId1"/>
@@ -871,7 +871,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -960,6 +960,11 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow (Body)"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -981,7 +986,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1036,6 +1041,9 @@
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2056,7 +2064,7 @@
       <c r="T8" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="U8" s="4" t="s">
+      <c r="U8" s="25" t="s">
         <v>181</v>
       </c>
       <c r="V8" s="4" t="s">
@@ -2567,7 +2575,7 @@
         <v>187</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="V14" s="4" t="s">
         <v>86</v>
@@ -2822,7 +2830,7 @@
         <v>200</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V17" s="4" t="s">
         <v>182</v>
@@ -2831,7 +2839,7 @@
         <v>182</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Y17" s="4" t="s">
         <v>86</v>
